--- a/data/clases/2026-06-02/Component_A_2026-06-02.xlsx
+++ b/data/clases/2026-06-02/Component_A_2026-06-02.xlsx
@@ -578,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K320"/>
+  <dimension ref="A1:K440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2142,165 +2142,194 @@
       <c r="H84" s="12" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL (sum of scores)</t>
-        </is>
-      </c>
-      <c r="C85" s="15" t="n">
-        <v>79</v>
-      </c>
-      <c r="D85" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>16</v>
-      </c>
-      <c r="F85" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="G85" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="H85" s="16" t="n"/>
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>70:45</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>And for example, here you're not mentioning Round. Round is ongoing and it's a possible candidate. Why is it not here? → Aryang</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D85" s="11" t="inlineStr"/>
+      <c r="E85" s="11" t="inlineStr"/>
+      <c r="F85" s="11" t="inlineStr"/>
+      <c r="G85" s="11" t="inlineStr"/>
+      <c r="H85" s="12" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="B86" s="17" t="inlineStr">
-        <is>
-          <t>Max possible (n_opp × 6)</t>
-        </is>
-      </c>
-      <c r="C86" s="18" t="n">
-        <v>186</v>
-      </c>
-      <c r="D86" s="18" t="n">
-        <v>42</v>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>54</v>
-      </c>
-      <c r="F86" s="18" t="n">
-        <v>36</v>
-      </c>
-      <c r="G86" s="18" t="n">
-        <v>36</v>
-      </c>
-      <c r="H86" s="12" t="n"/>
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>74:22</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Any other thing you want to share? For preliminary synthesis? (open)</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr"/>
+      <c r="D86" s="11" t="inlineStr"/>
+      <c r="E86" s="11" t="inlineStr"/>
+      <c r="F86" s="11" t="inlineStr"/>
+      <c r="G86" s="11" t="inlineStr"/>
+      <c r="H86" s="12" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="B87" s="19" t="inlineStr">
-        <is>
-          <t>% Grade (max 7.5%)</t>
-        </is>
-      </c>
-      <c r="C87" s="20" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="D87" s="20" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E87" s="20" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="F87" s="20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G87" s="20" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="H87" s="21" t="n"/>
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>75:33</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>And I gave you like, how are other countries solving this issue? (open)</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr"/>
+      <c r="D87" s="11" t="inlineStr"/>
+      <c r="E87" s="11" t="inlineStr"/>
+      <c r="F87" s="11" t="inlineStr"/>
+      <c r="G87" s="11" t="inlineStr"/>
+      <c r="H87" s="12" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>75:58</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>What have countries done? (open)</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr"/>
+      <c r="D88" s="11" t="inlineStr"/>
+      <c r="E88" s="11" t="inlineStr"/>
+      <c r="F88" s="11" t="inlineStr"/>
+      <c r="G88" s="11" t="inlineStr"/>
+      <c r="H88" s="12" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>PARTICIPATION (7.5%) — Questions from Student / Voluntary</t>
-        </is>
-      </c>
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>76:00</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Prior to the AI era or in the AI era. You want to really understand the global landscape. What are others doing? (open)</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr"/>
+      <c r="D89" s="11" t="inlineStr"/>
+      <c r="E89" s="11" t="inlineStr"/>
+      <c r="F89" s="11" t="inlineStr"/>
+      <c r="G89" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H89" s="12" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>Pregunta del alumno o comentario voluntario: 1–6 · Otros alumnos en esa fila: N/A</t>
-        </is>
-      </c>
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>76:24</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>How have they been? Yeah. → Sthepen</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr"/>
+      <c r="D90" s="11" t="inlineStr"/>
+      <c r="E90" s="11" t="inlineStr"/>
+      <c r="F90" s="11" t="inlineStr"/>
+      <c r="G90" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H90" s="12" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>76:40</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>What are countries that we know that are really best practice models that have solved this in a different way? → Sthepen</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr"/>
+      <c r="D91" s="11" t="inlineStr"/>
+      <c r="E91" s="11" t="inlineStr"/>
+      <c r="F91" s="11" t="inlineStr"/>
+      <c r="G91" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="12" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>Aryang</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
-        <is>
-          <t>Mega</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Chilaka</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>Grace</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>Sthepen</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>Notes / Feedback</t>
-        </is>
-      </c>
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>78:24</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Say that again, please? I couldn't understand. → Mega</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr"/>
+      <c r="D92" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" s="11" t="inlineStr"/>
+      <c r="F92" s="11" t="inlineStr"/>
+      <c r="G92" s="11" t="inlineStr"/>
+      <c r="H92" s="12" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>02:41</t>
+          <t>78:57</t>
         </is>
       </c>
       <c r="B93" s="10" t="inlineStr">
         <is>
-          <t>[Comment] presents and</t>
+          <t>Ah, so he already wants to match you with that company. → Mega</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr"/>
-      <c r="D93" s="11" t="inlineStr"/>
+      <c r="D93" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="E93" s="11" t="inlineStr"/>
-      <c r="F93" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F93" s="11" t="inlineStr"/>
       <c r="G93" s="11" t="inlineStr"/>
       <c r="H93" s="12" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>03:21</t>
+          <t>79:09</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Actually, they uh, they replied, they are available after 11, right?</t>
-        </is>
-      </c>
-      <c r="C94" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D94" s="11" t="inlineStr"/>
+          <t>So you're discussing with them with him about the possibility to match with that company. Okay. → Mega</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr"/>
+      <c r="D94" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="E94" s="11" t="inlineStr"/>
       <c r="F94" s="11" t="inlineStr"/>
       <c r="G94" s="11" t="inlineStr"/>
@@ -2309,58 +2338,58 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>03:25</t>
+          <t>80:51</t>
         </is>
       </c>
       <c r="B95" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah.</t>
+          <t>What else? (open)</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr"/>
-      <c r="D95" s="11" t="inlineStr"/>
+      <c r="D95" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E95" s="11" t="inlineStr"/>
-      <c r="F95" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F95" s="11" t="inlineStr"/>
       <c r="G95" s="11" t="inlineStr"/>
       <c r="H95" s="12" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>03:26</t>
+          <t>80:57</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Next month Monday.</t>
+          <t>You spoke to PLN about this? → Mega</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr"/>
-      <c r="D96" s="11" t="inlineStr"/>
+      <c r="D96" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E96" s="11" t="inlineStr"/>
-      <c r="F96" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F96" s="11" t="inlineStr"/>
       <c r="G96" s="11" t="inlineStr"/>
       <c r="H96" s="12" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>03:34</t>
+          <t>82:04</t>
         </is>
       </c>
       <c r="B97" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I think yeah.</t>
-        </is>
-      </c>
-      <c r="C97" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D97" s="11" t="inlineStr"/>
+          <t>You don't think I was a student, too? (open)</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr"/>
+      <c r="D97" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="E97" s="11" t="inlineStr"/>
       <c r="F97" s="11" t="inlineStr"/>
       <c r="G97" s="11" t="inlineStr"/>
@@ -2369,18 +2398,18 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>03:50</t>
+          <t>82:33</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So 11:15 to 11 to 12 to 1:15.</t>
-        </is>
-      </c>
-      <c r="C98" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D98" s="11" t="inlineStr"/>
+          <t>What do you understand for Let's go, okay. → Mega</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr"/>
+      <c r="D98" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="E98" s="11" t="inlineStr"/>
       <c r="F98" s="11" t="inlineStr"/>
       <c r="G98" s="11" t="inlineStr"/>
@@ -2389,18 +2418,18 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>03:57</t>
+          <t>82:36</t>
         </is>
       </c>
       <c r="B99" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Lunchtime.</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D99" s="11" t="inlineStr"/>
+          <t>Mega, is there anything you want to add more? → Mega</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr"/>
+      <c r="D99" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E99" s="11" t="inlineStr"/>
       <c r="F99" s="11" t="inlineStr"/>
       <c r="G99" s="11" t="inlineStr"/>
@@ -2409,37 +2438,35 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>03:58</t>
+          <t>83:14</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] No, no. No lunchtime.</t>
+          <t>Okay, anything else? → Mega</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr"/>
-      <c r="D100" s="11" t="inlineStr"/>
+      <c r="D100" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="E100" s="11" t="inlineStr"/>
-      <c r="F100" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F100" s="11" t="inlineStr"/>
       <c r="G100" s="11" t="inlineStr"/>
       <c r="H100" s="12" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>03:59</t>
+          <t>83:49</t>
         </is>
       </c>
       <c r="B101" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Oh, really?</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>to explain to me a little bit of what's the difference between stage one and sorry, stop. (open)</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr"/>
       <c r="D101" s="11" t="inlineStr"/>
       <c r="E101" s="11" t="inlineStr"/>
       <c r="F101" s="11" t="inlineStr"/>
@@ -2449,37 +2476,33 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>83:54</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Whoa, whoa, whoa, whoa.</t>
+          <t>I say. (open)</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr"/>
       <c r="D102" s="11" t="inlineStr"/>
       <c r="E102" s="11" t="inlineStr"/>
-      <c r="F102" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F102" s="11" t="inlineStr"/>
       <c r="G102" s="11" t="inlineStr"/>
       <c r="H102" s="12" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>04:11</t>
+          <t>83:56</t>
         </is>
       </c>
       <c r="B103" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Same, yeah.</t>
-        </is>
-      </c>
-      <c r="C103" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>Say. (open)</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr"/>
       <c r="D103" s="11" t="inlineStr"/>
       <c r="E103" s="11" t="inlineStr"/>
       <c r="F103" s="11" t="inlineStr"/>
@@ -2489,19 +2512,17 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>84:00</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Uh, I can go.</t>
+          <t>Between, between stage one. What's the difference between demand side, supply side and preliminary due diligence? (open)</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr"/>
       <c r="D104" s="11" t="inlineStr"/>
-      <c r="E104" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E104" s="11" t="inlineStr"/>
       <c r="F104" s="11" t="inlineStr"/>
       <c r="G104" s="11" t="inlineStr"/>
       <c r="H104" s="12" t="inlineStr"/>
@@ -2509,39 +2530,39 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>05:12</t>
+          <t>84:07</t>
         </is>
       </c>
       <c r="B105" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I, I want to talk about the stage one. I, I, I, I really understood it.</t>
+          <t>What do you think is the difference? (open)</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr"/>
       <c r="D105" s="11" t="inlineStr"/>
-      <c r="E105" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E105" s="11" t="inlineStr"/>
       <c r="F105" s="11" t="inlineStr"/>
-      <c r="G105" s="11" t="inlineStr"/>
+      <c r="G105" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H105" s="12" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>05:14</t>
+          <t>85:00</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Um, for me, this is like my first time coming across.</t>
-        </is>
-      </c>
-      <c r="C106" s="11" t="inlineStr"/>
+          <t>have you done it now? → Aryang</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D106" s="11" t="inlineStr"/>
-      <c r="E106" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E106" s="11" t="inlineStr"/>
       <c r="F106" s="11" t="inlineStr"/>
       <c r="G106" s="11" t="inlineStr"/>
       <c r="H106" s="12" t="inlineStr"/>
@@ -2549,19 +2570,19 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>85:10</t>
         </is>
       </c>
       <c r="B107" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because I've heard about project management, but in this form,</t>
-        </is>
-      </c>
-      <c r="C107" s="11" t="inlineStr"/>
+          <t>Nice. And the third part? → Aryang</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D107" s="11" t="inlineStr"/>
-      <c r="E107" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="E107" s="11" t="inlineStr"/>
       <c r="F107" s="11" t="inlineStr"/>
       <c r="G107" s="11" t="inlineStr"/>
       <c r="H107" s="12" t="inlineStr"/>
@@ -2569,19 +2590,17 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>05:18</t>
+          <t>85:28</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I've not really done anything with it, especially with the 5 Ys.</t>
+          <t>Anybody can help him? (open)</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr"/>
       <c r="D108" s="11" t="inlineStr"/>
-      <c r="E108" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E108" s="11" t="inlineStr"/>
       <c r="F108" s="11" t="inlineStr"/>
       <c r="G108" s="11" t="inlineStr"/>
       <c r="H108" s="12" t="inlineStr"/>
@@ -2589,19 +2608,17 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>85:30</t>
         </is>
       </c>
       <c r="B109" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So it actually, it made me understand a lot about</t>
+          <t>Are you all there? (open)</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr"/>
       <c r="D109" s="11" t="inlineStr"/>
-      <c r="E109" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E109" s="11" t="inlineStr"/>
       <c r="F109" s="11" t="inlineStr"/>
       <c r="G109" s="11" t="inlineStr"/>
       <c r="H109" s="12" t="inlineStr"/>
@@ -2609,19 +2626,19 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>85:39</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
         <is>
-          <t>[Comment] the project I was working on, you know, prior to coming for this class.</t>
-        </is>
-      </c>
-      <c r="C110" s="11" t="inlineStr"/>
+          <t>You want to complete or you want to go from the start? Whatever you want. → Aryang</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="D110" s="11" t="inlineStr"/>
-      <c r="E110" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E110" s="11" t="inlineStr"/>
       <c r="F110" s="11" t="inlineStr"/>
       <c r="G110" s="11" t="inlineStr"/>
       <c r="H110" s="12" t="inlineStr"/>
@@ -2629,19 +2646,19 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>05:24</t>
+          <t>89:38</t>
         </is>
       </c>
       <c r="B111" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because I've always struggled.</t>
-        </is>
-      </c>
-      <c r="C111" s="11" t="inlineStr"/>
+          <t>I'm sorry, what? → Aryang</t>
+        </is>
+      </c>
+      <c r="C111" s="13" t="n">
+        <v>0</v>
+      </c>
       <c r="D111" s="11" t="inlineStr"/>
-      <c r="E111" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E111" s="11" t="inlineStr"/>
       <c r="F111" s="11" t="inlineStr"/>
       <c r="G111" s="11" t="inlineStr"/>
       <c r="H111" s="12" t="inlineStr"/>
@@ -2649,19 +2666,17 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>05:25</t>
+          <t>89:44</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I said, Oh, why is it that this project is having this issue?</t>
+          <t>Definitely. You guys all know, didn't know that we have a summer semester? (open)</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr"/>
       <c r="D112" s="11" t="inlineStr"/>
-      <c r="E112" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E112" s="11" t="inlineStr"/>
       <c r="F112" s="11" t="inlineStr"/>
       <c r="G112" s="11" t="inlineStr"/>
       <c r="H112" s="12" t="inlineStr"/>
@@ -2669,12 +2684,12 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>05:27</t>
+          <t>89:50</t>
         </is>
       </c>
       <c r="B113" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Oh, why is it that we need to carry out this thing?</t>
+          <t>Did didn't inform them? → Chilaka</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr"/>
@@ -2689,18 +2704,18 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>05:29</t>
+          <t>89:58</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, for the 5 Ys, it gave me a depth into understanding what I'm doing.</t>
+          <t>Chilaka, you didn't tell them? → Chilaka</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr"/>
       <c r="D114" s="11" t="inlineStr"/>
-      <c r="E114" s="9" t="n">
-        <v>4</v>
+      <c r="E114" s="13" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="inlineStr"/>
       <c r="G114" s="11" t="inlineStr"/>
@@ -2709,19 +2724,19 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>05:32</t>
+          <t>90:08</t>
         </is>
       </c>
       <c r="B115" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So it's something that I would always like to put into practice.</t>
-        </is>
-      </c>
-      <c r="C115" s="11" t="inlineStr"/>
+          <t>But did you inform? → Aryang</t>
+        </is>
+      </c>
+      <c r="C115" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D115" s="11" t="inlineStr"/>
-      <c r="E115" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E115" s="11" t="inlineStr"/>
       <c r="F115" s="11" t="inlineStr"/>
       <c r="G115" s="11" t="inlineStr"/>
       <c r="H115" s="12" t="inlineStr"/>
@@ -2729,19 +2744,17 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>90:33</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because, um, I have so many ideas,</t>
+          <t>Yeah, two or three weeks like that. During the winter summer program, they will organize several activities, okay? (open)</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr"/>
       <c r="D116" s="11" t="inlineStr"/>
-      <c r="E116" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E116" s="11" t="inlineStr"/>
       <c r="F116" s="11" t="inlineStr"/>
       <c r="G116" s="11" t="inlineStr"/>
       <c r="H116" s="12" t="inlineStr"/>
@@ -2749,19 +2762,19 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>92:46</t>
         </is>
       </c>
       <c r="B117" s="10" t="inlineStr">
         <is>
-          <t>[Comment] but I just need to define them. Define the problem, define everything.</t>
-        </is>
-      </c>
-      <c r="C117" s="11" t="inlineStr"/>
+          <t>Now, I'm gonna give you uh five minutes, 10 minutes? How much do you want? Five minutes because we I wanna go through your comments. (open)</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D117" s="11" t="inlineStr"/>
-      <c r="E117" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E117" s="11" t="inlineStr"/>
       <c r="F117" s="11" t="inlineStr"/>
       <c r="G117" s="11" t="inlineStr"/>
       <c r="H117" s="12" t="inlineStr"/>
@@ -2769,19 +2782,17 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>05:39</t>
+          <t>92:55</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, that was really helpful for me.</t>
+          <t>Five minutes is enough? (open)</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr"/>
       <c r="D118" s="11" t="inlineStr"/>
-      <c r="E118" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="E118" s="11" t="inlineStr"/>
       <c r="F118" s="11" t="inlineStr"/>
       <c r="G118" s="11" t="inlineStr"/>
       <c r="H118" s="12" t="inlineStr"/>
@@ -2789,19 +2800,17 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>05:42</t>
+          <t>93:00</t>
         </is>
       </c>
       <c r="B119" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah.</t>
+          <t>What are what? (open)</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr"/>
       <c r="D119" s="11" t="inlineStr"/>
-      <c r="E119" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E119" s="11" t="inlineStr"/>
       <c r="F119" s="11" t="inlineStr"/>
       <c r="G119" s="11" t="inlineStr"/>
       <c r="H119" s="12" t="inlineStr"/>
@@ -2809,199 +2818,164 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>93:01</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I can go.</t>
-        </is>
-      </c>
-      <c r="C120" s="11" t="inlineStr"/>
+          <t>Okay, 10 minutes. So let's come back at 3:20, okay? (open)</t>
+        </is>
+      </c>
+      <c r="C120" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D120" s="11" t="inlineStr"/>
       <c r="E120" s="11" t="inlineStr"/>
-      <c r="F120" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F120" s="11" t="inlineStr"/>
       <c r="G120" s="11" t="inlineStr"/>
       <c r="H120" s="12" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>05:53</t>
-        </is>
-      </c>
-      <c r="B121" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] Okay.</t>
-        </is>
-      </c>
-      <c r="C121" s="11" t="inlineStr"/>
-      <c r="D121" s="11" t="inlineStr"/>
-      <c r="E121" s="11" t="inlineStr"/>
-      <c r="F121" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G121" s="11" t="inlineStr"/>
-      <c r="H121" s="12" t="inlineStr"/>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL (sum of scores)</t>
+        </is>
+      </c>
+      <c r="C121" s="15" t="n">
+        <v>101</v>
+      </c>
+      <c r="D121" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F121" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G121" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="H121" s="16" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>05:54</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] So, I'll go with the first stage.</t>
-        </is>
-      </c>
-      <c r="C122" s="11" t="inlineStr"/>
-      <c r="D122" s="11" t="inlineStr"/>
-      <c r="E122" s="11" t="inlineStr"/>
-      <c r="F122" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G122" s="11" t="inlineStr"/>
-      <c r="H122" s="12" t="inlineStr"/>
+      <c r="B122" s="17" t="inlineStr">
+        <is>
+          <t>Max possible (n_opp × 6)</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="n">
+        <v>234</v>
+      </c>
+      <c r="D122" s="18" t="n">
+        <v>96</v>
+      </c>
+      <c r="E122" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="F122" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="G122" s="18" t="n">
+        <v>60</v>
+      </c>
+      <c r="H122" s="12" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>05:55</t>
-        </is>
-      </c>
-      <c r="B123" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] Um, for me, the first stage, the 5 Ys</t>
-        </is>
-      </c>
-      <c r="C123" s="11" t="inlineStr"/>
-      <c r="D123" s="11" t="inlineStr"/>
-      <c r="E123" s="11" t="inlineStr"/>
-      <c r="F123" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G123" s="11" t="inlineStr"/>
-      <c r="H123" s="12" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="9" t="inlineStr">
-        <is>
-          <t>05:57</t>
-        </is>
-      </c>
-      <c r="B124" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] was actually an eye opener, and the SMART goals.</t>
-        </is>
-      </c>
-      <c r="C124" s="11" t="inlineStr"/>
-      <c r="D124" s="11" t="inlineStr"/>
-      <c r="E124" s="11" t="inlineStr"/>
-      <c r="F124" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G124" s="11" t="inlineStr"/>
-      <c r="H124" s="12" t="inlineStr"/>
+      <c r="B123" s="19" t="inlineStr">
+        <is>
+          <t>% Grade (max 7.5%)</t>
+        </is>
+      </c>
+      <c r="C123" s="20" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="D123" s="20" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E123" s="20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F123" s="20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G123" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H123" s="21" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="9" t="inlineStr">
-        <is>
-          <t>05:59</t>
-        </is>
-      </c>
-      <c r="B125" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] It made me realize that some of the goals I had before were not SMART goals.</t>
-        </is>
-      </c>
-      <c r="C125" s="11" t="inlineStr"/>
-      <c r="D125" s="11" t="inlineStr"/>
-      <c r="E125" s="11" t="inlineStr"/>
-      <c r="F125" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G125" s="11" t="inlineStr"/>
-      <c r="H125" s="12" t="inlineStr"/>
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>PARTICIPATION (7.5%) — Questions from Student / Voluntary</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="9" t="inlineStr">
-        <is>
-          <t>06:02</t>
-        </is>
-      </c>
-      <c r="B126" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] They were just goals.</t>
-        </is>
-      </c>
-      <c r="C126" s="11" t="inlineStr"/>
-      <c r="D126" s="11" t="inlineStr"/>
-      <c r="E126" s="11" t="inlineStr"/>
-      <c r="F126" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G126" s="11" t="inlineStr"/>
-      <c r="H126" s="12" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="9" t="inlineStr">
-        <is>
-          <t>06:03</t>
-        </is>
-      </c>
-      <c r="B127" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] And it also made me realize that some of my projects,</t>
-        </is>
-      </c>
-      <c r="C127" s="11" t="inlineStr"/>
-      <c r="D127" s="11" t="inlineStr"/>
-      <c r="E127" s="11" t="inlineStr"/>
-      <c r="F127" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G127" s="11" t="inlineStr"/>
-      <c r="H127" s="12" t="inlineStr"/>
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>Pregunta del alumno o comentario voluntario: 1–6 · Otros alumnos en esa fila: N/A</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="inlineStr">
-        <is>
-          <t>06:05</t>
-        </is>
-      </c>
-      <c r="B128" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] they don't really have a long-term goal for them.</t>
-        </is>
-      </c>
-      <c r="C128" s="11" t="inlineStr"/>
-      <c r="D128" s="11" t="inlineStr"/>
-      <c r="E128" s="11" t="inlineStr"/>
-      <c r="F128" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G128" s="11" t="inlineStr"/>
-      <c r="H128" s="12" t="inlineStr"/>
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Aryang</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>Chilaka</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>Sthepen</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>Notes / Feedback</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>02:41</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>[Comment] It was just, Okay, I'm working on this.</t>
+          <t>[Comment] presents and</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr"/>
       <c r="D129" s="11" t="inlineStr"/>
       <c r="E129" s="11" t="inlineStr"/>
       <c r="F129" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G129" s="11" t="inlineStr"/>
       <c r="H129" s="12" t="inlineStr"/>
@@ -3009,39 +2983,39 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>03:21</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I just want to like, achieve this, and then that's it.</t>
-        </is>
-      </c>
-      <c r="C130" s="11" t="inlineStr"/>
+          <t>[Question to Professor] Actually, they uh, they replied, they are available after 11, right?</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D130" s="11" t="inlineStr"/>
       <c r="E130" s="11" t="inlineStr"/>
-      <c r="F130" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="F130" s="11" t="inlineStr"/>
       <c r="G130" s="11" t="inlineStr"/>
       <c r="H130" s="12" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>03:25</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, the 5 Ys helped me to like, understand</t>
+          <t>[Comment] Yeah.</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr"/>
       <c r="D131" s="11" t="inlineStr"/>
       <c r="E131" s="11" t="inlineStr"/>
       <c r="F131" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G131" s="11" t="inlineStr"/>
       <c r="H131" s="12" t="inlineStr"/>
@@ -3049,19 +3023,19 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>03:26</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>[Comment] that I needed to go deeper into the why of the project.</t>
+          <t>[Comment] Next month Monday.</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr"/>
       <c r="D132" s="11" t="inlineStr"/>
       <c r="E132" s="11" t="inlineStr"/>
       <c r="F132" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G132" s="11" t="inlineStr"/>
       <c r="H132" s="12" t="inlineStr"/>
@@ -3069,807 +3043,807 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>06:17</t>
+          <t>03:34</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And also with the SMART goals, I needed to make sure that my goals</t>
-        </is>
-      </c>
-      <c r="C133" s="11" t="inlineStr"/>
+          <t>[Comment] I think yeah.</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D133" s="11" t="inlineStr"/>
       <c r="E133" s="11" t="inlineStr"/>
-      <c r="F133" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="F133" s="11" t="inlineStr"/>
       <c r="G133" s="11" t="inlineStr"/>
       <c r="H133" s="12" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>03:50</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>[Comment] are SMART goals.</t>
-        </is>
-      </c>
-      <c r="C134" s="11" t="inlineStr"/>
+          <t>[Comment] So 11:15 to 11 to 12 to 1:15.</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D134" s="11" t="inlineStr"/>
       <c r="E134" s="11" t="inlineStr"/>
-      <c r="F134" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F134" s="11" t="inlineStr"/>
       <c r="G134" s="11" t="inlineStr"/>
       <c r="H134" s="12" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>03:57</t>
         </is>
       </c>
       <c r="B135" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, that for me, was a really good takeaway from the first stage.</t>
-        </is>
-      </c>
-      <c r="C135" s="11" t="inlineStr"/>
+          <t>[Comment] Lunchtime.</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D135" s="11" t="inlineStr"/>
       <c r="E135" s="11" t="inlineStr"/>
-      <c r="F135" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="F135" s="11" t="inlineStr"/>
       <c r="G135" s="11" t="inlineStr"/>
       <c r="H135" s="12" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>03:58</t>
         </is>
       </c>
       <c r="B136" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I can go.</t>
+          <t>[Voluntary Response] No, no. No lunchtime.</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr"/>
       <c r="D136" s="11" t="inlineStr"/>
       <c r="E136" s="11" t="inlineStr"/>
-      <c r="F136" s="11" t="inlineStr"/>
-      <c r="G136" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F136" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G136" s="11" t="inlineStr"/>
       <c r="H136" s="12" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>06:46</t>
+          <t>03:59</t>
         </is>
       </c>
       <c r="B137" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah.</t>
-        </is>
-      </c>
-      <c r="C137" s="11" t="inlineStr"/>
+          <t>[Comment] Oh, really?</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D137" s="11" t="inlineStr"/>
       <c r="E137" s="11" t="inlineStr"/>
       <c r="F137" s="11" t="inlineStr"/>
-      <c r="G137" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G137" s="11" t="inlineStr"/>
       <c r="H137" s="12" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>06:47</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B138" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Okay.</t>
+          <t>[Comment] Whoa, whoa, whoa, whoa.</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr"/>
       <c r="D138" s="11" t="inlineStr"/>
       <c r="E138" s="11" t="inlineStr"/>
-      <c r="F138" s="11" t="inlineStr"/>
-      <c r="G138" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F138" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G138" s="11" t="inlineStr"/>
       <c r="H138" s="12" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>06:47</t>
+          <t>04:11</t>
         </is>
       </c>
       <c r="B139" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, for the homework review, uh, I think this first stage one has been an eye-opener.</t>
-        </is>
-      </c>
-      <c r="C139" s="11" t="inlineStr"/>
+          <t>[Comment] Same, yeah.</t>
+        </is>
+      </c>
+      <c r="C139" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D139" s="11" t="inlineStr"/>
       <c r="E139" s="11" t="inlineStr"/>
       <c r="F139" s="11" t="inlineStr"/>
-      <c r="G139" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="G139" s="11" t="inlineStr"/>
       <c r="H139" s="12" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="B140" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh, especially the 5 Ys and the SMART goals.</t>
+          <t>[Voluntary Response] Uh, I can go.</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr"/>
       <c r="D140" s="11" t="inlineStr"/>
-      <c r="E140" s="11" t="inlineStr"/>
+      <c r="E140" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F140" s="11" t="inlineStr"/>
-      <c r="G140" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G140" s="11" t="inlineStr"/>
       <c r="H140" s="12" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="B141" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And what I really liked about it is how we had to connect them.</t>
+          <t>[Comment] I, I want to talk about the stage one. I, I, I, I really understood it.</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr"/>
       <c r="D141" s="11" t="inlineStr"/>
-      <c r="E141" s="11" t="inlineStr"/>
+      <c r="E141" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="F141" s="11" t="inlineStr"/>
-      <c r="G141" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="G141" s="11" t="inlineStr"/>
       <c r="H141" s="12" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>05:14</t>
         </is>
       </c>
       <c r="B142" s="10" t="inlineStr">
         <is>
-          <t>[Comment] The problem statement,</t>
+          <t>[Comment] Um, for me, this is like my first time coming across.</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr"/>
       <c r="D142" s="11" t="inlineStr"/>
-      <c r="E142" s="11" t="inlineStr"/>
+      <c r="E142" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="F142" s="11" t="inlineStr"/>
-      <c r="G142" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G142" s="11" t="inlineStr"/>
       <c r="H142" s="12" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>[Comment] and then use the 5 Ys to dig deeper to find the root causes.</t>
+          <t>[Comment] Because I've heard about project management, but in this form,</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr"/>
       <c r="D143" s="11" t="inlineStr"/>
-      <c r="E143" s="11" t="inlineStr"/>
+      <c r="E143" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="F143" s="11" t="inlineStr"/>
-      <c r="G143" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G143" s="11" t="inlineStr"/>
       <c r="H143" s="12" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>06:58</t>
+          <t>05:18</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And from the root causes, then you come up with the objectives,</t>
+          <t>[Comment] I've not really done anything with it, especially with the 5 Ys.</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr"/>
       <c r="D144" s="11" t="inlineStr"/>
-      <c r="E144" s="11" t="inlineStr"/>
+      <c r="E144" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="F144" s="11" t="inlineStr"/>
-      <c r="G144" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G144" s="11" t="inlineStr"/>
       <c r="H144" s="12" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>[Comment] and then using the SMART goals for the objectives.</t>
+          <t>[Comment] So it actually, it made me understand a lot about</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr"/>
       <c r="D145" s="11" t="inlineStr"/>
-      <c r="E145" s="11" t="inlineStr"/>
+      <c r="E145" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="F145" s="11" t="inlineStr"/>
-      <c r="G145" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G145" s="11" t="inlineStr"/>
       <c r="H145" s="12" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, it was really a flow.</t>
+          <t>[Comment] the project I was working on, you know, prior to coming for this class.</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr"/>
       <c r="D146" s="11" t="inlineStr"/>
-      <c r="E146" s="11" t="inlineStr"/>
+      <c r="E146" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="F146" s="11" t="inlineStr"/>
-      <c r="G146" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G146" s="11" t="inlineStr"/>
       <c r="H146" s="12" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>07:03</t>
+          <t>05:24</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And it, it helped me understand that a project is not just</t>
+          <t>[Comment] Because I've always struggled.</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr"/>
       <c r="D147" s="11" t="inlineStr"/>
-      <c r="E147" s="11" t="inlineStr"/>
+      <c r="E147" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="F147" s="11" t="inlineStr"/>
-      <c r="G147" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G147" s="11" t="inlineStr"/>
       <c r="H147" s="12" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>05:25</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>[Comment] something you just get up and say, Oh, I want to do this, then you go do it.</t>
+          <t>[Comment] I said, Oh, why is it that this project is having this issue?</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr"/>
       <c r="D148" s="11" t="inlineStr"/>
-      <c r="E148" s="11" t="inlineStr"/>
+      <c r="E148" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="F148" s="11" t="inlineStr"/>
-      <c r="G148" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G148" s="11" t="inlineStr"/>
       <c r="H148" s="12" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh, there's always a proper process.</t>
+          <t>[Comment] Oh, why is it that we need to carry out this thing?</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr"/>
       <c r="D149" s="11" t="inlineStr"/>
-      <c r="E149" s="11" t="inlineStr"/>
+      <c r="E149" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="F149" s="11" t="inlineStr"/>
-      <c r="G149" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G149" s="11" t="inlineStr"/>
       <c r="H149" s="12" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>07:09</t>
+          <t>05:29</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And that's why they say planning is very important.</t>
+          <t>[Comment] So, for the 5 Ys, it gave me a depth into understanding what I'm doing.</t>
         </is>
       </c>
       <c r="C150" s="11" t="inlineStr"/>
       <c r="D150" s="11" t="inlineStr"/>
-      <c r="E150" s="11" t="inlineStr"/>
+      <c r="E150" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="F150" s="11" t="inlineStr"/>
-      <c r="G150" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="G150" s="11" t="inlineStr"/>
       <c r="H150" s="12" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>05:32</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because you would have to define your problem correctly,</t>
+          <t>[Comment] So it's something that I would always like to put into practice.</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr"/>
       <c r="D151" s="11" t="inlineStr"/>
-      <c r="E151" s="11" t="inlineStr"/>
+      <c r="E151" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="F151" s="11" t="inlineStr"/>
-      <c r="G151" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G151" s="11" t="inlineStr"/>
       <c r="H151" s="12" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>[Comment] define your root causes correctly.</t>
+          <t>[Comment] Because, um, I have so many ideas,</t>
         </is>
       </c>
       <c r="C152" s="11" t="inlineStr"/>
       <c r="D152" s="11" t="inlineStr"/>
-      <c r="E152" s="11" t="inlineStr"/>
+      <c r="E152" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="F152" s="11" t="inlineStr"/>
-      <c r="G152" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G152" s="11" t="inlineStr"/>
       <c r="H152" s="12" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>05:36</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>[Comment] From there, you would have your objectives.</t>
+          <t>[Comment] but I just need to define them. Define the problem, define everything.</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr"/>
       <c r="D153" s="11" t="inlineStr"/>
-      <c r="E153" s="11" t="inlineStr"/>
+      <c r="E153" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="F153" s="11" t="inlineStr"/>
-      <c r="G153" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G153" s="11" t="inlineStr"/>
       <c r="H153" s="12" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>07:17</t>
+          <t>05:39</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And with the objectives,</t>
+          <t>[Comment] So, that was really helpful for me.</t>
         </is>
       </c>
       <c r="C154" s="11" t="inlineStr"/>
       <c r="D154" s="11" t="inlineStr"/>
-      <c r="E154" s="11" t="inlineStr"/>
+      <c r="E154" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="F154" s="11" t="inlineStr"/>
-      <c r="G154" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G154" s="11" t="inlineStr"/>
       <c r="H154" s="12" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>05:42</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>[Comment] you can now use your SMART goals for each objective.</t>
+          <t>[Voluntary Response] Yeah.</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr"/>
       <c r="D155" s="11" t="inlineStr"/>
-      <c r="E155" s="11" t="inlineStr"/>
+      <c r="E155" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F155" s="11" t="inlineStr"/>
-      <c r="G155" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G155" s="11" t="inlineStr"/>
       <c r="H155" s="12" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, this part of the stage one, it's very important.</t>
+          <t>[Voluntary Response] I can go.</t>
         </is>
       </c>
       <c r="C156" s="11" t="inlineStr"/>
       <c r="D156" s="11" t="inlineStr"/>
       <c r="E156" s="11" t="inlineStr"/>
-      <c r="F156" s="11" t="inlineStr"/>
-      <c r="G156" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="F156" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G156" s="11" t="inlineStr"/>
       <c r="H156" s="12" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And it's something I definitely will apply to my projects.</t>
+          <t>[Comment] Okay.</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr"/>
       <c r="D157" s="11" t="inlineStr"/>
       <c r="E157" s="11" t="inlineStr"/>
-      <c r="F157" s="11" t="inlineStr"/>
-      <c r="G157" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="F157" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" s="11" t="inlineStr"/>
       <c r="H157" s="12" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>05:54</t>
         </is>
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I can go.</t>
-        </is>
-      </c>
-      <c r="C158" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Comment] So, I'll go with the first stage.</t>
+        </is>
+      </c>
+      <c r="C158" s="11" t="inlineStr"/>
       <c r="D158" s="11" t="inlineStr"/>
       <c r="E158" s="11" t="inlineStr"/>
-      <c r="F158" s="11" t="inlineStr"/>
+      <c r="F158" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="G158" s="11" t="inlineStr"/>
       <c r="H158" s="12" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh.</t>
-        </is>
-      </c>
-      <c r="C159" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Comment] Um, for me, the first stage, the 5 Ys</t>
+        </is>
+      </c>
+      <c r="C159" s="11" t="inlineStr"/>
       <c r="D159" s="11" t="inlineStr"/>
       <c r="E159" s="11" t="inlineStr"/>
-      <c r="F159" s="11" t="inlineStr"/>
+      <c r="F159" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="G159" s="11" t="inlineStr"/>
       <c r="H159" s="12" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>05:57</t>
         </is>
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Actually, I also have similar opinions.</t>
-        </is>
-      </c>
-      <c r="C160" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] was actually an eye opener, and the SMART goals.</t>
+        </is>
+      </c>
+      <c r="C160" s="11" t="inlineStr"/>
       <c r="D160" s="11" t="inlineStr"/>
       <c r="E160" s="11" t="inlineStr"/>
-      <c r="F160" s="11" t="inlineStr"/>
+      <c r="F160" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="G160" s="11" t="inlineStr"/>
       <c r="H160" s="12" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Um, I think stage one also is really interesting to me.</t>
-        </is>
-      </c>
-      <c r="C161" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] It made me realize that some of the goals I had before were not SMART goals.</t>
+        </is>
+      </c>
+      <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr"/>
       <c r="E161" s="11" t="inlineStr"/>
-      <c r="F161" s="11" t="inlineStr"/>
+      <c r="F161" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="G161" s="11" t="inlineStr"/>
       <c r="H161" s="12" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And I can actually, uh, apply these things.</t>
-        </is>
-      </c>
-      <c r="C162" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] They were just goals.</t>
+        </is>
+      </c>
+      <c r="C162" s="11" t="inlineStr"/>
       <c r="D162" s="11" t="inlineStr"/>
       <c r="E162" s="11" t="inlineStr"/>
-      <c r="F162" s="11" t="inlineStr"/>
+      <c r="F162" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="G162" s="11" t="inlineStr"/>
       <c r="H162" s="12" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Like, in the future, if I want to have my own project.</t>
-        </is>
-      </c>
-      <c r="C163" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] And it also made me realize that some of my projects,</t>
+        </is>
+      </c>
+      <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr"/>
       <c r="E163" s="11" t="inlineStr"/>
-      <c r="F163" s="11" t="inlineStr"/>
+      <c r="F163" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="G163" s="11" t="inlineStr"/>
       <c r="H163" s="12" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Or also in my working experience, like in the next job.</t>
-        </is>
-      </c>
-      <c r="C164" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] they don't really have a long-term goal for them.</t>
+        </is>
+      </c>
+      <c r="C164" s="11" t="inlineStr"/>
       <c r="D164" s="11" t="inlineStr"/>
       <c r="E164" s="11" t="inlineStr"/>
-      <c r="F164" s="11" t="inlineStr"/>
+      <c r="F164" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="G164" s="11" t="inlineStr"/>
       <c r="H164" s="12" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I can use these things to improve my projects.</t>
-        </is>
-      </c>
-      <c r="C165" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] It was just, Okay, I'm working on this.</t>
+        </is>
+      </c>
+      <c r="C165" s="11" t="inlineStr"/>
       <c r="D165" s="11" t="inlineStr"/>
       <c r="E165" s="11" t="inlineStr"/>
-      <c r="F165" s="11" t="inlineStr"/>
+      <c r="F165" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="G165" s="11" t="inlineStr"/>
       <c r="H165" s="12" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Um, for example, the project that I want to apply to my country,</t>
-        </is>
-      </c>
-      <c r="C166" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] I just want to like, achieve this, and then that's it.</t>
+        </is>
+      </c>
+      <c r="C166" s="11" t="inlineStr"/>
       <c r="D166" s="11" t="inlineStr"/>
       <c r="E166" s="11" t="inlineStr"/>
-      <c r="F166" s="11" t="inlineStr"/>
+      <c r="F166" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="G166" s="11" t="inlineStr"/>
       <c r="H166" s="12" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I actually, before I only have a little bit of idea.</t>
-        </is>
-      </c>
-      <c r="C167" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] So, the 5 Ys helped me to like, understand</t>
+        </is>
+      </c>
+      <c r="C167" s="11" t="inlineStr"/>
       <c r="D167" s="11" t="inlineStr"/>
       <c r="E167" s="11" t="inlineStr"/>
-      <c r="F167" s="11" t="inlineStr"/>
+      <c r="F167" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="G167" s="11" t="inlineStr"/>
       <c r="H167" s="12" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But with the 5 Ys and the SMART goals,</t>
-        </is>
-      </c>
-      <c r="C168" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] that I needed to go deeper into the why of the project.</t>
+        </is>
+      </c>
+      <c r="C168" s="11" t="inlineStr"/>
       <c r="D168" s="11" t="inlineStr"/>
       <c r="E168" s="11" t="inlineStr"/>
-      <c r="F168" s="11" t="inlineStr"/>
+      <c r="F168" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="G168" s="11" t="inlineStr"/>
       <c r="H168" s="12" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>06:17</t>
         </is>
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I can actually, like, build it systematically.</t>
-        </is>
-      </c>
-      <c r="C169" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] And also with the SMART goals, I needed to make sure that my goals</t>
+        </is>
+      </c>
+      <c r="C169" s="11" t="inlineStr"/>
       <c r="D169" s="11" t="inlineStr"/>
       <c r="E169" s="11" t="inlineStr"/>
-      <c r="F169" s="11" t="inlineStr"/>
+      <c r="F169" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="G169" s="11" t="inlineStr"/>
       <c r="H169" s="12" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Um, so it's not just a big idea,</t>
-        </is>
-      </c>
-      <c r="C170" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] are SMART goals.</t>
+        </is>
+      </c>
+      <c r="C170" s="11" t="inlineStr"/>
       <c r="D170" s="11" t="inlineStr"/>
       <c r="E170" s="11" t="inlineStr"/>
-      <c r="F170" s="11" t="inlineStr"/>
+      <c r="F170" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="G170" s="11" t="inlineStr"/>
       <c r="H170" s="12" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>[Comment] but something that I can actually apply to my country.</t>
-        </is>
-      </c>
-      <c r="C171" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] So, that for me, was a really good takeaway from the first stage.</t>
+        </is>
+      </c>
+      <c r="C171" s="11" t="inlineStr"/>
       <c r="D171" s="11" t="inlineStr"/>
       <c r="E171" s="11" t="inlineStr"/>
-      <c r="F171" s="11" t="inlineStr"/>
+      <c r="F171" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="G171" s="11" t="inlineStr"/>
       <c r="H171" s="12" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I'll go next.</t>
+          <t>[Voluntary Response] I can go.</t>
         </is>
       </c>
       <c r="C172" s="11" t="inlineStr"/>
-      <c r="D172" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="D172" s="11" t="inlineStr"/>
       <c r="E172" s="11" t="inlineStr"/>
       <c r="F172" s="11" t="inlineStr"/>
-      <c r="G172" s="11" t="inlineStr"/>
+      <c r="G172" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H172" s="12" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>06:46</t>
         </is>
       </c>
       <c r="B173" s="10" t="inlineStr">
@@ -3878,323 +3852,323 @@
         </is>
       </c>
       <c r="C173" s="11" t="inlineStr"/>
-      <c r="D173" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="D173" s="11" t="inlineStr"/>
       <c r="E173" s="11" t="inlineStr"/>
       <c r="F173" s="11" t="inlineStr"/>
-      <c r="G173" s="11" t="inlineStr"/>
+      <c r="G173" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H173" s="12" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>06:47</t>
         </is>
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh, for me, I think the important things are to understand the problem.</t>
+          <t>[Comment] Okay.</t>
         </is>
       </c>
       <c r="C174" s="11" t="inlineStr"/>
-      <c r="D174" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="D174" s="11" t="inlineStr"/>
       <c r="E174" s="11" t="inlineStr"/>
       <c r="F174" s="11" t="inlineStr"/>
-      <c r="G174" s="11" t="inlineStr"/>
+      <c r="G174" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H174" s="12" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>06:47</t>
         </is>
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And the reason why we need to understand the problem,</t>
+          <t>[Comment] So, for the homework review, uh, I think this first stage one has been an eye-opener.</t>
         </is>
       </c>
       <c r="C175" s="11" t="inlineStr"/>
-      <c r="D175" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="D175" s="11" t="inlineStr"/>
       <c r="E175" s="11" t="inlineStr"/>
       <c r="F175" s="11" t="inlineStr"/>
-      <c r="G175" s="11" t="inlineStr"/>
+      <c r="G175" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="H175" s="12" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>[Comment] and what we want to solve.</t>
+          <t>[Comment] Uh, especially the 5 Ys and the SMART goals.</t>
         </is>
       </c>
       <c r="C176" s="11" t="inlineStr"/>
-      <c r="D176" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="D176" s="11" t="inlineStr"/>
       <c r="E176" s="11" t="inlineStr"/>
       <c r="F176" s="11" t="inlineStr"/>
-      <c r="G176" s="11" t="inlineStr"/>
+      <c r="G176" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H176" s="12" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh, so, the 5 Ys</t>
+          <t>[Comment] And what I really liked about it is how we had to connect them.</t>
         </is>
       </c>
       <c r="C177" s="11" t="inlineStr"/>
-      <c r="D177" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="D177" s="11" t="inlineStr"/>
       <c r="E177" s="11" t="inlineStr"/>
       <c r="F177" s="11" t="inlineStr"/>
-      <c r="G177" s="11" t="inlineStr"/>
+      <c r="G177" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="H177" s="12" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>[Comment] and the problem statement,</t>
+          <t>[Comment] The problem statement,</t>
         </is>
       </c>
       <c r="C178" s="11" t="inlineStr"/>
-      <c r="D178" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="D178" s="11" t="inlineStr"/>
       <c r="E178" s="11" t="inlineStr"/>
       <c r="F178" s="11" t="inlineStr"/>
-      <c r="G178" s="11" t="inlineStr"/>
+      <c r="G178" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H178" s="12" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>[Comment] uh, it's very important to ensure that the project is realistic,</t>
+          <t>[Comment] and then use the 5 Ys to dig deeper to find the root causes.</t>
         </is>
       </c>
       <c r="C179" s="11" t="inlineStr"/>
-      <c r="D179" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="D179" s="11" t="inlineStr"/>
       <c r="E179" s="11" t="inlineStr"/>
       <c r="F179" s="11" t="inlineStr"/>
-      <c r="G179" s="11" t="inlineStr"/>
+      <c r="G179" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H179" s="12" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>06:58</t>
         </is>
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>[Comment] and also to, to make sure that the project is measurable.</t>
+          <t>[Comment] And from the root causes, then you come up with the objectives,</t>
         </is>
       </c>
       <c r="C180" s="11" t="inlineStr"/>
-      <c r="D180" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="D180" s="11" t="inlineStr"/>
       <c r="E180" s="11" t="inlineStr"/>
       <c r="F180" s="11" t="inlineStr"/>
-      <c r="G180" s="11" t="inlineStr"/>
+      <c r="G180" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H180" s="12" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because if it's not measurable, we can't really assess if we achieve our goals.</t>
+          <t>[Comment] and then using the SMART goals for the objectives.</t>
         </is>
       </c>
       <c r="C181" s="11" t="inlineStr"/>
-      <c r="D181" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="D181" s="11" t="inlineStr"/>
       <c r="E181" s="11" t="inlineStr"/>
       <c r="F181" s="11" t="inlineStr"/>
-      <c r="G181" s="11" t="inlineStr"/>
+      <c r="G181" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H181" s="12" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And also the main problem that we want to address.</t>
+          <t>[Comment] So, it was really a flow.</t>
         </is>
       </c>
       <c r="C182" s="11" t="inlineStr"/>
-      <c r="D182" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="D182" s="11" t="inlineStr"/>
       <c r="E182" s="11" t="inlineStr"/>
       <c r="F182" s="11" t="inlineStr"/>
-      <c r="G182" s="11" t="inlineStr"/>
+      <c r="G182" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H182" s="12" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:03</t>
         </is>
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, for me, the 5 Ys is actually very practical and helpful.</t>
+          <t>[Comment] And it, it helped me understand that a project is not just</t>
         </is>
       </c>
       <c r="C183" s="11" t="inlineStr"/>
-      <c r="D183" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="D183" s="11" t="inlineStr"/>
       <c r="E183" s="11" t="inlineStr"/>
       <c r="F183" s="11" t="inlineStr"/>
-      <c r="G183" s="11" t="inlineStr"/>
+      <c r="G183" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H183" s="12" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So I think I can use this in the future as well.</t>
+          <t>[Comment] something you just get up and say, Oh, I want to do this, then you go do it.</t>
         </is>
       </c>
       <c r="C184" s="11" t="inlineStr"/>
-      <c r="D184" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="D184" s="11" t="inlineStr"/>
       <c r="E184" s="11" t="inlineStr"/>
       <c r="F184" s="11" t="inlineStr"/>
-      <c r="G184" s="11" t="inlineStr"/>
+      <c r="G184" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H184" s="12" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Very useful.</t>
+          <t>[Comment] Uh, there's always a proper process.</t>
         </is>
       </c>
       <c r="C185" s="11" t="inlineStr"/>
       <c r="D185" s="11" t="inlineStr"/>
-      <c r="E185" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E185" s="11" t="inlineStr"/>
       <c r="F185" s="11" t="inlineStr"/>
-      <c r="G185" s="11" t="inlineStr"/>
+      <c r="G185" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H185" s="12" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>07:09</t>
         </is>
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Very useful.</t>
+          <t>[Comment] And that's why they say planning is very important.</t>
         </is>
       </c>
       <c r="C186" s="11" t="inlineStr"/>
       <c r="D186" s="11" t="inlineStr"/>
       <c r="E186" s="11" t="inlineStr"/>
-      <c r="F186" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G186" s="11" t="inlineStr"/>
+      <c r="F186" s="11" t="inlineStr"/>
+      <c r="G186" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="H186" s="12" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Thank you.</t>
+          <t>[Comment] Because you would have to define your problem correctly,</t>
         </is>
       </c>
       <c r="C187" s="11" t="inlineStr"/>
       <c r="D187" s="11" t="inlineStr"/>
-      <c r="E187" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E187" s="11" t="inlineStr"/>
       <c r="F187" s="11" t="inlineStr"/>
-      <c r="G187" s="11" t="inlineStr"/>
+      <c r="G187" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H187" s="12" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Thank you.</t>
-        </is>
-      </c>
-      <c r="C188" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Comment] define your root causes correctly.</t>
+        </is>
+      </c>
+      <c r="C188" s="11" t="inlineStr"/>
       <c r="D188" s="11" t="inlineStr"/>
       <c r="E188" s="11" t="inlineStr"/>
       <c r="F188" s="11" t="inlineStr"/>
-      <c r="G188" s="11" t="inlineStr"/>
+      <c r="G188" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H188" s="12" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Thank you, Professor.</t>
+          <t>[Comment] From there, you would have your objectives.</t>
         </is>
       </c>
       <c r="C189" s="11" t="inlineStr"/>
@@ -4202,59 +4176,59 @@
       <c r="E189" s="11" t="inlineStr"/>
       <c r="F189" s="11" t="inlineStr"/>
       <c r="G189" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H189" s="12" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Thank you, Professor.</t>
+          <t>[Comment] And with the objectives,</t>
         </is>
       </c>
       <c r="C190" s="11" t="inlineStr"/>
       <c r="D190" s="11" t="inlineStr"/>
       <c r="E190" s="11" t="inlineStr"/>
-      <c r="F190" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G190" s="11" t="inlineStr"/>
+      <c r="F190" s="11" t="inlineStr"/>
+      <c r="G190" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H190" s="12" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Thank you, ma'am.</t>
+          <t>[Comment] you can now use your SMART goals for each objective.</t>
         </is>
       </c>
       <c r="C191" s="11" t="inlineStr"/>
-      <c r="D191" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="D191" s="11" t="inlineStr"/>
       <c r="E191" s="11" t="inlineStr"/>
       <c r="F191" s="11" t="inlineStr"/>
-      <c r="G191" s="11" t="inlineStr"/>
+      <c r="G191" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H191" s="12" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah, yeah.</t>
+          <t>[Comment] So, this part of the stage one, it's very important.</t>
         </is>
       </c>
       <c r="C192" s="11" t="inlineStr"/>
@@ -4262,19 +4236,19 @@
       <c r="E192" s="11" t="inlineStr"/>
       <c r="F192" s="11" t="inlineStr"/>
       <c r="G192" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H192" s="12" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>[Comment] They're doing so much in Nigeria right now.</t>
+          <t>[Comment] And it's something I definitely will apply to my projects.</t>
         </is>
       </c>
       <c r="C193" s="11" t="inlineStr"/>
@@ -4282,63 +4256,63 @@
       <c r="E193" s="11" t="inlineStr"/>
       <c r="F193" s="11" t="inlineStr"/>
       <c r="G193" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H193" s="12" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>[Comment] That's from Korea.</t>
-        </is>
-      </c>
-      <c r="C194" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] I can go.</t>
+        </is>
+      </c>
+      <c r="C194" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D194" s="11" t="inlineStr"/>
       <c r="E194" s="11" t="inlineStr"/>
       <c r="F194" s="11" t="inlineStr"/>
-      <c r="G194" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G194" s="11" t="inlineStr"/>
       <c r="H194" s="12" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] The company has to be like 10 years in the [inaudible].</t>
-        </is>
-      </c>
-      <c r="C195" s="11" t="inlineStr"/>
+          <t>[Comment] Uh.</t>
+        </is>
+      </c>
+      <c r="C195" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D195" s="11" t="inlineStr"/>
       <c r="E195" s="11" t="inlineStr"/>
       <c r="F195" s="11" t="inlineStr"/>
-      <c r="G195" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="G195" s="11" t="inlineStr"/>
       <c r="H195" s="12" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Ah, okay. So, so we cannot [inaudible].</t>
+          <t>[Comment] Actually, I also have similar opinions.</t>
         </is>
       </c>
       <c r="C196" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D196" s="11" t="inlineStr"/>
       <c r="E196" s="11" t="inlineStr"/>
@@ -4349,16 +4323,16 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I see.</t>
+          <t>[Comment] Um, I think stage one also is really interesting to me.</t>
         </is>
       </c>
       <c r="C197" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D197" s="11" t="inlineStr"/>
       <c r="E197" s="11" t="inlineStr"/>
@@ -4369,12 +4343,12 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>[Comment] His son. Is that Hong?</t>
+          <t>[Comment] And I can actually, uh, apply these things.</t>
         </is>
       </c>
       <c r="C198" s="9" t="n">
@@ -4389,16 +4363,16 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But from what he's saying, he said he's not them that sends the invitation that I they don't have any business with sending the invitation. No Nypa. The Ministry of Foreign Affairs and the Ministry of Science and Technology.</t>
+          <t>[Comment] Like, in the future, if I want to have my own project.</t>
         </is>
       </c>
       <c r="C199" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D199" s="11" t="inlineStr"/>
       <c r="E199" s="11" t="inlineStr"/>
@@ -4409,12 +4383,12 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>[Comment] They said it's not even Science and Technology or Nypa.</t>
+          <t>[Comment] Or also in my working experience, like in the next job.</t>
         </is>
       </c>
       <c r="C200" s="9" t="n">
@@ -4429,16 +4403,16 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because I'm I'm supposed to meet him and Professor next month on the 22nd.</t>
+          <t>[Comment] I can use these things to improve my projects.</t>
         </is>
       </c>
       <c r="C201" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D201" s="11" t="inlineStr"/>
       <c r="E201" s="11" t="inlineStr"/>
@@ -4449,16 +4423,16 @@
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So he said it's part of the I think is initiated from our home countries. That is normally sent to Ministry of Finance, not even Science and Technology.</t>
+          <t>[Comment] Um, for example, the project that I want to apply to my country,</t>
         </is>
       </c>
       <c r="C202" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D202" s="11" t="inlineStr"/>
       <c r="E202" s="11" t="inlineStr"/>
@@ -4469,16 +4443,16 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>[Comment] They they might not even know when they send.</t>
+          <t>[Comment] I actually, before I only have a little bit of idea.</t>
         </is>
       </c>
       <c r="C203" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D203" s="11" t="inlineStr"/>
       <c r="E203" s="11" t="inlineStr"/>
@@ -4489,16 +4463,16 @@
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>[Comment] African Development Bank. And it's in partnership with Ministry of Finance of Korea. That they they normally send it to Ministry of Finance of the of the other countries.</t>
+          <t>[Comment] But with the 5 Ys and the SMART goals,</t>
         </is>
       </c>
       <c r="C204" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D204" s="11" t="inlineStr"/>
       <c r="E204" s="11" t="inlineStr"/>
@@ -4509,16 +4483,16 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Gido. right?</t>
+          <t>[Comment] I can actually, like, build it systematically.</t>
         </is>
       </c>
       <c r="C205" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D205" s="11" t="inlineStr"/>
       <c r="E205" s="11" t="inlineStr"/>
@@ -4529,12 +4503,12 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>[Comment] around September or so.</t>
+          <t>[Comment] Um, so it's not just a big idea,</t>
         </is>
       </c>
       <c r="C206" s="9" t="n">
@@ -4549,12 +4523,12 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I think it's July.</t>
+          <t>[Comment] but something that I can actually apply to my country.</t>
         </is>
       </c>
       <c r="C207" s="9" t="n">
@@ -4569,18 +4543,18 @@
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] I think it's July.</t>
-        </is>
-      </c>
-      <c r="C208" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D208" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] I'll go next.</t>
+        </is>
+      </c>
+      <c r="C208" s="11" t="inlineStr"/>
+      <c r="D208" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="E208" s="11" t="inlineStr"/>
       <c r="F208" s="11" t="inlineStr"/>
       <c r="G208" s="11" t="inlineStr"/>
@@ -4589,18 +4563,18 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="B209" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I I Yeah.</t>
-        </is>
-      </c>
-      <c r="C209" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D209" s="11" t="inlineStr"/>
+          <t>[Comment] Yeah.</t>
+        </is>
+      </c>
+      <c r="C209" s="11" t="inlineStr"/>
+      <c r="D209" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="E209" s="11" t="inlineStr"/>
       <c r="F209" s="11" t="inlineStr"/>
       <c r="G209" s="11" t="inlineStr"/>
@@ -4609,18 +4583,18 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah, yeah, yeah. I heard that it's gonna be in July. The visit the African Minister's visit.</t>
-        </is>
-      </c>
-      <c r="C210" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D210" s="11" t="inlineStr"/>
+          <t>[Comment] Uh, for me, I think the important things are to understand the problem.</t>
+        </is>
+      </c>
+      <c r="C210" s="11" t="inlineStr"/>
+      <c r="D210" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E210" s="11" t="inlineStr"/>
       <c r="F210" s="11" t="inlineStr"/>
       <c r="G210" s="11" t="inlineStr"/>
@@ -4629,18 +4603,18 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah, for them, the only thing I mean it's an it's just an invitation because they know how to fast track their own visa. You just need.</t>
-        </is>
-      </c>
-      <c r="C211" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D211" s="11" t="inlineStr"/>
+          <t>[Comment] And the reason why we need to understand the problem,</t>
+        </is>
+      </c>
+      <c r="C211" s="11" t="inlineStr"/>
+      <c r="D211" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E211" s="11" t="inlineStr"/>
       <c r="F211" s="11" t="inlineStr"/>
       <c r="G211" s="11" t="inlineStr"/>
@@ -4649,18 +4623,18 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So that that's why that's where I had the challenge. I told him, and he said them and Minister of Science and ICT don't have any anything to do with with that invitation. That the Minister of Finance normally sends it to the Minister of Finance of African countries.</t>
-        </is>
-      </c>
-      <c r="C212" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D212" s="11" t="inlineStr"/>
+          <t>[Comment] and what we want to solve.</t>
+        </is>
+      </c>
+      <c r="C212" s="11" t="inlineStr"/>
+      <c r="D212" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E212" s="11" t="inlineStr"/>
       <c r="F212" s="11" t="inlineStr"/>
       <c r="G212" s="11" t="inlineStr"/>
@@ -4669,18 +4643,18 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah.</t>
-        </is>
-      </c>
-      <c r="C213" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D213" s="11" t="inlineStr"/>
+          <t>[Comment] Uh, so, the 5 Ys</t>
+        </is>
+      </c>
+      <c r="C213" s="11" t="inlineStr"/>
+      <c r="D213" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E213" s="11" t="inlineStr"/>
       <c r="F213" s="11" t="inlineStr"/>
       <c r="G213" s="11" t="inlineStr"/>
@@ -4689,18 +4663,18 @@
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So that we have to find out on our own.</t>
-        </is>
-      </c>
-      <c r="C214" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D214" s="11" t="inlineStr"/>
+          <t>[Comment] and the problem statement,</t>
+        </is>
+      </c>
+      <c r="C214" s="11" t="inlineStr"/>
+      <c r="D214" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E214" s="11" t="inlineStr"/>
       <c r="F214" s="11" t="inlineStr"/>
       <c r="G214" s="11" t="inlineStr"/>
@@ -4709,18 +4683,18 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="B215" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah, I and it's on AI and digital transformation. So I'm wondering why they're only inviting only Ministers of of Finance instead of the relevant ministers.</t>
-        </is>
-      </c>
-      <c r="C215" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D215" s="11" t="inlineStr"/>
+          <t>[Comment] uh, it's very important to ensure that the project is realistic,</t>
+        </is>
+      </c>
+      <c r="C215" s="11" t="inlineStr"/>
+      <c r="D215" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="E215" s="11" t="inlineStr"/>
       <c r="F215" s="11" t="inlineStr"/>
       <c r="G215" s="11" t="inlineStr"/>
@@ -4729,18 +4703,18 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah.</t>
-        </is>
-      </c>
-      <c r="C216" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D216" s="11" t="inlineStr"/>
+          <t>[Comment] and also to, to make sure that the project is measurable.</t>
+        </is>
+      </c>
+      <c r="C216" s="11" t="inlineStr"/>
+      <c r="D216" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="E216" s="11" t="inlineStr"/>
       <c r="F216" s="11" t="inlineStr"/>
       <c r="G216" s="11" t="inlineStr"/>
@@ -4749,18 +4723,18 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="B217" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah.</t>
-        </is>
-      </c>
-      <c r="C217" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D217" s="11" t="inlineStr"/>
+          <t>[Comment] Because if it's not measurable, we can't really assess if we achieve our goals.</t>
+        </is>
+      </c>
+      <c r="C217" s="11" t="inlineStr"/>
+      <c r="D217" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E217" s="11" t="inlineStr"/>
       <c r="F217" s="11" t="inlineStr"/>
       <c r="G217" s="11" t="inlineStr"/>
@@ -4769,18 +4743,18 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But I think he told</t>
-        </is>
-      </c>
-      <c r="C218" s="9" t="n">
+          <t>[Comment] And also the main problem that we want to address.</t>
+        </is>
+      </c>
+      <c r="C218" s="11" t="inlineStr"/>
+      <c r="D218" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="D218" s="11" t="inlineStr"/>
       <c r="E218" s="11" t="inlineStr"/>
       <c r="F218" s="11" t="inlineStr"/>
       <c r="G218" s="11" t="inlineStr"/>
@@ -4789,18 +4763,18 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="B219" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But I'll still give it a try because I told my my boss today that they should find out from Ministry of Finance if they received any official letter from from Korea. If if it was this kind of thing, I would have, like, if if it was Costa Rica, I would have tried to, hey, if you guys started, like I would just call my minister or ask your minister or advisors to the minister, do you know if the minister is well acquainted with the Ministry of Finance? If they're well acquainted, from peer to peer, they will say, hey, you know, if you're going to Korea, one of the key projects for me would be this. So if you meet together with the minister of finance, please talk about this. Just that key thing, because we think if those agendas happen, they're going to be one-on-one meetings. Formal meetings.</t>
-        </is>
-      </c>
-      <c r="C219" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D219" s="11" t="inlineStr"/>
+          <t>[Comment] So, for me, the 5 Ys is actually very practical and helpful.</t>
+        </is>
+      </c>
+      <c r="C219" s="11" t="inlineStr"/>
+      <c r="D219" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="E219" s="11" t="inlineStr"/>
       <c r="F219" s="11" t="inlineStr"/>
       <c r="G219" s="11" t="inlineStr"/>
@@ -4809,18 +4783,18 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>23:16</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Also, um there are two Nigerians that are coming for the digitology event. Both of them are working in African Development Bank. So these are other and other people that that I want to use because I also already told the that we should schedule a meeting with with them when they arrive for the let's have like even if it's 30 minutes, let's have a meeting together and and discuss on they because for them, they know the areas that you can apply for funds for and it will get easier, easier approval.</t>
-        </is>
-      </c>
-      <c r="C220" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D220" s="11" t="inlineStr"/>
+          <t>[Comment] So I think I can use this in the future as well.</t>
+        </is>
+      </c>
+      <c r="C220" s="11" t="inlineStr"/>
+      <c r="D220" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E220" s="11" t="inlineStr"/>
       <c r="F220" s="11" t="inlineStr"/>
       <c r="G220" s="11" t="inlineStr"/>
@@ -4829,19 +4803,19 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>30:44</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="B221" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah, I have some ongoing and pending.</t>
-        </is>
-      </c>
-      <c r="C221" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Voluntary Response] Very useful.</t>
+        </is>
+      </c>
+      <c r="C221" s="11" t="inlineStr"/>
       <c r="D221" s="11" t="inlineStr"/>
-      <c r="E221" s="11" t="inlineStr"/>
+      <c r="E221" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F221" s="11" t="inlineStr"/>
       <c r="G221" s="11" t="inlineStr"/>
       <c r="H221" s="12" t="inlineStr"/>
@@ -4849,39 +4823,39 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>30:46</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Okay.</t>
-        </is>
-      </c>
-      <c r="C222" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Voluntary Response] Very useful.</t>
+        </is>
+      </c>
+      <c r="C222" s="11" t="inlineStr"/>
       <c r="D222" s="11" t="inlineStr"/>
       <c r="E222" s="11" t="inlineStr"/>
-      <c r="F222" s="11" t="inlineStr"/>
+      <c r="F222" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="G222" s="11" t="inlineStr"/>
       <c r="H222" s="12" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>30:49</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="B223" s="10" t="inlineStr">
         <is>
-          <t>[Comment] because I initiated direct discussion with the DG of the NDTI to introduce the NTS adoption concept and to gauge his.</t>
-        </is>
-      </c>
-      <c r="C223" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] Thank you.</t>
+        </is>
+      </c>
+      <c r="C223" s="11" t="inlineStr"/>
       <c r="D223" s="11" t="inlineStr"/>
-      <c r="E223" s="11" t="inlineStr"/>
+      <c r="E223" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F223" s="11" t="inlineStr"/>
       <c r="G223" s="11" t="inlineStr"/>
       <c r="H223" s="12" t="inlineStr"/>
@@ -4889,12 +4863,12 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>30:59</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Institutional interest.</t>
+          <t>[Comment] Thank you.</t>
         </is>
       </c>
       <c r="C224" s="9" t="n">
@@ -4909,58 +4883,58 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>31:02</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="B225" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So the DG expressed optimism that the collaboration will solve both NBTIS operational problem and Nigeria's broader R&amp;D coordination challenge.</t>
-        </is>
-      </c>
-      <c r="C225" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] Thank you, Professor.</t>
+        </is>
+      </c>
+      <c r="C225" s="11" t="inlineStr"/>
       <c r="D225" s="11" t="inlineStr"/>
       <c r="E225" s="11" t="inlineStr"/>
       <c r="F225" s="11" t="inlineStr"/>
-      <c r="G225" s="11" t="inlineStr"/>
+      <c r="G225" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H225" s="12" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
         <is>
-          <t>31:13</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So also the supervising director, I I discussed with him. So he the he confirmed ministry level relevance and undertook to escalate also to the DG of NBTI.</t>
-        </is>
-      </c>
-      <c r="C226" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] Thank you, Professor.</t>
+        </is>
+      </c>
+      <c r="C226" s="11" t="inlineStr"/>
       <c r="D226" s="11" t="inlineStr"/>
       <c r="E226" s="11" t="inlineStr"/>
-      <c r="F226" s="11" t="inlineStr"/>
+      <c r="F226" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="G226" s="11" t="inlineStr"/>
       <c r="H226" s="12" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>34:45</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="B227" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I identify FMS the Federal Ministry of Innovation, Science and Technology as a primary institutional owner of the proposed collaboration.</t>
-        </is>
-      </c>
-      <c r="C227" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D227" s="11" t="inlineStr"/>
+          <t>[Comment] Thank you, ma'am.</t>
+        </is>
+      </c>
+      <c r="C227" s="11" t="inlineStr"/>
+      <c r="D227" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E227" s="11" t="inlineStr"/>
       <c r="F227" s="11" t="inlineStr"/>
       <c r="G227" s="11" t="inlineStr"/>
@@ -4969,99 +4943,99 @@
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
         <is>
-          <t>34:54</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Who are the holders of the econ mandate executive for the five authority.</t>
-        </is>
-      </c>
-      <c r="C228" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Voluntary Response] Yeah, yeah.</t>
+        </is>
+      </c>
+      <c r="C228" s="11" t="inlineStr"/>
       <c r="D228" s="11" t="inlineStr"/>
       <c r="E228" s="11" t="inlineStr"/>
       <c r="F228" s="11" t="inlineStr"/>
-      <c r="G228" s="11" t="inlineStr"/>
+      <c r="G228" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H228" s="12" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="9" t="inlineStr">
         <is>
-          <t>34:58</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="B229" s="10" t="inlineStr">
         <is>
-          <t>[Comment] budgetary authority.</t>
-        </is>
-      </c>
-      <c r="C229" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Comment] They're doing so much in Nigeria right now.</t>
+        </is>
+      </c>
+      <c r="C229" s="11" t="inlineStr"/>
       <c r="D229" s="11" t="inlineStr"/>
       <c r="E229" s="11" t="inlineStr"/>
       <c r="F229" s="11" t="inlineStr"/>
-      <c r="G229" s="11" t="inlineStr"/>
+      <c r="G229" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H229" s="12" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="9" t="inlineStr">
         <is>
-          <t>35:13</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Maybe it depends on the level of collaboration they had with-</t>
-        </is>
-      </c>
-      <c r="C230" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] That's from Korea.</t>
+        </is>
+      </c>
+      <c r="C230" s="11" t="inlineStr"/>
       <c r="D230" s="11" t="inlineStr"/>
       <c r="E230" s="11" t="inlineStr"/>
       <c r="F230" s="11" t="inlineStr"/>
-      <c r="G230" s="11" t="inlineStr"/>
+      <c r="G230" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H230" s="12" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>36:48</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="B231" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah.</t>
+          <t>[Question to Professor] The company has to be like 10 years in the [inaudible].</t>
         </is>
       </c>
       <c r="C231" s="11" t="inlineStr"/>
       <c r="D231" s="11" t="inlineStr"/>
-      <c r="E231" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E231" s="11" t="inlineStr"/>
       <c r="F231" s="11" t="inlineStr"/>
-      <c r="G231" s="11" t="inlineStr"/>
+      <c r="G231" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="H231" s="12" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="9" t="inlineStr">
         <is>
-          <t>36:54</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Supply side that's the Korean side.</t>
-        </is>
-      </c>
-      <c r="C232" s="11" t="inlineStr"/>
+          <t>[Question to Professor] Ah, okay. So, so we cannot [inaudible].</t>
+        </is>
+      </c>
+      <c r="C232" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="D232" s="11" t="inlineStr"/>
-      <c r="E232" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="E232" s="11" t="inlineStr"/>
       <c r="F232" s="11" t="inlineStr"/>
       <c r="G232" s="11" t="inlineStr"/>
       <c r="H232" s="12" t="inlineStr"/>
@@ -5069,16 +5043,16 @@
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>41:12</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="B233" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because it</t>
+          <t>[Comment] I see.</t>
         </is>
       </c>
       <c r="C233" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D233" s="11" t="inlineStr"/>
       <c r="E233" s="11" t="inlineStr"/>
@@ -5089,16 +5063,16 @@
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>41:17</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="B234" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah, from they sort of they give a conducive environment for for development of startups where they develop their</t>
+          <t>[Comment] His son. Is that Hong?</t>
         </is>
       </c>
       <c r="C234" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D234" s="11" t="inlineStr"/>
       <c r="E234" s="11" t="inlineStr"/>
@@ -5109,16 +5083,16 @@
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>43:31</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="B235" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I'm looking at it from the angle that like A3, like even the what she explained earlier today, that so many startups, they they</t>
+          <t>[Comment] But from what he's saying, he said he's not them that sends the invitation that I they don't have any business with sending the invitation. No Nypa. The Ministry of Foreign Affairs and the Ministry of Science and Technology.</t>
         </is>
       </c>
       <c r="C235" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D235" s="11" t="inlineStr"/>
       <c r="E235" s="11" t="inlineStr"/>
@@ -5129,16 +5103,16 @@
     <row r="236">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>45:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="B236" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Okay.</t>
+          <t>[Comment] They said it's not even Science and Technology or Nypa.</t>
         </is>
       </c>
       <c r="C236" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D236" s="11" t="inlineStr"/>
       <c r="E236" s="11" t="inlineStr"/>
@@ -5149,16 +5123,16 @@
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>50:13</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="B237" s="10" t="inlineStr">
         <is>
-          <t>[Comment] [inaudible] synthesis.</t>
+          <t>[Comment] Because I'm I'm supposed to meet him and Professor next month on the 22nd.</t>
         </is>
       </c>
       <c r="C237" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D237" s="11" t="inlineStr"/>
       <c r="E237" s="11" t="inlineStr"/>
@@ -5169,16 +5143,16 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>50:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="B238" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Okay. Uh for me, uh I input the contextual intelligence uh I have uh one ongoing which is benchmarking for AI globally.</t>
+          <t>[Comment] So he said it's part of the I think is initiated from our home countries. That is normally sent to Ministry of Finance, not even Science and Technology.</t>
         </is>
       </c>
       <c r="C238" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D238" s="11" t="inlineStr"/>
       <c r="E238" s="11" t="inlineStr"/>
@@ -5189,16 +5163,16 @@
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>50:39</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="B239" s="10" t="inlineStr">
         <is>
-          <t>[Comment] and validate.</t>
+          <t>[Comment] They they might not even know when they send.</t>
         </is>
       </c>
       <c r="C239" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D239" s="11" t="inlineStr"/>
       <c r="E239" s="11" t="inlineStr"/>
@@ -5209,16 +5183,16 @@
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>50:40</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah.</t>
+          <t>[Comment] African Development Bank. And it's in partnership with Ministry of Finance of Korea. That they they normally send it to Ministry of Finance of the of the other countries.</t>
         </is>
       </c>
       <c r="C240" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D240" s="11" t="inlineStr"/>
       <c r="E240" s="11" t="inlineStr"/>
@@ -5229,16 +5203,16 @@
     <row r="241">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>51:09</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="B241" s="10" t="inlineStr">
         <is>
-          <t>[Comment] It's totally different.</t>
+          <t>[Comment] Gido. right?</t>
         </is>
       </c>
       <c r="C241" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D241" s="11" t="inlineStr"/>
       <c r="E241" s="11" t="inlineStr"/>
@@ -5249,32 +5223,32 @@
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>51:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>[Comment] The person is still to bring the minister of Science and Technology to, because it wouldn't only focus on NTIS then, because so many other things will speak of.</t>
-        </is>
-      </c>
-      <c r="C242" s="11" t="inlineStr"/>
+          <t>[Comment] around September or so.</t>
+        </is>
+      </c>
+      <c r="C242" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D242" s="11" t="inlineStr"/>
       <c r="E242" s="11" t="inlineStr"/>
       <c r="F242" s="11" t="inlineStr"/>
-      <c r="G242" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="G242" s="11" t="inlineStr"/>
       <c r="H242" s="12" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>51:19</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="B243" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So I tried kinda to find the which one is the use the business division that they will approach.</t>
+          <t>[Comment] I think it's July.</t>
         </is>
       </c>
       <c r="C243" s="9" t="n">
@@ -5289,12 +5263,12 @@
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
         <is>
-          <t>51:27</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So maybe after I get the that information, I will</t>
+          <t>[Question to Professor] I think it's July.</t>
         </is>
       </c>
       <c r="C244" s="9" t="n">
@@ -5309,16 +5283,16 @@
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>51:31</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="B245" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah, try to match my my problem statement. So uh but uh up till now I haven't still get the the result. So I put it in can be. For the for the use case targeted. The business side.</t>
+          <t>[Comment] I I Yeah.</t>
         </is>
       </c>
       <c r="C245" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D245" s="11" t="inlineStr"/>
       <c r="E245" s="11" t="inlineStr"/>
@@ -5329,16 +5303,16 @@
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
         <is>
-          <t>51:45</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And for the stakeholder engagement,</t>
+          <t>[Comment] Yeah, yeah, yeah. I heard that it's gonna be in July. The visit the African Minister's visit.</t>
         </is>
       </c>
       <c r="C246" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D246" s="11" t="inlineStr"/>
       <c r="E246" s="11" t="inlineStr"/>
@@ -5349,19 +5323,19 @@
     <row r="247">
       <c r="A247" s="9" t="inlineStr">
         <is>
-          <t>51:46</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="B247" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Well.</t>
-        </is>
-      </c>
-      <c r="C247" s="11" t="inlineStr"/>
+          <t>[Comment] Yeah, for them, the only thing I mean it's an it's just an invitation because they know how to fast track their own visa. You just need.</t>
+        </is>
+      </c>
+      <c r="C247" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="D247" s="11" t="inlineStr"/>
-      <c r="E247" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E247" s="11" t="inlineStr"/>
       <c r="F247" s="11" t="inlineStr"/>
       <c r="G247" s="11" t="inlineStr"/>
       <c r="H247" s="12" t="inlineStr"/>
@@ -5369,16 +5343,16 @@
     <row r="248">
       <c r="A248" s="9" t="inlineStr">
         <is>
-          <t>51:50</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="B248" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Ah yeah, actually it's two.</t>
+          <t>[Comment] So that that's why that's where I had the challenge. I told him, and he said them and Minister of Science and ICT don't have any anything to do with with that invitation. That the Minister of Finance normally sends it to the Minister of Finance of African countries.</t>
         </is>
       </c>
       <c r="C248" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D248" s="11" t="inlineStr"/>
       <c r="E248" s="11" t="inlineStr"/>
@@ -5389,16 +5363,16 @@
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>51:55</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="B249" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah. Next to help my statement.</t>
+          <t>[Comment] Yeah.</t>
         </is>
       </c>
       <c r="C249" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D249" s="11" t="inlineStr"/>
       <c r="E249" s="11" t="inlineStr"/>
@@ -5409,19 +5383,19 @@
     <row r="250">
       <c r="A250" s="9" t="inlineStr">
         <is>
-          <t>51:56</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="B250" s="10" t="inlineStr">
         <is>
-          <t>[Comment] It's.</t>
-        </is>
-      </c>
-      <c r="C250" s="11" t="inlineStr"/>
+          <t>[Comment] So that we have to find out on our own.</t>
+        </is>
+      </c>
+      <c r="C250" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="D250" s="11" t="inlineStr"/>
-      <c r="E250" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E250" s="11" t="inlineStr"/>
       <c r="F250" s="11" t="inlineStr"/>
       <c r="G250" s="11" t="inlineStr"/>
       <c r="H250" s="12" t="inlineStr"/>
@@ -5429,12 +5403,12 @@
     <row r="251">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>51:59</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="B251" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And for uh for the stakeholder engagement, confirm legal clearance from BRI legal team for collaboration. In term of the, let's say I go with uh either either either partner, toorus, Moai or blah blah blah. Uh so it is also uh in uh pending.</t>
+          <t>[Comment] Yeah, I and it's on AI and digital transformation. So I'm wondering why they're only inviting only Ministers of of Finance instead of the relevant ministers.</t>
         </is>
       </c>
       <c r="C251" s="9" t="n">
@@ -5449,16 +5423,16 @@
     <row r="252">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>52:24</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="B252" s="10" t="inlineStr">
         <is>
-          <t>[Comment] In term after we get the TTS model can uh is it legal to to to be deployed to deploy in?</t>
+          <t>[Comment] Yeah.</t>
         </is>
       </c>
       <c r="C252" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D252" s="11" t="inlineStr"/>
       <c r="E252" s="11" t="inlineStr"/>
@@ -5469,16 +5443,16 @@
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>52:35</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="B253" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Oh yeah, yeah, yeah. I I put it also.</t>
+          <t>[Comment] Yeah.</t>
         </is>
       </c>
       <c r="C253" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D253" s="11" t="inlineStr"/>
       <c r="E253" s="11" t="inlineStr"/>
@@ -5489,16 +5463,16 @@
     <row r="254">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>52:38</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="B254" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh and next I move to the technology scouting.</t>
+          <t>[Comment] But I think he told</t>
         </is>
       </c>
       <c r="C254" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D254" s="11" t="inlineStr"/>
       <c r="E254" s="11" t="inlineStr"/>
@@ -5509,16 +5483,16 @@
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>52:57</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="B255" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Uh Professor Yun, she also already replied.</t>
+          <t>[Comment] But I'll still give it a try because I told my my boss today that they should find out from Ministry of Finance if they received any official letter from from Korea. If if it was this kind of thing, I would have, like, if if it was Costa Rica, I would have tried to, hey, if you guys started, like I would just call my minister or ask your minister or advisors to the minister, do you know if the minister is well acquainted with the Ministry of Finance? If they're well acquainted, from peer to peer, they will say, hey, you know, if you're going to Korea, one of the key projects for me would be this. So if you meet together with the minister of finance, please talk about this. Just that key thing, because we think if those agendas happen, they're going to be one-on-one meetings. Formal meetings.</t>
         </is>
       </c>
       <c r="C255" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D255" s="11" t="inlineStr"/>
       <c r="E255" s="11" t="inlineStr"/>
@@ -5529,16 +5503,16 @@
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>53:01</t>
+          <t>23:16</t>
         </is>
       </c>
       <c r="B256" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And now this, I actually I put it in the maybe I can just jump, jump.</t>
+          <t>[Comment] Also, um there are two Nigerians that are coming for the digitology event. Both of them are working in African Development Bank. So these are other and other people that that I want to use because I also already told the that we should schedule a meeting with with them when they arrive for the let's have like even if it's 30 minutes, let's have a meeting together and and discuss on they because for them, they know the areas that you can apply for funds for and it will get easier, easier approval.</t>
         </is>
       </c>
       <c r="C256" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D256" s="11" t="inlineStr"/>
       <c r="E256" s="11" t="inlineStr"/>
@@ -5549,16 +5523,16 @@
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>53:07</t>
+          <t>30:44</t>
         </is>
       </c>
       <c r="B257" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Jump, jump.</t>
+          <t>[Voluntary Response] Yeah, I have some ongoing and pending.</t>
         </is>
       </c>
       <c r="C257" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D257" s="11" t="inlineStr"/>
       <c r="E257" s="11" t="inlineStr"/>
@@ -5569,16 +5543,16 @@
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>53:40</t>
+          <t>30:46</t>
         </is>
       </c>
       <c r="B258" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Exactly. But to to to watering down, maybe I will put the Koika and I will try to explain them. Uh actually, there will be, I can, sorry, uh I can approach the Koika. But still you need to also show the the the BRI uh must have so some need also.</t>
+          <t>[Comment] Okay.</t>
         </is>
       </c>
       <c r="C258" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D258" s="11" t="inlineStr"/>
       <c r="E258" s="11" t="inlineStr"/>
@@ -5589,16 +5563,16 @@
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>54:04</t>
+          <t>30:49</t>
         </is>
       </c>
       <c r="B259" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah, that that's so that's time.</t>
+          <t>[Comment] because I initiated direct discussion with the DG of the NDTI to introduce the NTS adoption concept and to gauge his.</t>
         </is>
       </c>
       <c r="C259" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D259" s="11" t="inlineStr"/>
       <c r="E259" s="11" t="inlineStr"/>
@@ -5609,16 +5583,16 @@
     <row r="260">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>54:07</t>
+          <t>30:59</t>
         </is>
       </c>
       <c r="B260" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yes, the commitment and I and that's kind of the thing that I want to to to approach to them, to to the to the</t>
+          <t>[Comment] Institutional interest.</t>
         </is>
       </c>
       <c r="C260" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D260" s="11" t="inlineStr"/>
       <c r="E260" s="11" t="inlineStr"/>
@@ -5629,12 +5603,12 @@
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>54:21</t>
+          <t>31:02</t>
         </is>
       </c>
       <c r="B261" s="10" t="inlineStr">
         <is>
-          <t>[Comment] That's why I'm uh before</t>
+          <t>[Comment] So the DG expressed optimism that the collaboration will solve both NBTIS operational problem and Nigeria's broader R&amp;D coordination challenge.</t>
         </is>
       </c>
       <c r="C261" s="9" t="n">
@@ -5649,16 +5623,16 @@
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>54:35</t>
+          <t>31:13</t>
         </is>
       </c>
       <c r="B262" s="10" t="inlineStr">
         <is>
-          <t>[Comment] No, yeah, yeah.</t>
+          <t>[Comment] So also the supervising director, I I discussed with him. So he the he confirmed ministry level relevance and undertook to escalate also to the DG of NBTI.</t>
         </is>
       </c>
       <c r="C262" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D262" s="11" t="inlineStr"/>
       <c r="E262" s="11" t="inlineStr"/>
@@ -5669,12 +5643,12 @@
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>54:37</t>
+          <t>34:45</t>
         </is>
       </c>
       <c r="B263" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But I mean, uh in term So but in term to I replay more to the Professor Yuan.</t>
+          <t>[Comment] I identify FMS the Federal Ministry of Innovation, Science and Technology as a primary institutional owner of the proposed collaboration.</t>
         </is>
       </c>
       <c r="C263" s="9" t="n">
@@ -5689,16 +5663,16 @@
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>54:45</t>
+          <t>34:54</t>
         </is>
       </c>
       <c r="B264" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yun, Professor Yun, I have to at least I think I need to state the budget. So you you see</t>
+          <t>[Question to Professor] Who are the holders of the econ mandate executive for the five authority.</t>
         </is>
       </c>
       <c r="C264" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D264" s="11" t="inlineStr"/>
       <c r="E264" s="11" t="inlineStr"/>
@@ -5709,16 +5683,16 @@
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>55:11</t>
+          <t>34:58</t>
         </is>
       </c>
       <c r="B265" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] So I will try to communicate with them and then I will try to escalate it to his boss or her boss.</t>
+          <t>[Comment] budgetary authority.</t>
         </is>
       </c>
       <c r="C265" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D265" s="11" t="inlineStr"/>
       <c r="E265" s="11" t="inlineStr"/>
@@ -5729,16 +5703,16 @@
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>56:05</t>
+          <t>35:13</t>
         </is>
       </c>
       <c r="B266" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah.</t>
+          <t>[Comment] Maybe it depends on the level of collaboration they had with-</t>
         </is>
       </c>
       <c r="C266" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D266" s="11" t="inlineStr"/>
       <c r="E266" s="11" t="inlineStr"/>
@@ -5749,19 +5723,19 @@
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>56:12</t>
+          <t>36:48</t>
         </is>
       </c>
       <c r="B267" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh, I will just share my experience. Actually, I tried to approach one of the, uh, in charge in [inaudible] I will not mention names of course. I just asked her if, um, for the project that I want to propose, is it possible to be granted using the Korean Fund because one of my friends worked on a project and that project was granted by the Korean Fund. So, uh, I just asked her if it's possible. And she said that, um, for the Korean Fund, um, they are only granting projects that is between the Korean government and the Indonesian government. So, if your project is from your institution, for example, your research center, and you will ask for a grant, if the counterpart of the fund is the Korean company, it's possible. But if it's not and you're just asking for a fund for your personal project, it's not possible. But if you have, uh, for example, you work in a research center and then your research center will ask for a fund and the fund is from the Korean government, but then your counterpart, for example, in the research center is from Korea, then it's possible. But she mentioned that as far as I know, this is from the perspective of this person that I talked to, she said that it has to be a government-to-government transaction to avail a Korean fund, not from a personal or individual. So, I don't know if that is really the case or maybe it depends on the agency. So that's why, um, if you are, if you will just approach a person, they might give you, uh, a different answer.</t>
+          <t>[Comment] Yeah.</t>
         </is>
       </c>
       <c r="C267" s="11" t="inlineStr"/>
-      <c r="D267" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E267" s="11" t="inlineStr"/>
+      <c r="D267" s="11" t="inlineStr"/>
+      <c r="E267" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F267" s="11" t="inlineStr"/>
       <c r="G267" s="11" t="inlineStr"/>
       <c r="H267" s="12" t="inlineStr"/>
@@ -5769,19 +5743,19 @@
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>60:06</t>
+          <t>36:54</t>
         </is>
       </c>
       <c r="B268" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Okay. Okay. I got it. So I think it's fair that it is, yeah, if I think my company should give uh a demo first for that just to impress the Indonesian partner.</t>
-        </is>
-      </c>
-      <c r="C268" s="9" t="n">
-        <v>6</v>
-      </c>
+          <t>[Comment] Supply side that's the Korean side.</t>
+        </is>
+      </c>
+      <c r="C268" s="11" t="inlineStr"/>
       <c r="D268" s="11" t="inlineStr"/>
-      <c r="E268" s="11" t="inlineStr"/>
+      <c r="E268" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="F268" s="11" t="inlineStr"/>
       <c r="G268" s="11" t="inlineStr"/>
       <c r="H268" s="12" t="inlineStr"/>
@@ -5789,16 +5763,16 @@
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>60:29</t>
+          <t>41:12</t>
         </is>
       </c>
       <c r="B269" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yes, right.</t>
+          <t>[Comment] Because it</t>
         </is>
       </c>
       <c r="C269" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D269" s="11" t="inlineStr"/>
       <c r="E269" s="11" t="inlineStr"/>
@@ -5809,18 +5783,18 @@
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>60:35</t>
+          <t>41:17</t>
         </is>
       </c>
       <c r="B270" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Okay. Ma'am.</t>
-        </is>
-      </c>
-      <c r="C270" s="11" t="inlineStr"/>
-      <c r="D270" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Voluntary Response] Yeah, from they sort of they give a conducive environment for for development of startups where they develop their</t>
+        </is>
+      </c>
+      <c r="C270" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D270" s="11" t="inlineStr"/>
       <c r="E270" s="11" t="inlineStr"/>
       <c r="F270" s="11" t="inlineStr"/>
       <c r="G270" s="11" t="inlineStr"/>
@@ -5829,18 +5803,18 @@
     <row r="271">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>60:36</t>
+          <t>43:31</t>
         </is>
       </c>
       <c r="B271" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Yes, ma'am. I actually I don't want to add anything because our agenda is fixed already. But uh earlier, uh you told that if they're having the meeting, if we should uh provide to them the the time and then the the duration, right? So the agenda is 1 hour long. So when they're having the meeting, should we like put the time, for example, 30 minutes for the presentation, then 10 minutes for Q&amp;A something like that?</t>
-        </is>
-      </c>
-      <c r="C271" s="11" t="inlineStr"/>
-      <c r="D271" s="9" t="n">
-        <v>6</v>
-      </c>
+          <t>[Voluntary Response] I'm looking at it from the angle that like A3, like even the what she explained earlier today, that so many startups, they they</t>
+        </is>
+      </c>
+      <c r="C271" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D271" s="11" t="inlineStr"/>
       <c r="E271" s="11" t="inlineStr"/>
       <c r="F271" s="11" t="inlineStr"/>
       <c r="G271" s="11" t="inlineStr"/>
@@ -5849,98 +5823,98 @@
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>61:54</t>
+          <t>45:00</t>
         </is>
       </c>
       <c r="B272" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Ma'am.</t>
-        </is>
-      </c>
-      <c r="C272" s="11" t="inlineStr"/>
+          <t>[Comment] Okay.</t>
+        </is>
+      </c>
+      <c r="C272" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D272" s="11" t="inlineStr"/>
       <c r="E272" s="11" t="inlineStr"/>
-      <c r="F272" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F272" s="11" t="inlineStr"/>
       <c r="G272" s="11" t="inlineStr"/>
       <c r="H272" s="12" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>61:56</t>
+          <t>50:13</t>
         </is>
       </c>
       <c r="B273" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yes, ma'am. Uh, earlier this year, I did my internship in a company called [inaudible]. Uh, it is a Korean company, uh, also. So, uh, I asked one of my supervisor in there who are, who is Korean. So I asked him like, is there any like fund for like students to do like research for their final project or something? So he told me that actually Korea has a lot of funding, uh, but it's not for like international students. It's only for Korean students. Yeah, so I don't know why. So, uh, I didn't push it further because like I thought like, yeah, it's only for Korean students and I'm not Korean. So yeah.</t>
-        </is>
-      </c>
-      <c r="C273" s="11" t="inlineStr"/>
+          <t>[Comment] [inaudible] synthesis.</t>
+        </is>
+      </c>
+      <c r="C273" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="D273" s="11" t="inlineStr"/>
       <c r="E273" s="11" t="inlineStr"/>
-      <c r="F273" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F273" s="11" t="inlineStr"/>
       <c r="G273" s="11" t="inlineStr"/>
       <c r="H273" s="12" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>62:00</t>
+          <t>50:27</t>
         </is>
       </c>
       <c r="B274" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Um, I think no, ma'am. I think it's good already. I just want to clarify for number four because if we confirm with them that we are meeting with them already. Do we still need to send the invitation to them or can we just have the meeting right away since it's already confirmed?</t>
-        </is>
-      </c>
-      <c r="C274" s="11" t="inlineStr"/>
+          <t>[Comment] Okay. Uh for me, uh I input the contextual intelligence uh I have uh one ongoing which is benchmarking for AI globally.</t>
+        </is>
+      </c>
+      <c r="C274" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D274" s="11" t="inlineStr"/>
       <c r="E274" s="11" t="inlineStr"/>
-      <c r="F274" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="F274" s="11" t="inlineStr"/>
       <c r="G274" s="11" t="inlineStr"/>
       <c r="H274" s="12" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>63:06</t>
+          <t>50:39</t>
         </is>
       </c>
       <c r="B275" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Oh, is it?</t>
-        </is>
-      </c>
-      <c r="C275" s="11" t="inlineStr"/>
+          <t>[Comment] and validate.</t>
+        </is>
+      </c>
+      <c r="C275" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D275" s="11" t="inlineStr"/>
       <c r="E275" s="11" t="inlineStr"/>
-      <c r="F275" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F275" s="11" t="inlineStr"/>
       <c r="G275" s="11" t="inlineStr"/>
       <c r="H275" s="12" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>63:17</t>
+          <t>50:40</t>
         </is>
       </c>
       <c r="B276" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] No, ma'am. I did not send the email yet. Because I told you that my partner actually haven't given me a response when will be the meeting so I think I should send it when they actually give a response.</t>
-        </is>
-      </c>
-      <c r="C276" s="11" t="inlineStr"/>
-      <c r="D276" s="9" t="n">
-        <v>6</v>
-      </c>
+          <t>[Voluntary Response] Yeah.</t>
+        </is>
+      </c>
+      <c r="C276" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D276" s="11" t="inlineStr"/>
       <c r="E276" s="11" t="inlineStr"/>
       <c r="F276" s="11" t="inlineStr"/>
       <c r="G276" s="11" t="inlineStr"/>
@@ -5949,56 +5923,56 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>64:08</t>
+          <t>51:09</t>
         </is>
       </c>
       <c r="B277" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Uh, no, ma'am. I also still need to work on it.</t>
-        </is>
-      </c>
-      <c r="C277" s="11" t="inlineStr"/>
+          <t>[Comment] It's totally different.</t>
+        </is>
+      </c>
+      <c r="C277" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D277" s="11" t="inlineStr"/>
       <c r="E277" s="11" t="inlineStr"/>
       <c r="F277" s="11" t="inlineStr"/>
-      <c r="G277" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G277" s="11" t="inlineStr"/>
       <c r="H277" s="12" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>64:28</t>
+          <t>51:18</t>
         </is>
       </c>
       <c r="B278" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Okay, ma'am.</t>
+          <t>[Comment] The person is still to bring the minister of Science and Technology to, because it wouldn't only focus on NTIS then, because so many other things will speak of.</t>
         </is>
       </c>
       <c r="C278" s="11" t="inlineStr"/>
       <c r="D278" s="11" t="inlineStr"/>
       <c r="E278" s="11" t="inlineStr"/>
-      <c r="F278" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G278" s="11" t="inlineStr"/>
+      <c r="F278" s="11" t="inlineStr"/>
+      <c r="G278" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="H278" s="12" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>64:36</t>
+          <t>51:19</t>
         </is>
       </c>
       <c r="B279" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yes, ma'am.</t>
+          <t>[Comment] So I tried kinda to find the which one is the use the business division that they will approach.</t>
         </is>
       </c>
       <c r="C279" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D279" s="11" t="inlineStr"/>
       <c r="E279" s="11" t="inlineStr"/>
@@ -6009,39 +5983,39 @@
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>64:39</t>
+          <t>51:27</t>
         </is>
       </c>
       <c r="B280" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] No, ma'am. I haven't tried to, uh, approach anybody.</t>
-        </is>
-      </c>
-      <c r="C280" s="11" t="inlineStr"/>
+          <t>[Comment] So maybe after I get the that information, I will</t>
+        </is>
+      </c>
+      <c r="C280" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D280" s="11" t="inlineStr"/>
       <c r="E280" s="11" t="inlineStr"/>
       <c r="F280" s="11" t="inlineStr"/>
-      <c r="G280" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G280" s="11" t="inlineStr"/>
       <c r="H280" s="12" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>64:59</t>
+          <t>51:31</t>
         </is>
       </c>
       <c r="B281" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yes, ma'am.</t>
-        </is>
-      </c>
-      <c r="C281" s="11" t="inlineStr"/>
+          <t>[Comment] Yeah, try to match my my problem statement. So uh but uh up till now I haven't still get the the result. So I put it in can be. For the for the use case targeted. The business side.</t>
+        </is>
+      </c>
+      <c r="C281" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="D281" s="11" t="inlineStr"/>
-      <c r="E281" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E281" s="11" t="inlineStr"/>
       <c r="F281" s="11" t="inlineStr"/>
       <c r="G281" s="11" t="inlineStr"/>
       <c r="H281" s="12" t="inlineStr"/>
@@ -6049,39 +6023,39 @@
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>66:18</t>
+          <t>51:45</t>
         </is>
       </c>
       <c r="B282" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Okay, thank you.</t>
-        </is>
-      </c>
-      <c r="C282" s="11" t="inlineStr"/>
+          <t>[Comment] And for the stakeholder engagement,</t>
+        </is>
+      </c>
+      <c r="C282" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D282" s="11" t="inlineStr"/>
       <c r="E282" s="11" t="inlineStr"/>
       <c r="F282" s="11" t="inlineStr"/>
-      <c r="G282" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G282" s="11" t="inlineStr"/>
       <c r="H282" s="12" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>66:28</t>
+          <t>51:46</t>
         </is>
       </c>
       <c r="B283" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I think Stephen.</t>
+          <t>[Voluntary Response] Well.</t>
         </is>
       </c>
       <c r="C283" s="11" t="inlineStr"/>
-      <c r="D283" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E283" s="11" t="inlineStr"/>
+      <c r="D283" s="11" t="inlineStr"/>
+      <c r="E283" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F283" s="11" t="inlineStr"/>
       <c r="G283" s="11" t="inlineStr"/>
       <c r="H283" s="12" t="inlineStr"/>
@@ -6089,747 +6063,3147 @@
     <row r="284">
       <c r="A284" s="9" t="inlineStr">
         <is>
-          <t>66:36</t>
+          <t>51:50</t>
         </is>
       </c>
       <c r="B284" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah, uh, I think number one was just to do the scanning about the contextual intelligence about data data graph.</t>
-        </is>
-      </c>
-      <c r="C284" s="11" t="inlineStr"/>
+          <t>[Comment] Ah yeah, actually it's two.</t>
+        </is>
+      </c>
+      <c r="C284" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D284" s="11" t="inlineStr"/>
       <c r="E284" s="11" t="inlineStr"/>
       <c r="F284" s="11" t="inlineStr"/>
-      <c r="G284" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="G284" s="11" t="inlineStr"/>
       <c r="H284" s="12" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="9" t="inlineStr">
         <is>
-          <t>66:49</t>
+          <t>51:55</t>
         </is>
       </c>
       <c r="B285" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] My main activities here were I was only the one.</t>
-        </is>
-      </c>
-      <c r="C285" s="11" t="inlineStr"/>
+          <t>[Comment] Yeah. Next to help my statement.</t>
+        </is>
+      </c>
+      <c r="C285" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D285" s="11" t="inlineStr"/>
       <c r="E285" s="11" t="inlineStr"/>
       <c r="F285" s="11" t="inlineStr"/>
-      <c r="G285" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G285" s="11" t="inlineStr"/>
       <c r="H285" s="12" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="9" t="inlineStr">
         <is>
-          <t>66:57</t>
+          <t>51:56</t>
         </is>
       </c>
       <c r="B286" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Have any issues?</t>
+          <t>[Comment] It's.</t>
         </is>
       </c>
       <c r="C286" s="11" t="inlineStr"/>
       <c r="D286" s="11" t="inlineStr"/>
-      <c r="E286" s="11" t="inlineStr"/>
+      <c r="E286" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F286" s="11" t="inlineStr"/>
-      <c r="G286" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G286" s="11" t="inlineStr"/>
       <c r="H286" s="12" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="9" t="inlineStr">
         <is>
-          <t>66:59</t>
+          <t>51:59</t>
         </is>
       </c>
       <c r="B287" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] If you go by operational steps here, in this part, you automatically look for something to do.</t>
-        </is>
-      </c>
-      <c r="C287" s="11" t="inlineStr"/>
+          <t>[Comment] And for uh for the stakeholder engagement, confirm legal clearance from BRI legal team for collaboration. In term of the, let's say I go with uh either either either partner, toorus, Moai or blah blah blah. Uh so it is also uh in uh pending.</t>
+        </is>
+      </c>
+      <c r="C287" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="D287" s="11" t="inlineStr"/>
       <c r="E287" s="11" t="inlineStr"/>
       <c r="F287" s="11" t="inlineStr"/>
-      <c r="G287" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G287" s="11" t="inlineStr"/>
       <c r="H287" s="12" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="9" t="inlineStr">
         <is>
-          <t>67:06</t>
+          <t>52:24</t>
         </is>
       </c>
       <c r="B288" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And then.</t>
-        </is>
-      </c>
-      <c r="C288" s="11" t="inlineStr"/>
+          <t>[Comment] In term after we get the TTS model can uh is it legal to to to be deployed to deploy in?</t>
+        </is>
+      </c>
+      <c r="C288" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D288" s="11" t="inlineStr"/>
       <c r="E288" s="11" t="inlineStr"/>
       <c r="F288" s="11" t="inlineStr"/>
-      <c r="G288" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G288" s="11" t="inlineStr"/>
       <c r="H288" s="12" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>67:07</t>
+          <t>52:35</t>
         </is>
       </c>
       <c r="B289" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And then I also review the the the policy gap, we have currently, it was also there.</t>
-        </is>
-      </c>
-      <c r="C289" s="11" t="inlineStr"/>
+          <t>[Comment] Oh yeah, yeah, yeah. I I put it also.</t>
+        </is>
+      </c>
+      <c r="C289" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D289" s="11" t="inlineStr"/>
       <c r="E289" s="11" t="inlineStr"/>
       <c r="F289" s="11" t="inlineStr"/>
-      <c r="G289" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G289" s="11" t="inlineStr"/>
       <c r="H289" s="12" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="9" t="inlineStr">
         <is>
-          <t>67:14</t>
+          <t>52:38</t>
         </is>
       </c>
       <c r="B290" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And I also analyzing the the the the the the the</t>
-        </is>
-      </c>
-      <c r="C290" s="11" t="inlineStr"/>
+          <t>[Comment] Uh and next I move to the technology scouting.</t>
+        </is>
+      </c>
+      <c r="C290" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D290" s="11" t="inlineStr"/>
       <c r="E290" s="11" t="inlineStr"/>
       <c r="F290" s="11" t="inlineStr"/>
-      <c r="G290" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G290" s="11" t="inlineStr"/>
       <c r="H290" s="12" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="9" t="inlineStr">
         <is>
-          <t>67:21</t>
+          <t>52:57</t>
         </is>
       </c>
       <c r="B291" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Detail?</t>
-        </is>
-      </c>
-      <c r="C291" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] Uh Professor Yun, she also already replied.</t>
+        </is>
+      </c>
+      <c r="C291" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D291" s="11" t="inlineStr"/>
       <c r="E291" s="11" t="inlineStr"/>
       <c r="F291" s="11" t="inlineStr"/>
-      <c r="G291" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G291" s="11" t="inlineStr"/>
       <c r="H291" s="12" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="9" t="inlineStr">
         <is>
-          <t>67:22</t>
+          <t>53:01</t>
         </is>
       </c>
       <c r="B292" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Okay.</t>
-        </is>
-      </c>
-      <c r="C292" s="11" t="inlineStr"/>
+          <t>[Comment] And now this, I actually I put it in the maybe I can just jump, jump.</t>
+        </is>
+      </c>
+      <c r="C292" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D292" s="11" t="inlineStr"/>
       <c r="E292" s="11" t="inlineStr"/>
       <c r="F292" s="11" t="inlineStr"/>
-      <c r="G292" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G292" s="11" t="inlineStr"/>
       <c r="H292" s="12" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="9" t="inlineStr">
         <is>
-          <t>67:27</t>
+          <t>53:07</t>
         </is>
       </c>
       <c r="B293" s="10" t="inlineStr">
         <is>
-          <t>[Comment] For me, I thought it's an activity.</t>
-        </is>
-      </c>
-      <c r="C293" s="11" t="inlineStr"/>
+          <t>[Comment] Jump, jump.</t>
+        </is>
+      </c>
+      <c r="C293" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D293" s="11" t="inlineStr"/>
       <c r="E293" s="11" t="inlineStr"/>
       <c r="F293" s="11" t="inlineStr"/>
-      <c r="G293" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G293" s="11" t="inlineStr"/>
       <c r="H293" s="12" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="9" t="inlineStr">
         <is>
-          <t>67:36</t>
+          <t>53:40</t>
         </is>
       </c>
       <c r="B294" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Okay.</t>
-        </is>
-      </c>
-      <c r="C294" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] Exactly. But to to to watering down, maybe I will put the Koika and I will try to explain them. Uh actually, there will be, I can, sorry, uh I can approach the Koika. But still you need to also show the the the BRI uh must have so some need also.</t>
+        </is>
+      </c>
+      <c r="C294" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="D294" s="11" t="inlineStr"/>
       <c r="E294" s="11" t="inlineStr"/>
       <c r="F294" s="11" t="inlineStr"/>
-      <c r="G294" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G294" s="11" t="inlineStr"/>
       <c r="H294" s="12" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="9" t="inlineStr">
         <is>
-          <t>67:41</t>
+          <t>54:04</t>
         </is>
       </c>
       <c r="B295" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Identify the new</t>
-        </is>
-      </c>
-      <c r="C295" s="11" t="inlineStr"/>
+          <t>[Comment] Yeah, that that's so that's time.</t>
+        </is>
+      </c>
+      <c r="C295" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D295" s="11" t="inlineStr"/>
       <c r="E295" s="11" t="inlineStr"/>
       <c r="F295" s="11" t="inlineStr"/>
-      <c r="G295" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G295" s="11" t="inlineStr"/>
       <c r="H295" s="12" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="9" t="inlineStr">
         <is>
-          <t>68:14</t>
+          <t>54:07</t>
         </is>
       </c>
       <c r="B296" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] So I'm going for the stakeholders engagement.</t>
-        </is>
-      </c>
-      <c r="C296" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] Yes, the commitment and I and that's kind of the thing that I want to to to approach to them, to to the to the</t>
+        </is>
+      </c>
+      <c r="C296" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D296" s="11" t="inlineStr"/>
       <c r="E296" s="11" t="inlineStr"/>
       <c r="F296" s="11" t="inlineStr"/>
-      <c r="G296" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G296" s="11" t="inlineStr"/>
       <c r="H296" s="12" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="9" t="inlineStr">
         <is>
-          <t>68:23</t>
+          <t>54:21</t>
         </is>
       </c>
       <c r="B297" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah, I got it from that side.</t>
-        </is>
-      </c>
-      <c r="C297" s="11" t="inlineStr"/>
+          <t>[Comment] That's why I'm uh before</t>
+        </is>
+      </c>
+      <c r="C297" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D297" s="11" t="inlineStr"/>
       <c r="E297" s="11" t="inlineStr"/>
       <c r="F297" s="11" t="inlineStr"/>
-      <c r="G297" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G297" s="11" t="inlineStr"/>
       <c r="H297" s="12" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="9" t="inlineStr">
         <is>
-          <t>68:26</t>
+          <t>54:35</t>
         </is>
       </c>
       <c r="B298" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] That is mapping the institutional mandates.</t>
-        </is>
-      </c>
-      <c r="C298" s="11" t="inlineStr"/>
+          <t>[Comment] No, yeah, yeah.</t>
+        </is>
+      </c>
+      <c r="C298" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D298" s="11" t="inlineStr"/>
       <c r="E298" s="11" t="inlineStr"/>
       <c r="F298" s="11" t="inlineStr"/>
-      <c r="G298" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G298" s="11" t="inlineStr"/>
       <c r="H298" s="12" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="9" t="inlineStr">
         <is>
-          <t>68:29</t>
+          <t>54:37</t>
         </is>
       </c>
       <c r="B299" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I need to consult the rural ICT department, and this is the division manager Charles Tambo.</t>
-        </is>
-      </c>
-      <c r="C299" s="11" t="inlineStr"/>
+          <t>[Comment] But I mean, uh in term So but in term to I replay more to the Professor Yuan.</t>
+        </is>
+      </c>
+      <c r="C299" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D299" s="11" t="inlineStr"/>
       <c r="E299" s="11" t="inlineStr"/>
       <c r="F299" s="11" t="inlineStr"/>
-      <c r="G299" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G299" s="11" t="inlineStr"/>
       <c r="H299" s="12" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="9" t="inlineStr">
         <is>
-          <t>68:36</t>
+          <t>54:45</t>
         </is>
       </c>
       <c r="B300" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I saw I think you saw the email, I got a problem.</t>
-        </is>
-      </c>
-      <c r="C300" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] Yun, Professor Yun, I have to at least I think I need to state the budget. So you you see</t>
+        </is>
+      </c>
+      <c r="C300" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="D300" s="11" t="inlineStr"/>
       <c r="E300" s="11" t="inlineStr"/>
       <c r="F300" s="11" t="inlineStr"/>
-      <c r="G300" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G300" s="11" t="inlineStr"/>
       <c r="H300" s="12" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="9" t="inlineStr">
         <is>
-          <t>68:40</t>
+          <t>55:11</t>
         </is>
       </c>
       <c r="B301" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Uh and then I validate it just to align with the the technical specifications.</t>
-        </is>
-      </c>
-      <c r="C301" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] So I will try to communicate with them and then I will try to escalate it to his boss or her boss.</t>
+        </is>
+      </c>
+      <c r="C301" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D301" s="11" t="inlineStr"/>
       <c r="E301" s="11" t="inlineStr"/>
       <c r="F301" s="11" t="inlineStr"/>
-      <c r="G301" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G301" s="11" t="inlineStr"/>
       <c r="H301" s="12" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="9" t="inlineStr">
         <is>
-          <t>68:48</t>
+          <t>56:05</t>
         </is>
       </c>
       <c r="B302" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And then I go to technology coaching.</t>
-        </is>
-      </c>
-      <c r="C302" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] Yeah.</t>
+        </is>
+      </c>
+      <c r="C302" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D302" s="11" t="inlineStr"/>
       <c r="E302" s="11" t="inlineStr"/>
       <c r="F302" s="11" t="inlineStr"/>
-      <c r="G302" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G302" s="11" t="inlineStr"/>
       <c r="H302" s="12" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="9" t="inlineStr">
         <is>
-          <t>68:52</t>
+          <t>56:12</t>
         </is>
       </c>
       <c r="B303" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] So this is the here in Korea I've searched, and in fact, it's the</t>
+          <t>[Comment] Uh, I will just share my experience. Actually, I tried to approach one of the, uh, in charge in [inaudible] I will not mention names of course. I just asked her if, um, for the project that I want to propose, is it possible to be granted using the Korean Fund because one of my friends worked on a project and that project was granted by the Korean Fund. So, uh, I just asked her if it's possible. And she said that, um, for the Korean Fund, um, they are only granting projects that is between the Korean government and the Indonesian government. So, if your project is from your institution, for example, your research center, and you will ask for a grant, if the counterpart of the fund is the Korean company, it's possible. But if it's not and you're just asking for a fund for your personal project, it's not possible. But if you have, uh, for example, you work in a research center and then your research center will ask for a fund and the fund is from the Korean government, but then your counterpart, for example, in the research center is from Korea, then it's possible. But she mentioned that as far as I know, this is from the perspective of this person that I talked to, she said that it has to be a government-to-government transaction to avail a Korean fund, not from a personal or individual. So, I don't know if that is really the case or maybe it depends on the agency. So that's why, um, if you are, if you will just approach a person, they might give you, uh, a different answer.</t>
         </is>
       </c>
       <c r="C303" s="11" t="inlineStr"/>
-      <c r="D303" s="11" t="inlineStr"/>
+      <c r="D303" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="E303" s="11" t="inlineStr"/>
       <c r="F303" s="11" t="inlineStr"/>
-      <c r="G303" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G303" s="11" t="inlineStr"/>
       <c r="H303" s="12" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="9" t="inlineStr">
         <is>
-          <t>69:24</t>
+          <t>60:06</t>
         </is>
       </c>
       <c r="B304" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But what I saw from the website.</t>
-        </is>
-      </c>
-      <c r="C304" s="11" t="inlineStr"/>
+          <t>[Comment] Okay. Okay. I got it. So I think it's fair that it is, yeah, if I think my company should give uh a demo first for that just to impress the Indonesian partner.</t>
+        </is>
+      </c>
+      <c r="C304" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="D304" s="11" t="inlineStr"/>
       <c r="E304" s="11" t="inlineStr"/>
       <c r="F304" s="11" t="inlineStr"/>
-      <c r="G304" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G304" s="11" t="inlineStr"/>
       <c r="H304" s="12" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="B305" s="14" t="inlineStr">
+      <c r="A305" s="9" t="inlineStr">
+        <is>
+          <t>60:29</t>
+        </is>
+      </c>
+      <c r="B305" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Yes, right.</t>
+        </is>
+      </c>
+      <c r="C305" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D305" s="11" t="inlineStr"/>
+      <c r="E305" s="11" t="inlineStr"/>
+      <c r="F305" s="11" t="inlineStr"/>
+      <c r="G305" s="11" t="inlineStr"/>
+      <c r="H305" s="12" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="9" t="inlineStr">
+        <is>
+          <t>60:35</t>
+        </is>
+      </c>
+      <c r="B306" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Okay. Ma'am.</t>
+        </is>
+      </c>
+      <c r="C306" s="11" t="inlineStr"/>
+      <c r="D306" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E306" s="11" t="inlineStr"/>
+      <c r="F306" s="11" t="inlineStr"/>
+      <c r="G306" s="11" t="inlineStr"/>
+      <c r="H306" s="12" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="9" t="inlineStr">
+        <is>
+          <t>60:36</t>
+        </is>
+      </c>
+      <c r="B307" s="10" t="inlineStr">
+        <is>
+          <t>[Question to Professor] Yes, ma'am. I actually I don't want to add anything because our agenda is fixed already. But uh earlier, uh you told that if they're having the meeting, if we should uh provide to them the the time and then the the duration, right? So the agenda is 1 hour long. So when they're having the meeting, should we like put the time, for example, 30 minutes for the presentation, then 10 minutes for Q&amp;A something like that?</t>
+        </is>
+      </c>
+      <c r="C307" s="11" t="inlineStr"/>
+      <c r="D307" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E307" s="11" t="inlineStr"/>
+      <c r="F307" s="11" t="inlineStr"/>
+      <c r="G307" s="11" t="inlineStr"/>
+      <c r="H307" s="12" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="9" t="inlineStr">
+        <is>
+          <t>61:54</t>
+        </is>
+      </c>
+      <c r="B308" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Ma'am.</t>
+        </is>
+      </c>
+      <c r="C308" s="11" t="inlineStr"/>
+      <c r="D308" s="11" t="inlineStr"/>
+      <c r="E308" s="11" t="inlineStr"/>
+      <c r="F308" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G308" s="11" t="inlineStr"/>
+      <c r="H308" s="12" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="9" t="inlineStr">
+        <is>
+          <t>61:56</t>
+        </is>
+      </c>
+      <c r="B309" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Yes, ma'am. Uh, earlier this year, I did my internship in a company called [inaudible]. Uh, it is a Korean company, uh, also. So, uh, I asked one of my supervisor in there who are, who is Korean. So I asked him like, is there any like fund for like students to do like research for their final project or something? So he told me that actually Korea has a lot of funding, uh, but it's not for like international students. It's only for Korean students. Yeah, so I don't know why. So, uh, I didn't push it further because like I thought like, yeah, it's only for Korean students and I'm not Korean. So yeah.</t>
+        </is>
+      </c>
+      <c r="C309" s="11" t="inlineStr"/>
+      <c r="D309" s="11" t="inlineStr"/>
+      <c r="E309" s="11" t="inlineStr"/>
+      <c r="F309" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G309" s="11" t="inlineStr"/>
+      <c r="H309" s="12" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="9" t="inlineStr">
+        <is>
+          <t>62:00</t>
+        </is>
+      </c>
+      <c r="B310" s="10" t="inlineStr">
+        <is>
+          <t>[Question to Professor] Um, I think no, ma'am. I think it's good already. I just want to clarify for number four because if we confirm with them that we are meeting with them already. Do we still need to send the invitation to them or can we just have the meeting right away since it's already confirmed?</t>
+        </is>
+      </c>
+      <c r="C310" s="11" t="inlineStr"/>
+      <c r="D310" s="11" t="inlineStr"/>
+      <c r="E310" s="11" t="inlineStr"/>
+      <c r="F310" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G310" s="11" t="inlineStr"/>
+      <c r="H310" s="12" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="9" t="inlineStr">
+        <is>
+          <t>63:06</t>
+        </is>
+      </c>
+      <c r="B311" s="10" t="inlineStr">
+        <is>
+          <t>[Question to Professor] Oh, is it?</t>
+        </is>
+      </c>
+      <c r="C311" s="11" t="inlineStr"/>
+      <c r="D311" s="11" t="inlineStr"/>
+      <c r="E311" s="11" t="inlineStr"/>
+      <c r="F311" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G311" s="11" t="inlineStr"/>
+      <c r="H311" s="12" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="9" t="inlineStr">
+        <is>
+          <t>63:17</t>
+        </is>
+      </c>
+      <c r="B312" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] No, ma'am. I did not send the email yet. Because I told you that my partner actually haven't given me a response when will be the meeting so I think I should send it when they actually give a response.</t>
+        </is>
+      </c>
+      <c r="C312" s="11" t="inlineStr"/>
+      <c r="D312" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E312" s="11" t="inlineStr"/>
+      <c r="F312" s="11" t="inlineStr"/>
+      <c r="G312" s="11" t="inlineStr"/>
+      <c r="H312" s="12" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="9" t="inlineStr">
+        <is>
+          <t>64:08</t>
+        </is>
+      </c>
+      <c r="B313" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Uh, no, ma'am. I also still need to work on it.</t>
+        </is>
+      </c>
+      <c r="C313" s="11" t="inlineStr"/>
+      <c r="D313" s="11" t="inlineStr"/>
+      <c r="E313" s="11" t="inlineStr"/>
+      <c r="F313" s="11" t="inlineStr"/>
+      <c r="G313" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H313" s="12" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="9" t="inlineStr">
+        <is>
+          <t>64:28</t>
+        </is>
+      </c>
+      <c r="B314" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Okay, ma'am.</t>
+        </is>
+      </c>
+      <c r="C314" s="11" t="inlineStr"/>
+      <c r="D314" s="11" t="inlineStr"/>
+      <c r="E314" s="11" t="inlineStr"/>
+      <c r="F314" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G314" s="11" t="inlineStr"/>
+      <c r="H314" s="12" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="9" t="inlineStr">
+        <is>
+          <t>64:36</t>
+        </is>
+      </c>
+      <c r="B315" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Yes, ma'am.</t>
+        </is>
+      </c>
+      <c r="C315" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D315" s="11" t="inlineStr"/>
+      <c r="E315" s="11" t="inlineStr"/>
+      <c r="F315" s="11" t="inlineStr"/>
+      <c r="G315" s="11" t="inlineStr"/>
+      <c r="H315" s="12" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="9" t="inlineStr">
+        <is>
+          <t>64:39</t>
+        </is>
+      </c>
+      <c r="B316" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] No, ma'am. I haven't tried to, uh, approach anybody.</t>
+        </is>
+      </c>
+      <c r="C316" s="11" t="inlineStr"/>
+      <c r="D316" s="11" t="inlineStr"/>
+      <c r="E316" s="11" t="inlineStr"/>
+      <c r="F316" s="11" t="inlineStr"/>
+      <c r="G316" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H316" s="12" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="9" t="inlineStr">
+        <is>
+          <t>64:59</t>
+        </is>
+      </c>
+      <c r="B317" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Yes, ma'am.</t>
+        </is>
+      </c>
+      <c r="C317" s="11" t="inlineStr"/>
+      <c r="D317" s="11" t="inlineStr"/>
+      <c r="E317" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F317" s="11" t="inlineStr"/>
+      <c r="G317" s="11" t="inlineStr"/>
+      <c r="H317" s="12" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="9" t="inlineStr">
+        <is>
+          <t>66:18</t>
+        </is>
+      </c>
+      <c r="B318" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Okay, thank you.</t>
+        </is>
+      </c>
+      <c r="C318" s="11" t="inlineStr"/>
+      <c r="D318" s="11" t="inlineStr"/>
+      <c r="E318" s="11" t="inlineStr"/>
+      <c r="F318" s="11" t="inlineStr"/>
+      <c r="G318" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H318" s="12" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="9" t="inlineStr">
+        <is>
+          <t>66:28</t>
+        </is>
+      </c>
+      <c r="B319" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] I think Stephen.</t>
+        </is>
+      </c>
+      <c r="C319" s="11" t="inlineStr"/>
+      <c r="D319" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E319" s="11" t="inlineStr"/>
+      <c r="F319" s="11" t="inlineStr"/>
+      <c r="G319" s="11" t="inlineStr"/>
+      <c r="H319" s="12" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="9" t="inlineStr">
+        <is>
+          <t>66:36</t>
+        </is>
+      </c>
+      <c r="B320" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Yeah, uh, I think number one was just to do the scanning about the contextual intelligence about data data graph.</t>
+        </is>
+      </c>
+      <c r="C320" s="11" t="inlineStr"/>
+      <c r="D320" s="11" t="inlineStr"/>
+      <c r="E320" s="11" t="inlineStr"/>
+      <c r="F320" s="11" t="inlineStr"/>
+      <c r="G320" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H320" s="12" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="9" t="inlineStr">
+        <is>
+          <t>66:49</t>
+        </is>
+      </c>
+      <c r="B321" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] My main activities here were I was only the one.</t>
+        </is>
+      </c>
+      <c r="C321" s="11" t="inlineStr"/>
+      <c r="D321" s="11" t="inlineStr"/>
+      <c r="E321" s="11" t="inlineStr"/>
+      <c r="F321" s="11" t="inlineStr"/>
+      <c r="G321" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H321" s="12" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="9" t="inlineStr">
+        <is>
+          <t>66:57</t>
+        </is>
+      </c>
+      <c r="B322" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Have any issues?</t>
+        </is>
+      </c>
+      <c r="C322" s="11" t="inlineStr"/>
+      <c r="D322" s="11" t="inlineStr"/>
+      <c r="E322" s="11" t="inlineStr"/>
+      <c r="F322" s="11" t="inlineStr"/>
+      <c r="G322" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H322" s="12" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="9" t="inlineStr">
+        <is>
+          <t>66:59</t>
+        </is>
+      </c>
+      <c r="B323" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] If you go by operational steps here, in this part, you automatically look for something to do.</t>
+        </is>
+      </c>
+      <c r="C323" s="11" t="inlineStr"/>
+      <c r="D323" s="11" t="inlineStr"/>
+      <c r="E323" s="11" t="inlineStr"/>
+      <c r="F323" s="11" t="inlineStr"/>
+      <c r="G323" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H323" s="12" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="9" t="inlineStr">
+        <is>
+          <t>67:06</t>
+        </is>
+      </c>
+      <c r="B324" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] And then.</t>
+        </is>
+      </c>
+      <c r="C324" s="11" t="inlineStr"/>
+      <c r="D324" s="11" t="inlineStr"/>
+      <c r="E324" s="11" t="inlineStr"/>
+      <c r="F324" s="11" t="inlineStr"/>
+      <c r="G324" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H324" s="12" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="9" t="inlineStr">
+        <is>
+          <t>67:07</t>
+        </is>
+      </c>
+      <c r="B325" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] And then I also review the the the policy gap, we have currently, it was also there.</t>
+        </is>
+      </c>
+      <c r="C325" s="11" t="inlineStr"/>
+      <c r="D325" s="11" t="inlineStr"/>
+      <c r="E325" s="11" t="inlineStr"/>
+      <c r="F325" s="11" t="inlineStr"/>
+      <c r="G325" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H325" s="12" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="9" t="inlineStr">
+        <is>
+          <t>67:14</t>
+        </is>
+      </c>
+      <c r="B326" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] And I also analyzing the the the the the the the</t>
+        </is>
+      </c>
+      <c r="C326" s="11" t="inlineStr"/>
+      <c r="D326" s="11" t="inlineStr"/>
+      <c r="E326" s="11" t="inlineStr"/>
+      <c r="F326" s="11" t="inlineStr"/>
+      <c r="G326" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H326" s="12" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="9" t="inlineStr">
+        <is>
+          <t>67:21</t>
+        </is>
+      </c>
+      <c r="B327" s="10" t="inlineStr">
+        <is>
+          <t>[Question to Professor] Detail?</t>
+        </is>
+      </c>
+      <c r="C327" s="11" t="inlineStr"/>
+      <c r="D327" s="11" t="inlineStr"/>
+      <c r="E327" s="11" t="inlineStr"/>
+      <c r="F327" s="11" t="inlineStr"/>
+      <c r="G327" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H327" s="12" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="9" t="inlineStr">
+        <is>
+          <t>67:22</t>
+        </is>
+      </c>
+      <c r="B328" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Okay.</t>
+        </is>
+      </c>
+      <c r="C328" s="11" t="inlineStr"/>
+      <c r="D328" s="11" t="inlineStr"/>
+      <c r="E328" s="11" t="inlineStr"/>
+      <c r="F328" s="11" t="inlineStr"/>
+      <c r="G328" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H328" s="12" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="9" t="inlineStr">
+        <is>
+          <t>67:27</t>
+        </is>
+      </c>
+      <c r="B329" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] For me, I thought it's an activity.</t>
+        </is>
+      </c>
+      <c r="C329" s="11" t="inlineStr"/>
+      <c r="D329" s="11" t="inlineStr"/>
+      <c r="E329" s="11" t="inlineStr"/>
+      <c r="F329" s="11" t="inlineStr"/>
+      <c r="G329" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H329" s="12" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="9" t="inlineStr">
+        <is>
+          <t>67:36</t>
+        </is>
+      </c>
+      <c r="B330" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Okay.</t>
+        </is>
+      </c>
+      <c r="C330" s="11" t="inlineStr"/>
+      <c r="D330" s="11" t="inlineStr"/>
+      <c r="E330" s="11" t="inlineStr"/>
+      <c r="F330" s="11" t="inlineStr"/>
+      <c r="G330" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H330" s="12" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="9" t="inlineStr">
+        <is>
+          <t>67:41</t>
+        </is>
+      </c>
+      <c r="B331" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Identify the new</t>
+        </is>
+      </c>
+      <c r="C331" s="11" t="inlineStr"/>
+      <c r="D331" s="11" t="inlineStr"/>
+      <c r="E331" s="11" t="inlineStr"/>
+      <c r="F331" s="11" t="inlineStr"/>
+      <c r="G331" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H331" s="12" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="9" t="inlineStr">
+        <is>
+          <t>68:14</t>
+        </is>
+      </c>
+      <c r="B332" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] So I'm going for the stakeholders engagement.</t>
+        </is>
+      </c>
+      <c r="C332" s="11" t="inlineStr"/>
+      <c r="D332" s="11" t="inlineStr"/>
+      <c r="E332" s="11" t="inlineStr"/>
+      <c r="F332" s="11" t="inlineStr"/>
+      <c r="G332" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H332" s="12" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="9" t="inlineStr">
+        <is>
+          <t>68:23</t>
+        </is>
+      </c>
+      <c r="B333" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Yeah, I got it from that side.</t>
+        </is>
+      </c>
+      <c r="C333" s="11" t="inlineStr"/>
+      <c r="D333" s="11" t="inlineStr"/>
+      <c r="E333" s="11" t="inlineStr"/>
+      <c r="F333" s="11" t="inlineStr"/>
+      <c r="G333" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H333" s="12" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="9" t="inlineStr">
+        <is>
+          <t>68:26</t>
+        </is>
+      </c>
+      <c r="B334" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] That is mapping the institutional mandates.</t>
+        </is>
+      </c>
+      <c r="C334" s="11" t="inlineStr"/>
+      <c r="D334" s="11" t="inlineStr"/>
+      <c r="E334" s="11" t="inlineStr"/>
+      <c r="F334" s="11" t="inlineStr"/>
+      <c r="G334" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H334" s="12" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="9" t="inlineStr">
+        <is>
+          <t>68:29</t>
+        </is>
+      </c>
+      <c r="B335" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] I need to consult the rural ICT department, and this is the division manager Charles Tambo.</t>
+        </is>
+      </c>
+      <c r="C335" s="11" t="inlineStr"/>
+      <c r="D335" s="11" t="inlineStr"/>
+      <c r="E335" s="11" t="inlineStr"/>
+      <c r="F335" s="11" t="inlineStr"/>
+      <c r="G335" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H335" s="12" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="9" t="inlineStr">
+        <is>
+          <t>68:36</t>
+        </is>
+      </c>
+      <c r="B336" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] I saw I think you saw the email, I got a problem.</t>
+        </is>
+      </c>
+      <c r="C336" s="11" t="inlineStr"/>
+      <c r="D336" s="11" t="inlineStr"/>
+      <c r="E336" s="11" t="inlineStr"/>
+      <c r="F336" s="11" t="inlineStr"/>
+      <c r="G336" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H336" s="12" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="9" t="inlineStr">
+        <is>
+          <t>68:40</t>
+        </is>
+      </c>
+      <c r="B337" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Uh and then I validate it just to align with the the technical specifications.</t>
+        </is>
+      </c>
+      <c r="C337" s="11" t="inlineStr"/>
+      <c r="D337" s="11" t="inlineStr"/>
+      <c r="E337" s="11" t="inlineStr"/>
+      <c r="F337" s="11" t="inlineStr"/>
+      <c r="G337" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H337" s="12" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="9" t="inlineStr">
+        <is>
+          <t>68:48</t>
+        </is>
+      </c>
+      <c r="B338" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] And then I go to technology coaching.</t>
+        </is>
+      </c>
+      <c r="C338" s="11" t="inlineStr"/>
+      <c r="D338" s="11" t="inlineStr"/>
+      <c r="E338" s="11" t="inlineStr"/>
+      <c r="F338" s="11" t="inlineStr"/>
+      <c r="G338" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H338" s="12" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="9" t="inlineStr">
+        <is>
+          <t>68:52</t>
+        </is>
+      </c>
+      <c r="B339" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] So this is the here in Korea I've searched, and in fact, it's the</t>
+        </is>
+      </c>
+      <c r="C339" s="11" t="inlineStr"/>
+      <c r="D339" s="11" t="inlineStr"/>
+      <c r="E339" s="11" t="inlineStr"/>
+      <c r="F339" s="11" t="inlineStr"/>
+      <c r="G339" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H339" s="12" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="9" t="inlineStr">
+        <is>
+          <t>69:24</t>
+        </is>
+      </c>
+      <c r="B340" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] But what I saw from the website.</t>
+        </is>
+      </c>
+      <c r="C340" s="11" t="inlineStr"/>
+      <c r="D340" s="11" t="inlineStr"/>
+      <c r="E340" s="11" t="inlineStr"/>
+      <c r="F340" s="11" t="inlineStr"/>
+      <c r="G340" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H340" s="12" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="9" t="inlineStr">
+        <is>
+          <t>70:00</t>
+        </is>
+      </c>
+      <c r="B341" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] And then, uh, Kisa has the source of the regression and whatever, we're gonna mark from there.</t>
+        </is>
+      </c>
+      <c r="C341" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D341" s="11" t="inlineStr"/>
+      <c r="E341" s="11" t="inlineStr"/>
+      <c r="F341" s="11" t="inlineStr"/>
+      <c r="G341" s="11" t="inlineStr"/>
+      <c r="H341" s="12" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="9" t="inlineStr">
+        <is>
+          <t>70:09</t>
+        </is>
+      </c>
+      <c r="B342" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] And then I go to technology exploitation.</t>
+        </is>
+      </c>
+      <c r="C342" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D342" s="11" t="inlineStr"/>
+      <c r="E342" s="11" t="inlineStr"/>
+      <c r="F342" s="11" t="inlineStr"/>
+      <c r="G342" s="11" t="inlineStr"/>
+      <c r="H342" s="12" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="9" t="inlineStr">
+        <is>
+          <t>70:20</t>
+        </is>
+      </c>
+      <c r="B343" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Yeah, this is ongoing. that's what he told me.</t>
+        </is>
+      </c>
+      <c r="C343" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D343" s="11" t="inlineStr"/>
+      <c r="E343" s="11" t="inlineStr"/>
+      <c r="F343" s="11" t="inlineStr"/>
+      <c r="G343" s="11" t="inlineStr"/>
+      <c r="H343" s="12" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="9" t="inlineStr">
+        <is>
+          <t>70:23</t>
+        </is>
+      </c>
+      <c r="B344" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] So assessing the context of</t>
+        </is>
+      </c>
+      <c r="C344" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D344" s="11" t="inlineStr"/>
+      <c r="E344" s="11" t="inlineStr"/>
+      <c r="F344" s="11" t="inlineStr"/>
+      <c r="G344" s="11" t="inlineStr"/>
+      <c r="H344" s="12" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="9" t="inlineStr">
+        <is>
+          <t>70:55</t>
+        </is>
+      </c>
+      <c r="B345" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] And then I will after discussing with the lady did you because, you know, I</t>
+        </is>
+      </c>
+      <c r="C345" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D345" s="11" t="inlineStr"/>
+      <c r="E345" s="11" t="inlineStr"/>
+      <c r="F345" s="11" t="inlineStr"/>
+      <c r="G345" s="11" t="inlineStr"/>
+      <c r="H345" s="12" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="9" t="inlineStr">
+        <is>
+          <t>71:18</t>
+        </is>
+      </c>
+      <c r="B346" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] I really added the company for</t>
+        </is>
+      </c>
+      <c r="C346" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D346" s="11" t="inlineStr"/>
+      <c r="E346" s="11" t="inlineStr"/>
+      <c r="F346" s="11" t="inlineStr"/>
+      <c r="G346" s="11" t="inlineStr"/>
+      <c r="H346" s="12" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="9" t="inlineStr">
+        <is>
+          <t>71:20</t>
+        </is>
+      </c>
+      <c r="B347" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Or any other</t>
+        </is>
+      </c>
+      <c r="C347" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D347" s="11" t="inlineStr"/>
+      <c r="E347" s="11" t="inlineStr"/>
+      <c r="F347" s="11" t="inlineStr"/>
+      <c r="G347" s="11" t="inlineStr"/>
+      <c r="H347" s="12" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="9" t="inlineStr">
+        <is>
+          <t>71:21</t>
+        </is>
+      </c>
+      <c r="B348" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] They had what they call mobile security.</t>
+        </is>
+      </c>
+      <c r="C348" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D348" s="11" t="inlineStr"/>
+      <c r="E348" s="11" t="inlineStr"/>
+      <c r="F348" s="11" t="inlineStr"/>
+      <c r="G348" s="11" t="inlineStr"/>
+      <c r="H348" s="12" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="9" t="inlineStr">
+        <is>
+          <t>71:23</t>
+        </is>
+      </c>
+      <c r="B349" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] But I saw it is on the like after download and you have it on the your smartphone. That's why I need</t>
+        </is>
+      </c>
+      <c r="C349" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D349" s="11" t="inlineStr"/>
+      <c r="E349" s="11" t="inlineStr"/>
+      <c r="F349" s="11" t="inlineStr"/>
+      <c r="G349" s="11" t="inlineStr"/>
+      <c r="H349" s="12" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="9" t="inlineStr">
+        <is>
+          <t>71:31</t>
+        </is>
+      </c>
+      <c r="B350" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] It's good but in terms of my, you know, at the end of the day you need to think about the context of your country. That's why I said this is well good developed countries where everyone has an idea of smart for</t>
+        </is>
+      </c>
+      <c r="C350" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D350" s="11" t="inlineStr"/>
+      <c r="E350" s="11" t="inlineStr"/>
+      <c r="F350" s="11" t="inlineStr"/>
+      <c r="G350" s="11" t="inlineStr"/>
+      <c r="H350" s="12" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="9" t="inlineStr">
+        <is>
+          <t>72:01</t>
+        </is>
+      </c>
+      <c r="B351" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Okay.</t>
+        </is>
+      </c>
+      <c r="C351" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D351" s="11" t="inlineStr"/>
+      <c r="E351" s="11" t="inlineStr"/>
+      <c r="F351" s="11" t="inlineStr"/>
+      <c r="G351" s="11" t="inlineStr"/>
+      <c r="H351" s="12" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="9" t="inlineStr">
+        <is>
+          <t>72:47</t>
+        </is>
+      </c>
+      <c r="B352" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] DIY was misleaded by the because I'm here in Korea and I had the SK that is doing that. That's maybe I find myself and I found them.</t>
+        </is>
+      </c>
+      <c r="C352" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D352" s="11" t="inlineStr"/>
+      <c r="E352" s="11" t="inlineStr"/>
+      <c r="F352" s="11" t="inlineStr"/>
+      <c r="G352" s="11" t="inlineStr"/>
+      <c r="H352" s="12" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="9" t="inlineStr">
+        <is>
+          <t>73:39</t>
+        </is>
+      </c>
+      <c r="B353" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] [laughter]</t>
+        </is>
+      </c>
+      <c r="C353" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D353" s="11" t="inlineStr"/>
+      <c r="E353" s="11" t="inlineStr"/>
+      <c r="F353" s="11" t="inlineStr"/>
+      <c r="G353" s="11" t="inlineStr"/>
+      <c r="H353" s="12" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="9" t="inlineStr">
+        <is>
+          <t>74:25</t>
+        </is>
+      </c>
+      <c r="B354" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Other things are most impending process, all activities, I think I see</t>
+        </is>
+      </c>
+      <c r="C354" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D354" s="11" t="inlineStr"/>
+      <c r="E354" s="11" t="inlineStr"/>
+      <c r="F354" s="11" t="inlineStr"/>
+      <c r="G354" s="11" t="inlineStr"/>
+      <c r="H354" s="12" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="9" t="inlineStr">
+        <is>
+          <t>75:07</t>
+        </is>
+      </c>
+      <c r="B355" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] So if like they say brainstorm,</t>
+        </is>
+      </c>
+      <c r="C355" s="11" t="inlineStr"/>
+      <c r="D355" s="11" t="inlineStr"/>
+      <c r="E355" s="11" t="inlineStr"/>
+      <c r="F355" s="11" t="inlineStr"/>
+      <c r="G355" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H355" s="12" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="9" t="inlineStr">
+        <is>
+          <t>76:15</t>
+        </is>
+      </c>
+      <c r="B356" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Yeah, my ICT already, I have to.</t>
+        </is>
+      </c>
+      <c r="C356" s="11" t="inlineStr"/>
+      <c r="D356" s="11" t="inlineStr"/>
+      <c r="E356" s="11" t="inlineStr"/>
+      <c r="F356" s="11" t="inlineStr"/>
+      <c r="G356" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H356" s="12" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="9" t="inlineStr">
+        <is>
+          <t>76:22</t>
+        </is>
+      </c>
+      <c r="B357" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] I try to benchmark on the other countries.</t>
+        </is>
+      </c>
+      <c r="C357" s="11" t="inlineStr"/>
+      <c r="D357" s="11" t="inlineStr"/>
+      <c r="E357" s="11" t="inlineStr"/>
+      <c r="F357" s="11" t="inlineStr"/>
+      <c r="G357" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H357" s="12" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="9" t="inlineStr">
+        <is>
+          <t>77:05</t>
+        </is>
+      </c>
+      <c r="B358" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] I think the PPT I shared in the evening.</t>
+        </is>
+      </c>
+      <c r="C358" s="11" t="inlineStr"/>
+      <c r="D358" s="11" t="inlineStr"/>
+      <c r="E358" s="11" t="inlineStr"/>
+      <c r="F358" s="11" t="inlineStr"/>
+      <c r="G358" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H358" s="12" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="9" t="inlineStr">
+        <is>
+          <t>77:14</t>
+        </is>
+      </c>
+      <c r="B359" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] The US, Europe, Asia.</t>
+        </is>
+      </c>
+      <c r="C359" s="11" t="inlineStr"/>
+      <c r="D359" s="11" t="inlineStr"/>
+      <c r="E359" s="11" t="inlineStr"/>
+      <c r="F359" s="11" t="inlineStr"/>
+      <c r="G359" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H359" s="12" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="9" t="inlineStr">
+        <is>
+          <t>77:26</t>
+        </is>
+      </c>
+      <c r="B360" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Yes, professor.</t>
+        </is>
+      </c>
+      <c r="C360" s="11" t="inlineStr"/>
+      <c r="D360" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E360" s="11" t="inlineStr"/>
+      <c r="F360" s="11" t="inlineStr"/>
+      <c r="G360" s="11" t="inlineStr"/>
+      <c r="H360" s="12" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="9" t="inlineStr">
+        <is>
+          <t>77:29</t>
+        </is>
+      </c>
+      <c r="B361" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Yeah, thank you, professor.</t>
+        </is>
+      </c>
+      <c r="C361" s="11" t="inlineStr"/>
+      <c r="D361" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E361" s="11" t="inlineStr"/>
+      <c r="F361" s="11" t="inlineStr"/>
+      <c r="G361" s="11" t="inlineStr"/>
+      <c r="H361" s="12" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="9" t="inlineStr">
+        <is>
+          <t>77:30</t>
+        </is>
+      </c>
+      <c r="B362" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Um, after I knew the information that Chilaka already make uh similar of our project, I consultation with Professor Park. So there are there are a lot of data that I have to fulfill. So now it's already completed.</t>
+        </is>
+      </c>
+      <c r="C362" s="11" t="inlineStr"/>
+      <c r="D362" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E362" s="11" t="inlineStr"/>
+      <c r="F362" s="11" t="inlineStr"/>
+      <c r="G362" s="11" t="inlineStr"/>
+      <c r="H362" s="12" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="9" t="inlineStr">
+        <is>
+          <t>77:45</t>
+        </is>
+      </c>
+      <c r="B363" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Um, uh first time I put a socio-economic data collections like I put uh collected poverty. I already make a map also.</t>
+        </is>
+      </c>
+      <c r="C363" s="11" t="inlineStr"/>
+      <c r="D363" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E363" s="11" t="inlineStr"/>
+      <c r="F363" s="11" t="inlineStr"/>
+      <c r="G363" s="11" t="inlineStr"/>
+      <c r="H363" s="12" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="9" t="inlineStr">
+        <is>
+          <t>77:53</t>
+        </is>
+      </c>
+      <c r="B364" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Where is the poverty and also the electricity access uh and uh</t>
+        </is>
+      </c>
+      <c r="C364" s="11" t="inlineStr"/>
+      <c r="D364" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E364" s="11" t="inlineStr"/>
+      <c r="F364" s="11" t="inlineStr"/>
+      <c r="G364" s="11" t="inlineStr"/>
+      <c r="H364" s="12" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="9" t="inlineStr">
+        <is>
+          <t>78:02</t>
+        </is>
+      </c>
+      <c r="B365" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] uh the regulations, uh infrastructure and regulatory scans.</t>
+        </is>
+      </c>
+      <c r="C365" s="11" t="inlineStr"/>
+      <c r="D365" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E365" s="11" t="inlineStr"/>
+      <c r="F365" s="11" t="inlineStr"/>
+      <c r="G365" s="11" t="inlineStr"/>
+      <c r="H365" s="12" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="9" t="inlineStr">
+        <is>
+          <t>78:09</t>
+        </is>
+      </c>
+      <c r="B366" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] So um I put it also the demographic the demographic data.</t>
+        </is>
+      </c>
+      <c r="C366" s="11" t="inlineStr"/>
+      <c r="D366" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E366" s="11" t="inlineStr"/>
+      <c r="F366" s="11" t="inlineStr"/>
+      <c r="G366" s="11" t="inlineStr"/>
+      <c r="H366" s="12" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="9" t="inlineStr">
+        <is>
+          <t>78:15</t>
+        </is>
+      </c>
+      <c r="B367" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Uh the last time I told the professor is the data is already completed that I have to design the uh the design to give to the Infinithill.</t>
+        </is>
+      </c>
+      <c r="C367" s="11" t="inlineStr"/>
+      <c r="D367" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E367" s="11" t="inlineStr"/>
+      <c r="F367" s="11" t="inlineStr"/>
+      <c r="G367" s="11" t="inlineStr"/>
+      <c r="H367" s="12" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="9" t="inlineStr">
+        <is>
+          <t>78:27</t>
+        </is>
+      </c>
+      <c r="B368" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Uh. So the data that I have to fulfill um already completed for the demographical, socio-economic and also</t>
+        </is>
+      </c>
+      <c r="C368" s="11" t="inlineStr"/>
+      <c r="D368" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E368" s="11" t="inlineStr"/>
+      <c r="F368" s="11" t="inlineStr"/>
+      <c r="G368" s="11" t="inlineStr"/>
+      <c r="H368" s="12" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="9" t="inlineStr">
+        <is>
+          <t>78:34</t>
+        </is>
+      </c>
+      <c r="B369" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] It is actually same here.</t>
+        </is>
+      </c>
+      <c r="C369" s="11" t="inlineStr"/>
+      <c r="D369" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E369" s="11" t="inlineStr"/>
+      <c r="F369" s="11" t="inlineStr"/>
+      <c r="G369" s="11" t="inlineStr"/>
+      <c r="H369" s="12" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="9" t="inlineStr">
+        <is>
+          <t>78:37</t>
+        </is>
+      </c>
+      <c r="B370" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] But uh uh not all I put in here. I already make a report to professor.</t>
+        </is>
+      </c>
+      <c r="C370" s="11" t="inlineStr"/>
+      <c r="D370" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E370" s="11" t="inlineStr"/>
+      <c r="F370" s="11" t="inlineStr"/>
+      <c r="G370" s="11" t="inlineStr"/>
+      <c r="H370" s="12" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="9" t="inlineStr">
+        <is>
+          <t>78:45</t>
+        </is>
+      </c>
+      <c r="B371" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] And also after that um uh the professor wants me to make kind of the designs to give to Infinithill Lab.</t>
+        </is>
+      </c>
+      <c r="C371" s="11" t="inlineStr"/>
+      <c r="D371" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E371" s="11" t="inlineStr"/>
+      <c r="F371" s="11" t="inlineStr"/>
+      <c r="G371" s="11" t="inlineStr"/>
+      <c r="H371" s="12" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="9" t="inlineStr">
+        <is>
+          <t>79:03</t>
+        </is>
+      </c>
+      <c r="B372" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Infinithill Lab.</t>
+        </is>
+      </c>
+      <c r="C372" s="11" t="inlineStr"/>
+      <c r="D372" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E372" s="11" t="inlineStr"/>
+      <c r="F372" s="11" t="inlineStr"/>
+      <c r="G372" s="11" t="inlineStr"/>
+      <c r="H372" s="12" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="9" t="inlineStr">
+        <is>
+          <t>79:04</t>
+        </is>
+      </c>
+      <c r="B373" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Infinity Village.</t>
+        </is>
+      </c>
+      <c r="C373" s="11" t="inlineStr"/>
+      <c r="D373" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E373" s="11" t="inlineStr"/>
+      <c r="F373" s="11" t="inlineStr"/>
+      <c r="G373" s="11" t="inlineStr"/>
+      <c r="H373" s="12" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="9" t="inlineStr">
+        <is>
+          <t>79:05</t>
+        </is>
+      </c>
+      <c r="B374" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] And the Infinity Energy, Infinity Energy.</t>
+        </is>
+      </c>
+      <c r="C374" s="11" t="inlineStr"/>
+      <c r="D374" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E374" s="11" t="inlineStr"/>
+      <c r="F374" s="11" t="inlineStr"/>
+      <c r="G374" s="11" t="inlineStr"/>
+      <c r="H374" s="12" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="9" t="inlineStr">
+        <is>
+          <t>79:15</t>
+        </is>
+      </c>
+      <c r="B375" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Um uh</t>
+        </is>
+      </c>
+      <c r="C375" s="11" t="inlineStr"/>
+      <c r="D375" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E375" s="11" t="inlineStr"/>
+      <c r="F375" s="11" t="inlineStr"/>
+      <c r="G375" s="11" t="inlineStr"/>
+      <c r="H375" s="12" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="9" t="inlineStr">
+        <is>
+          <t>80:52</t>
+        </is>
+      </c>
+      <c r="B376" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Uh as for uh Indonesian sides, I already talk also the PLNs.</t>
+        </is>
+      </c>
+      <c r="C376" s="11" t="inlineStr"/>
+      <c r="D376" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E376" s="11" t="inlineStr"/>
+      <c r="F376" s="11" t="inlineStr"/>
+      <c r="G376" s="11" t="inlineStr"/>
+      <c r="H376" s="12" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="9" t="inlineStr">
+        <is>
+          <t>81:08</t>
+        </is>
+      </c>
+      <c r="B377" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Uh, because uh, uh, this, uh, that area has a, uh, equator area, so they, they will get a lot of energy from the solar.</t>
+        </is>
+      </c>
+      <c r="C377" s="11" t="inlineStr"/>
+      <c r="D377" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E377" s="11" t="inlineStr"/>
+      <c r="F377" s="11" t="inlineStr"/>
+      <c r="G377" s="11" t="inlineStr"/>
+      <c r="H377" s="12" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="9" t="inlineStr">
+        <is>
+          <t>81:21</t>
+        </is>
+      </c>
+      <c r="B378" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] And also, uh, there are a lot of uh.</t>
+        </is>
+      </c>
+      <c r="C378" s="11" t="inlineStr"/>
+      <c r="D378" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E378" s="11" t="inlineStr"/>
+      <c r="F378" s="11" t="inlineStr"/>
+      <c r="G378" s="11" t="inlineStr"/>
+      <c r="H378" s="12" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="9" t="inlineStr">
+        <is>
+          <t>81:28</t>
+        </is>
+      </c>
+      <c r="B379" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] So, uh,</t>
+        </is>
+      </c>
+      <c r="C379" s="11" t="inlineStr"/>
+      <c r="D379" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E379" s="11" t="inlineStr"/>
+      <c r="F379" s="11" t="inlineStr"/>
+      <c r="G379" s="11" t="inlineStr"/>
+      <c r="H379" s="12" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="9" t="inlineStr">
+        <is>
+          <t>81:30</t>
+        </is>
+      </c>
+      <c r="B380" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] uh, the, uh, PLN prefer to</t>
+        </is>
+      </c>
+      <c r="C380" s="11" t="inlineStr"/>
+      <c r="D380" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E380" s="11" t="inlineStr"/>
+      <c r="F380" s="11" t="inlineStr"/>
+      <c r="G380" s="11" t="inlineStr"/>
+      <c r="H380" s="12" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="9" t="inlineStr">
+        <is>
+          <t>81:33</t>
+        </is>
+      </c>
+      <c r="B381" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] uh, put the pilot project in the, uh, entity.</t>
+        </is>
+      </c>
+      <c r="C381" s="11" t="inlineStr"/>
+      <c r="D381" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E381" s="11" t="inlineStr"/>
+      <c r="F381" s="11" t="inlineStr"/>
+      <c r="G381" s="11" t="inlineStr"/>
+      <c r="H381" s="12" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="9" t="inlineStr">
+        <is>
+          <t>81:36</t>
+        </is>
+      </c>
+      <c r="B382" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] And also, um, previously I already contacted the, the director of energy there.</t>
+        </is>
+      </c>
+      <c r="C382" s="11" t="inlineStr"/>
+      <c r="D382" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E382" s="11" t="inlineStr"/>
+      <c r="F382" s="11" t="inlineStr"/>
+      <c r="G382" s="11" t="inlineStr"/>
+      <c r="H382" s="12" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="9" t="inlineStr">
+        <is>
+          <t>81:57</t>
+        </is>
+      </c>
+      <c r="B383" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Because I don't have, I didn't review your.</t>
+        </is>
+      </c>
+      <c r="C383" s="11" t="inlineStr"/>
+      <c r="D383" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E383" s="11" t="inlineStr"/>
+      <c r="F383" s="11" t="inlineStr"/>
+      <c r="G383" s="11" t="inlineStr"/>
+      <c r="H383" s="12" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="9" t="inlineStr">
+        <is>
+          <t>82:14</t>
+        </is>
+      </c>
+      <c r="B384" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Ah, okay.</t>
+        </is>
+      </c>
+      <c r="C384" s="11" t="inlineStr"/>
+      <c r="D384" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E384" s="11" t="inlineStr"/>
+      <c r="F384" s="11" t="inlineStr"/>
+      <c r="G384" s="11" t="inlineStr"/>
+      <c r="H384" s="12" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="9" t="inlineStr">
+        <is>
+          <t>82:30</t>
+        </is>
+      </c>
+      <c r="B385" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Yeah, uh, uh.</t>
+        </is>
+      </c>
+      <c r="C385" s="11" t="inlineStr"/>
+      <c r="D385" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E385" s="11" t="inlineStr"/>
+      <c r="F385" s="11" t="inlineStr"/>
+      <c r="G385" s="11" t="inlineStr"/>
+      <c r="H385" s="12" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="9" t="inlineStr">
+        <is>
+          <t>82:58</t>
+        </is>
+      </c>
+      <c r="B386" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] And then, uh the person, uh will be the pilot project. So, uh,</t>
+        </is>
+      </c>
+      <c r="C386" s="11" t="inlineStr"/>
+      <c r="D386" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E386" s="11" t="inlineStr"/>
+      <c r="F386" s="11" t="inlineStr"/>
+      <c r="G386" s="11" t="inlineStr"/>
+      <c r="H386" s="12" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="9" t="inlineStr">
+        <is>
+          <t>83:09</t>
+        </is>
+      </c>
+      <c r="B387" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Also the, the, the the area of solar PV. Okay.</t>
+        </is>
+      </c>
+      <c r="C387" s="11" t="inlineStr"/>
+      <c r="D387" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E387" s="11" t="inlineStr"/>
+      <c r="F387" s="11" t="inlineStr"/>
+      <c r="G387" s="11" t="inlineStr"/>
+      <c r="H387" s="12" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="9" t="inlineStr">
+        <is>
+          <t>84:14</t>
+        </is>
+      </c>
+      <c r="B388" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] At the demand side you need to prove if the</t>
+        </is>
+      </c>
+      <c r="C388" s="11" t="inlineStr"/>
+      <c r="D388" s="11" t="inlineStr"/>
+      <c r="E388" s="11" t="inlineStr"/>
+      <c r="F388" s="11" t="inlineStr"/>
+      <c r="G388" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H388" s="12" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="9" t="inlineStr">
+        <is>
+          <t>84:19</t>
+        </is>
+      </c>
+      <c r="B389" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] the problem you are talking about</t>
+        </is>
+      </c>
+      <c r="C389" s="11" t="inlineStr"/>
+      <c r="D389" s="11" t="inlineStr"/>
+      <c r="E389" s="11" t="inlineStr"/>
+      <c r="F389" s="11" t="inlineStr"/>
+      <c r="G389" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H389" s="12" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="9" t="inlineStr">
+        <is>
+          <t>84:21</t>
+        </is>
+      </c>
+      <c r="B390" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] is real, is is it real to be invested by the</t>
+        </is>
+      </c>
+      <c r="C390" s="11" t="inlineStr"/>
+      <c r="D390" s="11" t="inlineStr"/>
+      <c r="E390" s="11" t="inlineStr"/>
+      <c r="F390" s="11" t="inlineStr"/>
+      <c r="G390" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H390" s="12" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="9" t="inlineStr">
+        <is>
+          <t>84:29</t>
+        </is>
+      </c>
+      <c r="B391" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] maybe even demand, is it the real problem that the government can invest money or Somebody.</t>
+        </is>
+      </c>
+      <c r="C391" s="11" t="inlineStr"/>
+      <c r="D391" s="11" t="inlineStr"/>
+      <c r="E391" s="11" t="inlineStr"/>
+      <c r="F391" s="11" t="inlineStr"/>
+      <c r="G391" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H391" s="12" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="9" t="inlineStr">
+        <is>
+          <t>84:35</t>
+        </is>
+      </c>
+      <c r="B392" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Any donor? That's the demand side.</t>
+        </is>
+      </c>
+      <c r="C392" s="11" t="inlineStr"/>
+      <c r="D392" s="11" t="inlineStr"/>
+      <c r="E392" s="11" t="inlineStr"/>
+      <c r="F392" s="11" t="inlineStr"/>
+      <c r="G392" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H392" s="12" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="9" t="inlineStr">
+        <is>
+          <t>84:37</t>
+        </is>
+      </c>
+      <c r="B393" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] You need to show that they calculate the mathematics, the loopholes in the policies and whatever.</t>
+        </is>
+      </c>
+      <c r="C393" s="11" t="inlineStr"/>
+      <c r="D393" s="11" t="inlineStr"/>
+      <c r="E393" s="11" t="inlineStr"/>
+      <c r="F393" s="11" t="inlineStr"/>
+      <c r="G393" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H393" s="12" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="9" t="inlineStr">
+        <is>
+          <t>84:43</t>
+        </is>
+      </c>
+      <c r="B394" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] And then on the supply side,</t>
+        </is>
+      </c>
+      <c r="C394" s="11" t="inlineStr"/>
+      <c r="D394" s="11" t="inlineStr"/>
+      <c r="E394" s="11" t="inlineStr"/>
+      <c r="F394" s="11" t="inlineStr"/>
+      <c r="G394" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H394" s="12" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="9" t="inlineStr">
+        <is>
+          <t>84:45</t>
+        </is>
+      </c>
+      <c r="B395" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] I think</t>
+        </is>
+      </c>
+      <c r="C395" s="11" t="inlineStr"/>
+      <c r="D395" s="11" t="inlineStr"/>
+      <c r="E395" s="11" t="inlineStr"/>
+      <c r="F395" s="11" t="inlineStr"/>
+      <c r="G395" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H395" s="12" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="9" t="inlineStr">
+        <is>
+          <t>84:47</t>
+        </is>
+      </c>
+      <c r="B396" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] this is the</t>
+        </is>
+      </c>
+      <c r="C396" s="11" t="inlineStr"/>
+      <c r="D396" s="11" t="inlineStr"/>
+      <c r="E396" s="11" t="inlineStr"/>
+      <c r="F396" s="11" t="inlineStr"/>
+      <c r="G396" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H396" s="12" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="9" t="inlineStr">
+        <is>
+          <t>84:51</t>
+        </is>
+      </c>
+      <c r="B397" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] the the one who going to give you the the solution.</t>
+        </is>
+      </c>
+      <c r="C397" s="11" t="inlineStr"/>
+      <c r="D397" s="11" t="inlineStr"/>
+      <c r="E397" s="11" t="inlineStr"/>
+      <c r="F397" s="11" t="inlineStr"/>
+      <c r="G397" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H397" s="12" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="9" t="inlineStr">
+        <is>
+          <t>84:57</t>
+        </is>
+      </c>
+      <c r="B398" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Is is is the</t>
+        </is>
+      </c>
+      <c r="C398" s="11" t="inlineStr"/>
+      <c r="D398" s="11" t="inlineStr"/>
+      <c r="E398" s="11" t="inlineStr"/>
+      <c r="F398" s="11" t="inlineStr"/>
+      <c r="G398" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H398" s="12" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="9" t="inlineStr">
+        <is>
+          <t>85:09</t>
+        </is>
+      </c>
+      <c r="B399" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] that's how I understand it.</t>
+        </is>
+      </c>
+      <c r="C399" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D399" s="11" t="inlineStr"/>
+      <c r="E399" s="11" t="inlineStr"/>
+      <c r="F399" s="11" t="inlineStr"/>
+      <c r="G399" s="11" t="inlineStr"/>
+      <c r="H399" s="12" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="9" t="inlineStr">
+        <is>
+          <t>85:22</t>
+        </is>
+      </c>
+      <c r="B400" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] preliminary synthesis because it is the opportunity generation.</t>
+        </is>
+      </c>
+      <c r="C400" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D400" s="11" t="inlineStr"/>
+      <c r="E400" s="11" t="inlineStr"/>
+      <c r="F400" s="11" t="inlineStr"/>
+      <c r="G400" s="11" t="inlineStr"/>
+      <c r="H400" s="12" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="9" t="inlineStr">
+        <is>
+          <t>85:36</t>
+        </is>
+      </c>
+      <c r="B401" s="10" t="inlineStr">
+        <is>
+          <t>[Question to Professor] The last part or one to three?</t>
+        </is>
+      </c>
+      <c r="C401" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D401" s="11" t="inlineStr"/>
+      <c r="E401" s="11" t="inlineStr"/>
+      <c r="F401" s="11" t="inlineStr"/>
+      <c r="G401" s="11" t="inlineStr"/>
+      <c r="H401" s="12" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="9" t="inlineStr">
+        <is>
+          <t>87:56</t>
+        </is>
+      </c>
+      <c r="B402" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] So, trial version.</t>
+        </is>
+      </c>
+      <c r="C402" s="11" t="inlineStr"/>
+      <c r="D402" s="11" t="inlineStr"/>
+      <c r="E402" s="11" t="inlineStr"/>
+      <c r="F402" s="11" t="inlineStr"/>
+      <c r="G402" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H402" s="12" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="9" t="inlineStr">
+        <is>
+          <t>87:57</t>
+        </is>
+      </c>
+      <c r="B403" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Hmm.</t>
+        </is>
+      </c>
+      <c r="C403" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D403" s="11" t="inlineStr"/>
+      <c r="E403" s="11" t="inlineStr"/>
+      <c r="F403" s="11" t="inlineStr"/>
+      <c r="G403" s="11" t="inlineStr"/>
+      <c r="H403" s="12" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="9" t="inlineStr">
+        <is>
+          <t>87:58</t>
+        </is>
+      </c>
+      <c r="B404" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Trial, trial version.</t>
+        </is>
+      </c>
+      <c r="C404" s="11" t="inlineStr"/>
+      <c r="D404" s="11" t="inlineStr"/>
+      <c r="E404" s="11" t="inlineStr"/>
+      <c r="F404" s="11" t="inlineStr"/>
+      <c r="G404" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H404" s="12" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="9" t="inlineStr">
+        <is>
+          <t>89:31</t>
+        </is>
+      </c>
+      <c r="B405" s="10" t="inlineStr">
+        <is>
+          <t>[Question to Professor] You said summer, meaning we continue the project in summer?</t>
+        </is>
+      </c>
+      <c r="C405" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D405" s="11" t="inlineStr"/>
+      <c r="E405" s="11" t="inlineStr"/>
+      <c r="F405" s="11" t="inlineStr"/>
+      <c r="G405" s="11" t="inlineStr"/>
+      <c r="H405" s="12" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="9" t="inlineStr">
+        <is>
+          <t>89:36</t>
+        </is>
+      </c>
+      <c r="B406" s="10" t="inlineStr">
+        <is>
+          <t>[Question to Professor] You think there's no rest vacation?</t>
+        </is>
+      </c>
+      <c r="C406" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D406" s="11" t="inlineStr"/>
+      <c r="E406" s="11" t="inlineStr"/>
+      <c r="F406" s="11" t="inlineStr"/>
+      <c r="G406" s="11" t="inlineStr"/>
+      <c r="H406" s="12" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="9" t="inlineStr">
+        <is>
+          <t>89:41</t>
+        </is>
+      </c>
+      <c r="B407" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] July, August.</t>
+        </is>
+      </c>
+      <c r="C407" s="11" t="inlineStr"/>
+      <c r="D407" s="11" t="inlineStr"/>
+      <c r="E407" s="11" t="inlineStr"/>
+      <c r="F407" s="11" t="inlineStr"/>
+      <c r="G407" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H407" s="12" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="9" t="inlineStr">
+        <is>
+          <t>89:49</t>
+        </is>
+      </c>
+      <c r="B408" s="10" t="inlineStr">
+        <is>
+          <t>[Question to Professor] Summer?</t>
+        </is>
+      </c>
+      <c r="C408" s="11" t="inlineStr"/>
+      <c r="D408" s="11" t="inlineStr"/>
+      <c r="E408" s="11" t="inlineStr"/>
+      <c r="F408" s="11" t="inlineStr"/>
+      <c r="G408" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H408" s="12" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="9" t="inlineStr">
+        <is>
+          <t>90:00</t>
+        </is>
+      </c>
+      <c r="B409" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] I forgot.</t>
+        </is>
+      </c>
+      <c r="C409" s="11" t="inlineStr"/>
+      <c r="D409" s="11" t="inlineStr"/>
+      <c r="E409" s="11" t="inlineStr"/>
+      <c r="F409" s="11" t="inlineStr"/>
+      <c r="G409" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H409" s="12" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="9" t="inlineStr">
+        <is>
+          <t>90:01</t>
+        </is>
+      </c>
+      <c r="B410" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Because for me I already buy the ticket to</t>
+        </is>
+      </c>
+      <c r="C410" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D410" s="11" t="inlineStr"/>
+      <c r="E410" s="11" t="inlineStr"/>
+      <c r="F410" s="11" t="inlineStr"/>
+      <c r="G410" s="11" t="inlineStr"/>
+      <c r="H410" s="12" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="9" t="inlineStr">
+        <is>
+          <t>90:03</t>
+        </is>
+      </c>
+      <c r="B411" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] I forgot.</t>
+        </is>
+      </c>
+      <c r="C411" s="11" t="inlineStr"/>
+      <c r="D411" s="11" t="inlineStr"/>
+      <c r="E411" s="11" t="inlineStr"/>
+      <c r="F411" s="11" t="inlineStr"/>
+      <c r="G411" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H411" s="12" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="9" t="inlineStr">
+        <is>
+          <t>90:05</t>
+        </is>
+      </c>
+      <c r="B412" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Because for me I already buy the ticket to</t>
+        </is>
+      </c>
+      <c r="C412" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D412" s="11" t="inlineStr"/>
+      <c r="E412" s="11" t="inlineStr"/>
+      <c r="F412" s="11" t="inlineStr"/>
+      <c r="G412" s="11" t="inlineStr"/>
+      <c r="H412" s="12" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="9" t="inlineStr">
+        <is>
+          <t>90:10</t>
+        </is>
+      </c>
+      <c r="B413" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] They know.</t>
+        </is>
+      </c>
+      <c r="C413" s="11" t="inlineStr"/>
+      <c r="D413" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E413" s="11" t="inlineStr"/>
+      <c r="F413" s="11" t="inlineStr"/>
+      <c r="G413" s="11" t="inlineStr"/>
+      <c r="H413" s="12" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="9" t="inlineStr">
+        <is>
+          <t>90:12</t>
+        </is>
+      </c>
+      <c r="B414" s="10" t="inlineStr">
+        <is>
+          <t>[Question to Professor] We we inform, right?</t>
+        </is>
+      </c>
+      <c r="C414" s="11" t="inlineStr"/>
+      <c r="D414" s="11" t="inlineStr"/>
+      <c r="E414" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F414" s="11" t="inlineStr"/>
+      <c r="G414" s="11" t="inlineStr"/>
+      <c r="H414" s="12" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="9" t="inlineStr">
+        <is>
+          <t>90:22</t>
+        </is>
+      </c>
+      <c r="B415" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] 20, 21 days.</t>
+        </is>
+      </c>
+      <c r="C415" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D415" s="11" t="inlineStr"/>
+      <c r="E415" s="11" t="inlineStr"/>
+      <c r="F415" s="11" t="inlineStr"/>
+      <c r="G415" s="11" t="inlineStr"/>
+      <c r="H415" s="12" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="9" t="inlineStr">
+        <is>
+          <t>90:24</t>
+        </is>
+      </c>
+      <c r="B416" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Outside of the country.</t>
+        </is>
+      </c>
+      <c r="C416" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D416" s="11" t="inlineStr"/>
+      <c r="E416" s="11" t="inlineStr"/>
+      <c r="F416" s="11" t="inlineStr"/>
+      <c r="G416" s="11" t="inlineStr"/>
+      <c r="H416" s="12" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="9" t="inlineStr">
+        <is>
+          <t>90:32</t>
+        </is>
+      </c>
+      <c r="B417" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Two weeks and two weeks.</t>
+        </is>
+      </c>
+      <c r="C417" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D417" s="11" t="inlineStr"/>
+      <c r="E417" s="11" t="inlineStr"/>
+      <c r="F417" s="11" t="inlineStr"/>
+      <c r="G417" s="11" t="inlineStr"/>
+      <c r="H417" s="12" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="9" t="inlineStr">
+        <is>
+          <t>90:38</t>
+        </is>
+      </c>
+      <c r="B418" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] No problem.</t>
+        </is>
+      </c>
+      <c r="C418" s="11" t="inlineStr"/>
+      <c r="D418" s="11" t="inlineStr"/>
+      <c r="E418" s="11" t="inlineStr"/>
+      <c r="F418" s="11" t="inlineStr"/>
+      <c r="G418" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H418" s="12" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="9" t="inlineStr">
+        <is>
+          <t>91:03</t>
+        </is>
+      </c>
+      <c r="B419" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Maybe just you give it myself, uh, because I planned uh to go with the higher boss during my visit in Indonesia.</t>
+        </is>
+      </c>
+      <c r="C419" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D419" s="11" t="inlineStr"/>
+      <c r="E419" s="11" t="inlineStr"/>
+      <c r="F419" s="11" t="inlineStr"/>
+      <c r="G419" s="11" t="inlineStr"/>
+      <c r="H419" s="12" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="9" t="inlineStr">
+        <is>
+          <t>92:54</t>
+        </is>
+      </c>
+      <c r="B420" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Five.</t>
+        </is>
+      </c>
+      <c r="C420" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D420" s="11" t="inlineStr"/>
+      <c r="E420" s="11" t="inlineStr"/>
+      <c r="F420" s="11" t="inlineStr"/>
+      <c r="G420" s="11" t="inlineStr"/>
+      <c r="H420" s="12" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="9" t="inlineStr">
+        <is>
+          <t>92:56</t>
+        </is>
+      </c>
+      <c r="B421" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] 10 minutes.</t>
+        </is>
+      </c>
+      <c r="C421" s="11" t="inlineStr"/>
+      <c r="D421" s="11" t="inlineStr"/>
+      <c r="E421" s="11" t="inlineStr"/>
+      <c r="F421" s="11" t="inlineStr"/>
+      <c r="G421" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H421" s="12" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="9" t="inlineStr">
+        <is>
+          <t>92:57</t>
+        </is>
+      </c>
+      <c r="B422" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] 10 minutes, okay.</t>
+        </is>
+      </c>
+      <c r="C422" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D422" s="11" t="inlineStr"/>
+      <c r="E422" s="11" t="inlineStr"/>
+      <c r="F422" s="11" t="inlineStr"/>
+      <c r="G422" s="11" t="inlineStr"/>
+      <c r="H422" s="12" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="9" t="inlineStr">
+        <is>
+          <t>92:58</t>
+        </is>
+      </c>
+      <c r="B423" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] That that that'll be good.</t>
+        </is>
+      </c>
+      <c r="C423" s="11" t="inlineStr"/>
+      <c r="D423" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E423" s="11" t="inlineStr"/>
+      <c r="F423" s="11" t="inlineStr"/>
+      <c r="G423" s="11" t="inlineStr"/>
+      <c r="H423" s="12" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="9" t="inlineStr">
+        <is>
+          <t>92:59</t>
+        </is>
+      </c>
+      <c r="B424" s="10" t="inlineStr">
+        <is>
+          <t>[Question to Professor] What are we doing?</t>
+        </is>
+      </c>
+      <c r="C424" s="11" t="inlineStr"/>
+      <c r="D424" s="11" t="inlineStr"/>
+      <c r="E424" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F424" s="11" t="inlineStr"/>
+      <c r="G424" s="11" t="inlineStr"/>
+      <c r="H424" s="12" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="B425" s="14" t="inlineStr">
         <is>
           <t>TOTAL (sum of scores)</t>
         </is>
       </c>
-      <c r="C305" s="15" t="n">
-        <v>314</v>
-      </c>
-      <c r="D305" s="15" t="n">
-        <v>70</v>
-      </c>
-      <c r="E305" s="15" t="n">
-        <v>75</v>
-      </c>
-      <c r="F305" s="15" t="n">
+      <c r="C425" s="15" t="n">
+        <v>410</v>
+      </c>
+      <c r="D425" s="15" t="n">
+        <v>165</v>
+      </c>
+      <c r="E425" s="15" t="n">
         <v>81</v>
       </c>
-      <c r="G305" s="15" t="n">
-        <v>166</v>
-      </c>
-      <c r="H305" s="16" t="n"/>
-    </row>
-    <row r="306">
-      <c r="B306" s="17" t="inlineStr">
+      <c r="F425" s="15" t="n">
+        <v>81</v>
+      </c>
+      <c r="G425" s="15" t="n">
+        <v>232</v>
+      </c>
+      <c r="H425" s="16" t="n"/>
+    </row>
+    <row r="426">
+      <c r="B426" s="17" t="inlineStr">
         <is>
           <t>Max possible (n_opp × 6)</t>
         </is>
       </c>
-      <c r="C306" s="18" t="n">
-        <v>540</v>
-      </c>
-      <c r="D306" s="18" t="n">
-        <v>114</v>
-      </c>
-      <c r="E306" s="18" t="n">
-        <v>138</v>
-      </c>
-      <c r="F306" s="18" t="n">
+      <c r="C426" s="18" t="n">
+        <v>708</v>
+      </c>
+      <c r="D426" s="18" t="n">
+        <v>294</v>
+      </c>
+      <c r="E426" s="18" t="n">
+        <v>150</v>
+      </c>
+      <c r="F426" s="18" t="n">
         <v>168</v>
       </c>
-      <c r="G306" s="18" t="n">
-        <v>312</v>
-      </c>
-      <c r="H306" s="12" t="n"/>
-    </row>
-    <row r="307">
-      <c r="B307" s="19" t="inlineStr">
+      <c r="G426" s="18" t="n">
+        <v>456</v>
+      </c>
+      <c r="H426" s="12" t="n"/>
+    </row>
+    <row r="427">
+      <c r="B427" s="19" t="inlineStr">
         <is>
           <t>% Grade (max 7.5%)</t>
         </is>
       </c>
-      <c r="C307" s="20" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="D307" s="20" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="E307" s="20" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="F307" s="20" t="n">
+      <c r="C427" s="20" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="D427" s="20" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="E427" s="20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F427" s="20" t="n">
         <v>3.62</v>
       </c>
-      <c r="G307" s="20" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="H307" s="21" t="n"/>
-    </row>
-    <row r="309">
-      <c r="A309" s="7" t="inlineStr">
+      <c r="G427" s="20" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="H427" s="21" t="n"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="7" t="inlineStr">
         <is>
           <t>RESUMEN COMPONENTE A — COMPARATIVA DOS ESCENARIOS</t>
         </is>
       </c>
     </row>
-    <row r="310">
-      <c r="A310" s="8" t="inlineStr">
+    <row r="430">
+      <c r="A430" s="8" t="inlineStr">
         <is>
           <t>Escenario A: literal del silabo (solo calidad promedio). Escenario B: igual + bonus por cantidad de contribuciones (5-14:+0.5  15-29:+1.0  30+:+1.5)</t>
         </is>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" s="4" t="inlineStr">
+    <row r="432">
+      <c r="A432" s="4" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
       </c>
-      <c r="B312" s="4" t="inlineStr">
+      <c r="B432" s="4" t="inlineStr">
         <is>
           <t>Prep (7.5)</t>
         </is>
       </c>
-      <c r="C312" s="4" t="inlineStr">
+      <c r="C432" s="4" t="inlineStr">
         <is>
           <t>Att (5)</t>
         </is>
       </c>
-      <c r="D312" s="4" t="inlineStr">
+      <c r="D432" s="4" t="inlineStr">
         <is>
           <t>─ Esc A ─</t>
         </is>
       </c>
-      <c r="E312" s="4" t="inlineStr">
+      <c r="E432" s="4" t="inlineStr">
         <is>
           <t>Part A</t>
         </is>
       </c>
-      <c r="F312" s="4" t="inlineStr">
+      <c r="F432" s="4" t="inlineStr">
         <is>
           <t>TOTAL A</t>
         </is>
       </c>
-      <c r="G312" s="4" t="inlineStr">
+      <c r="G432" s="4" t="inlineStr">
         <is>
           <t>% A</t>
         </is>
       </c>
-      <c r="H312" s="4" t="inlineStr">
+      <c r="H432" s="4" t="inlineStr">
         <is>
           <t>─ Esc B ─</t>
         </is>
       </c>
-      <c r="I312" s="4" t="inlineStr">
+      <c r="I432" s="4" t="inlineStr">
         <is>
           <t>Part B (+bonus)</t>
         </is>
       </c>
-      <c r="J312" s="4" t="inlineStr">
+      <c r="J432" s="4" t="inlineStr">
         <is>
           <t>TOTAL B</t>
         </is>
       </c>
-      <c r="K312" s="4" t="inlineStr">
+      <c r="K432" s="4" t="inlineStr">
         <is>
           <t>% B</t>
         </is>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" s="22" t="inlineStr">
+    <row r="433">
+      <c r="A433" s="22" t="inlineStr">
         <is>
           <t>Aryang</t>
         </is>
       </c>
-      <c r="B313" s="23" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="C313" s="23" t="n">
+      <c r="B433" s="23" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="C433" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="D313" s="9" t="inlineStr"/>
-      <c r="E313" s="23" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="F313" s="24" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="G313" s="25" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="H313" s="9" t="inlineStr"/>
-      <c r="I313" s="9" t="inlineStr">
-        <is>
-          <t>5.86 (+1.5)</t>
-        </is>
-      </c>
-      <c r="J313" s="20" t="n">
-        <v>14.05</v>
-      </c>
-      <c r="K313" s="25" t="n">
-        <v>70.2</v>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" s="22" t="inlineStr">
+      <c r="D433" s="9" t="inlineStr"/>
+      <c r="E433" s="23" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="F433" s="24" t="n">
+        <v>12.58</v>
+      </c>
+      <c r="G433" s="25" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="H433" s="9" t="inlineStr"/>
+      <c r="I433" s="9" t="inlineStr">
+        <is>
+          <t>5.84 (+1.5)</t>
+        </is>
+      </c>
+      <c r="J433" s="20" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="K433" s="25" t="n">
+        <v>70.40000000000001</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="22" t="inlineStr">
         <is>
           <t>Mega</t>
         </is>
       </c>
-      <c r="B314" s="23" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="C314" s="23" t="n">
+      <c r="B434" s="23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="C434" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="D314" s="9" t="inlineStr"/>
-      <c r="E314" s="23" t="n">
-        <v>4.61</v>
-      </c>
-      <c r="F314" s="24" t="n">
-        <v>12.47</v>
-      </c>
-      <c r="G314" s="25" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="H314" s="9" t="inlineStr"/>
-      <c r="I314" s="9" t="inlineStr">
-        <is>
-          <t>5.61 (+1.0)</t>
-        </is>
-      </c>
-      <c r="J314" s="20" t="n">
-        <v>13.47</v>
-      </c>
-      <c r="K314" s="25" t="n">
-        <v>67.3</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="22" t="inlineStr">
+      <c r="D434" s="9" t="inlineStr"/>
+      <c r="E434" s="23" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="F434" s="24" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="G434" s="25" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="H434" s="9" t="inlineStr"/>
+      <c r="I434" s="9" t="inlineStr">
+        <is>
+          <t>5.71 (+1.5)</t>
+        </is>
+      </c>
+      <c r="J434" s="20" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K434" s="25" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="22" t="inlineStr">
         <is>
           <t>Chilaka</t>
         </is>
       </c>
-      <c r="B315" s="23" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="C315" s="23" t="n">
+      <c r="B435" s="23" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C435" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="D315" s="9" t="inlineStr"/>
-      <c r="E315" s="23" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="F315" s="24" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="G315" s="25" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="H315" s="9" t="inlineStr"/>
-      <c r="I315" s="9" t="inlineStr">
-        <is>
-          <t>5.08 (+1.0)</t>
-        </is>
-      </c>
-      <c r="J315" s="20" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="K315" s="25" t="n">
-        <v>61.5</v>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" s="22" t="inlineStr">
+      <c r="D435" s="9" t="inlineStr"/>
+      <c r="E435" s="23" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="F435" s="24" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="G435" s="25" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="H435" s="9" t="inlineStr"/>
+      <c r="I435" s="9" t="inlineStr">
+        <is>
+          <t>5.05 (+1.0)</t>
+        </is>
+      </c>
+      <c r="J435" s="20" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="K435" s="25" t="n">
+        <v>61.6</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="22" t="inlineStr">
         <is>
           <t>Grace</t>
         </is>
       </c>
-      <c r="B316" s="23" t="n">
+      <c r="B436" s="23" t="n">
         <v>2.5</v>
       </c>
-      <c r="C316" s="23" t="n">
+      <c r="C436" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="D316" s="9" t="inlineStr"/>
-      <c r="E316" s="23" t="n">
+      <c r="D436" s="9" t="inlineStr"/>
+      <c r="E436" s="23" t="n">
         <v>3.62</v>
       </c>
-      <c r="F316" s="24" t="n">
+      <c r="F436" s="24" t="n">
         <v>11.12</v>
       </c>
-      <c r="G316" s="25" t="n">
+      <c r="G436" s="25" t="n">
         <v>55.6</v>
       </c>
-      <c r="H316" s="9" t="inlineStr"/>
-      <c r="I316" s="9" t="inlineStr">
+      <c r="H436" s="9" t="inlineStr"/>
+      <c r="I436" s="9" t="inlineStr">
         <is>
           <t>4.62 (+1.0)</t>
         </is>
       </c>
-      <c r="J316" s="20" t="n">
+      <c r="J436" s="20" t="n">
         <v>12.12</v>
       </c>
-      <c r="K316" s="25" t="n">
+      <c r="K436" s="25" t="n">
         <v>60.6</v>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" s="22" t="inlineStr">
+    <row r="437">
+      <c r="A437" s="22" t="inlineStr">
         <is>
           <t>Sthepen</t>
         </is>
       </c>
-      <c r="B317" s="23" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="C317" s="23" t="n">
+      <c r="B437" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C437" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="D317" s="9" t="inlineStr"/>
-      <c r="E317" s="23" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="F317" s="24" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="G317" s="25" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="H317" s="9" t="inlineStr"/>
-      <c r="I317" s="9" t="inlineStr">
-        <is>
-          <t>5.49 (+1.5)</t>
-        </is>
-      </c>
-      <c r="J317" s="20" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="K317" s="25" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="319">
-      <c r="A319" s="26" t="inlineStr">
+      <c r="D437" s="9" t="inlineStr"/>
+      <c r="E437" s="23" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="F437" s="24" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="G437" s="25" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="H437" s="9" t="inlineStr"/>
+      <c r="I437" s="9" t="inlineStr">
+        <is>
+          <t>5.32 (+1.5)</t>
+        </is>
+      </c>
+      <c r="J437" s="20" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="K437" s="25" t="n">
+        <v>66.59999999999999</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="26" t="inlineStr">
         <is>
           <t>🟡 Escenario A — apego literal al silabo</t>
         </is>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" s="27" t="inlineStr">
+    <row r="440">
+      <c r="A440" s="27" t="inlineStr">
         <is>
           <t>🟢 Escenario B — sugerido: reconoce engagement sin romper rúbrica</t>
         </is>
@@ -6837,13 +9211,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A309:J309"/>
-    <mergeCell ref="A90:I90"/>
+    <mergeCell ref="A430:J430"/>
     <mergeCell ref="A10:I10"/>
-    <mergeCell ref="A89:I89"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A310:J310"/>
     <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A126:I126"/>
+    <mergeCell ref="A429:J429"/>
+    <mergeCell ref="A125:I125"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/clases/2026-06-02/Component_A_2026-06-02.xlsx
+++ b/data/clases/2026-06-02/Component_A_2026-06-02.xlsx
@@ -578,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K440"/>
+  <dimension ref="A1:K492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2836,164 +2836,183 @@
       <c r="H120" s="12" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="B121" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL (sum of scores)</t>
-        </is>
-      </c>
-      <c r="C121" s="15" t="n">
-        <v>101</v>
-      </c>
-      <c r="D121" s="15" t="n">
-        <v>37</v>
-      </c>
-      <c r="E121" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="F121" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="G121" s="15" t="n">
-        <v>24</v>
-      </c>
-      <c r="H121" s="16" t="n"/>
+      <c r="A121" s="9" t="inlineStr">
+        <is>
+          <t>192:28</t>
+        </is>
+      </c>
+      <c r="B121" s="10" t="inlineStr">
+        <is>
+          <t>Yeah, but you guys Am I your robot? (open)</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr"/>
+      <c r="D121" s="11" t="inlineStr"/>
+      <c r="E121" s="11" t="inlineStr"/>
+      <c r="F121" s="11" t="inlineStr"/>
+      <c r="G121" s="11" t="inlineStr"/>
+      <c r="H121" s="12" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="B122" s="17" t="inlineStr">
-        <is>
-          <t>Max possible (n_opp × 6)</t>
-        </is>
-      </c>
-      <c r="C122" s="18" t="n">
-        <v>234</v>
-      </c>
-      <c r="D122" s="18" t="n">
-        <v>96</v>
-      </c>
-      <c r="E122" s="18" t="n">
-        <v>66</v>
-      </c>
-      <c r="F122" s="18" t="n">
-        <v>36</v>
-      </c>
-      <c r="G122" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="H122" s="12" t="n"/>
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>192:36</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>Great. If you solved them? (open)</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr"/>
+      <c r="D122" s="11" t="inlineStr"/>
+      <c r="E122" s="11" t="inlineStr"/>
+      <c r="F122" s="11" t="inlineStr"/>
+      <c r="G122" s="11" t="inlineStr"/>
+      <c r="H122" s="12" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="B123" s="19" t="inlineStr">
-        <is>
-          <t>% Grade (max 7.5%)</t>
-        </is>
-      </c>
-      <c r="C123" s="20" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="D123" s="20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E123" s="20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="F123" s="20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G123" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="H123" s="21" t="n"/>
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>100:48</t>
+        </is>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>Could you use somebody else? → Sthepen</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr"/>
+      <c r="D123" s="11" t="inlineStr"/>
+      <c r="E123" s="11" t="inlineStr"/>
+      <c r="F123" s="11" t="inlineStr"/>
+      <c r="G123" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H123" s="12" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>101:22</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>You know 90-60-90, Mega? → Mega</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr"/>
+      <c r="D124" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="11" t="inlineStr"/>
+      <c r="F124" s="11" t="inlineStr"/>
+      <c r="G124" s="11" t="inlineStr"/>
+      <c r="H124" s="12" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="7" t="inlineStr">
-        <is>
-          <t>PARTICIPATION (7.5%) — Questions from Student / Voluntary</t>
-        </is>
-      </c>
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>102:14</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
+        <is>
+          <t>Right? (open)</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr"/>
+      <c r="D125" s="11" t="inlineStr"/>
+      <c r="E125" s="11" t="inlineStr"/>
+      <c r="F125" s="11" t="inlineStr"/>
+      <c r="G125" s="11" t="inlineStr"/>
+      <c r="H125" s="12" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="8" t="inlineStr">
-        <is>
-          <t>Pregunta del alumno o comentario voluntario: 1–6 · Otros alumnos en esa fila: N/A</t>
-        </is>
-      </c>
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>102:14</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>So, as developing countries, do we have to keep referencing on, on just 80, 80, 80 because it's difficult to become 90-60-90? (open)</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr"/>
+      <c r="D126" s="11" t="inlineStr"/>
+      <c r="E126" s="11" t="inlineStr"/>
+      <c r="F126" s="11" t="inlineStr"/>
+      <c r="G126" s="11" t="inlineStr"/>
+      <c r="H126" s="12" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>103:01</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="inlineStr">
+        <is>
+          <t>But what are these 90-60-90s? (open)</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr"/>
+      <c r="D127" s="11" t="inlineStr"/>
+      <c r="E127" s="11" t="inlineStr"/>
+      <c r="F127" s="11" t="inlineStr"/>
+      <c r="G127" s="11" t="inlineStr"/>
+      <c r="H127" s="12" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="4" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
-        <is>
-          <t>Contribution</t>
-        </is>
-      </c>
-      <c r="C128" s="4" t="inlineStr">
-        <is>
-          <t>Aryang</t>
-        </is>
-      </c>
-      <c r="D128" s="4" t="inlineStr">
-        <is>
-          <t>Mega</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>Chilaka</t>
-        </is>
-      </c>
-      <c r="F128" s="4" t="inlineStr">
-        <is>
-          <t>Grace</t>
-        </is>
-      </c>
-      <c r="G128" s="4" t="inlineStr">
-        <is>
-          <t>Sthepen</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>Notes / Feedback</t>
-        </is>
-      </c>
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>103:03</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>What is the guys to really, really match the best beauty standards, the best NID safe standards, right? (open)</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr"/>
+      <c r="D128" s="11" t="inlineStr"/>
+      <c r="E128" s="11" t="inlineStr"/>
+      <c r="F128" s="11" t="inlineStr"/>
+      <c r="G128" s="11" t="inlineStr"/>
+      <c r="H128" s="12" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>02:41</t>
+          <t>103:10</t>
         </is>
       </c>
       <c r="B129" s="10" t="inlineStr">
         <is>
-          <t>[Comment] presents and</t>
+          <t>What did these guys do? (open)</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr"/>
       <c r="D129" s="11" t="inlineStr"/>
       <c r="E129" s="11" t="inlineStr"/>
-      <c r="F129" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F129" s="11" t="inlineStr"/>
       <c r="G129" s="11" t="inlineStr"/>
       <c r="H129" s="12" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>03:21</t>
+          <t>105:34</t>
         </is>
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Actually, they uh, they replied, they are available after 11, right?</t>
-        </is>
-      </c>
-      <c r="C130" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>Make sense? (open)</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr"/>
       <c r="D130" s="11" t="inlineStr"/>
       <c r="E130" s="11" t="inlineStr"/>
       <c r="F130" s="11" t="inlineStr"/>
@@ -3003,56 +3022,54 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>03:25</t>
+          <t>111:05</t>
         </is>
       </c>
       <c r="B131" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah.</t>
-        </is>
-      </c>
-      <c r="C131" s="11" t="inlineStr"/>
+          <t>So yeah, but then there is no electricity and so what? (open)</t>
+        </is>
+      </c>
+      <c r="C131" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D131" s="11" t="inlineStr"/>
       <c r="E131" s="11" t="inlineStr"/>
-      <c r="F131" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F131" s="11" t="inlineStr"/>
       <c r="G131" s="11" t="inlineStr"/>
       <c r="H131" s="12" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>03:26</t>
+          <t>111:20</t>
         </is>
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Next month Monday.</t>
+          <t>But are they willing to pay for it? Are they able to pay for it? Is there a model to give them or is there a subsidy to There is no electricity because either there is no demand, or there is no demand who can pay for it. (open)</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr"/>
       <c r="D132" s="11" t="inlineStr"/>
       <c r="E132" s="11" t="inlineStr"/>
-      <c r="F132" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F132" s="11" t="inlineStr"/>
       <c r="G132" s="11" t="inlineStr"/>
       <c r="H132" s="12" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>03:34</t>
+          <t>130:05</t>
         </is>
       </c>
       <c r="B133" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I think yeah.</t>
+          <t>But I'm gonna do a different topic for my master's. Right? (open)</t>
         </is>
       </c>
       <c r="C133" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D133" s="11" t="inlineStr"/>
       <c r="E133" s="11" t="inlineStr"/>
@@ -3063,17 +3080,15 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>03:50</t>
+          <t>132:10</t>
         </is>
       </c>
       <c r="B134" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So 11:15 to 11 to 12 to 1:15.</t>
-        </is>
-      </c>
-      <c r="C134" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>Okay? (open)</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr"/>
       <c r="D134" s="11" t="inlineStr"/>
       <c r="E134" s="11" t="inlineStr"/>
       <c r="F134" s="11" t="inlineStr"/>
@@ -3081,201 +3096,166 @@
       <c r="H134" s="12" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>03:57</t>
-        </is>
-      </c>
-      <c r="B135" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] Lunchtime.</t>
-        </is>
-      </c>
-      <c r="C135" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D135" s="11" t="inlineStr"/>
-      <c r="E135" s="11" t="inlineStr"/>
-      <c r="F135" s="11" t="inlineStr"/>
-      <c r="G135" s="11" t="inlineStr"/>
-      <c r="H135" s="12" t="inlineStr"/>
+      <c r="B135" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL (sum of scores)</t>
+        </is>
+      </c>
+      <c r="C135" s="15" t="n">
+        <v>107</v>
+      </c>
+      <c r="D135" s="15" t="n">
+        <v>37</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F135" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G135" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="H135" s="16" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="9" t="inlineStr">
-        <is>
-          <t>03:58</t>
-        </is>
-      </c>
-      <c r="B136" s="10" t="inlineStr">
-        <is>
-          <t>[Voluntary Response] No, no. No lunchtime.</t>
-        </is>
-      </c>
-      <c r="C136" s="11" t="inlineStr"/>
-      <c r="D136" s="11" t="inlineStr"/>
-      <c r="E136" s="11" t="inlineStr"/>
-      <c r="F136" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G136" s="11" t="inlineStr"/>
-      <c r="H136" s="12" t="inlineStr"/>
+      <c r="B136" s="17" t="inlineStr">
+        <is>
+          <t>Max possible (n_opp × 6)</t>
+        </is>
+      </c>
+      <c r="C136" s="18" t="n">
+        <v>246</v>
+      </c>
+      <c r="D136" s="18" t="n">
+        <v>102</v>
+      </c>
+      <c r="E136" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="F136" s="18" t="n">
+        <v>36</v>
+      </c>
+      <c r="G136" s="18" t="n">
+        <v>66</v>
+      </c>
+      <c r="H136" s="12" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="inlineStr">
-        <is>
-          <t>03:59</t>
-        </is>
-      </c>
-      <c r="B137" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] Oh, really?</t>
-        </is>
-      </c>
-      <c r="C137" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D137" s="11" t="inlineStr"/>
-      <c r="E137" s="11" t="inlineStr"/>
-      <c r="F137" s="11" t="inlineStr"/>
-      <c r="G137" s="11" t="inlineStr"/>
-      <c r="H137" s="12" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="9" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="B138" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] Whoa, whoa, whoa, whoa.</t>
-        </is>
-      </c>
-      <c r="C138" s="11" t="inlineStr"/>
-      <c r="D138" s="11" t="inlineStr"/>
-      <c r="E138" s="11" t="inlineStr"/>
-      <c r="F138" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G138" s="11" t="inlineStr"/>
-      <c r="H138" s="12" t="inlineStr"/>
+      <c r="B137" s="19" t="inlineStr">
+        <is>
+          <t>% Grade (max 7.5%)</t>
+        </is>
+      </c>
+      <c r="C137" s="20" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="D137" s="20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="E137" s="20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F137" s="20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G137" s="20" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="H137" s="21" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="9" t="inlineStr">
-        <is>
-          <t>04:11</t>
-        </is>
-      </c>
-      <c r="B139" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] Same, yeah.</t>
-        </is>
-      </c>
-      <c r="C139" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D139" s="11" t="inlineStr"/>
-      <c r="E139" s="11" t="inlineStr"/>
-      <c r="F139" s="11" t="inlineStr"/>
-      <c r="G139" s="11" t="inlineStr"/>
-      <c r="H139" s="12" t="inlineStr"/>
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>PARTICIPATION (7.5%) — Questions from Student / Voluntary</t>
+        </is>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="9" t="inlineStr">
-        <is>
-          <t>05:10</t>
-        </is>
-      </c>
-      <c r="B140" s="10" t="inlineStr">
-        <is>
-          <t>[Voluntary Response] Uh, I can go.</t>
-        </is>
-      </c>
-      <c r="C140" s="11" t="inlineStr"/>
-      <c r="D140" s="11" t="inlineStr"/>
-      <c r="E140" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F140" s="11" t="inlineStr"/>
-      <c r="G140" s="11" t="inlineStr"/>
-      <c r="H140" s="12" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="9" t="inlineStr">
-        <is>
-          <t>05:12</t>
-        </is>
-      </c>
-      <c r="B141" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] I, I want to talk about the stage one. I, I, I, I really understood it.</t>
-        </is>
-      </c>
-      <c r="C141" s="11" t="inlineStr"/>
-      <c r="D141" s="11" t="inlineStr"/>
-      <c r="E141" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F141" s="11" t="inlineStr"/>
-      <c r="G141" s="11" t="inlineStr"/>
-      <c r="H141" s="12" t="inlineStr"/>
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>Pregunta del alumno o comentario voluntario: 1–6 · Otros alumnos en esa fila: N/A</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="9" t="inlineStr">
-        <is>
-          <t>05:14</t>
-        </is>
-      </c>
-      <c r="B142" s="10" t="inlineStr">
-        <is>
-          <t>[Comment] Um, for me, this is like my first time coming across.</t>
-        </is>
-      </c>
-      <c r="C142" s="11" t="inlineStr"/>
-      <c r="D142" s="11" t="inlineStr"/>
-      <c r="E142" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F142" s="11" t="inlineStr"/>
-      <c r="G142" s="11" t="inlineStr"/>
-      <c r="H142" s="12" t="inlineStr"/>
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>Contribution</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>Aryang</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>Mega</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>Chilaka</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>Sthepen</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>Notes / Feedback</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>05:16</t>
+          <t>02:41</t>
         </is>
       </c>
       <c r="B143" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because I've heard about project management, but in this form,</t>
+          <t>[Comment] presents and</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr"/>
       <c r="D143" s="11" t="inlineStr"/>
-      <c r="E143" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="F143" s="11" t="inlineStr"/>
+      <c r="E143" s="11" t="inlineStr"/>
+      <c r="F143" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="G143" s="11" t="inlineStr"/>
       <c r="H143" s="12" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>05:18</t>
+          <t>03:21</t>
         </is>
       </c>
       <c r="B144" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I've not really done anything with it, especially with the 5 Ys.</t>
-        </is>
-      </c>
-      <c r="C144" s="11" t="inlineStr"/>
+          <t>[Question to Professor] Actually, they uh, they replied, they are available after 11, right?</t>
+        </is>
+      </c>
+      <c r="C144" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D144" s="11" t="inlineStr"/>
-      <c r="E144" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E144" s="11" t="inlineStr"/>
       <c r="F144" s="11" t="inlineStr"/>
       <c r="G144" s="11" t="inlineStr"/>
       <c r="H144" s="12" t="inlineStr"/>
@@ -3283,59 +3263,59 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>05:20</t>
+          <t>03:25</t>
         </is>
       </c>
       <c r="B145" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So it actually, it made me understand a lot about</t>
+          <t>[Comment] Yeah.</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr"/>
       <c r="D145" s="11" t="inlineStr"/>
-      <c r="E145" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F145" s="11" t="inlineStr"/>
+      <c r="E145" s="11" t="inlineStr"/>
+      <c r="F145" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="G145" s="11" t="inlineStr"/>
       <c r="H145" s="12" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>05:22</t>
+          <t>03:26</t>
         </is>
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>[Comment] the project I was working on, you know, prior to coming for this class.</t>
+          <t>[Comment] Next month Monday.</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr"/>
       <c r="D146" s="11" t="inlineStr"/>
-      <c r="E146" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F146" s="11" t="inlineStr"/>
+      <c r="E146" s="11" t="inlineStr"/>
+      <c r="F146" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="G146" s="11" t="inlineStr"/>
       <c r="H146" s="12" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>05:24</t>
+          <t>03:34</t>
         </is>
       </c>
       <c r="B147" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because I've always struggled.</t>
-        </is>
-      </c>
-      <c r="C147" s="11" t="inlineStr"/>
+          <t>[Comment] I think yeah.</t>
+        </is>
+      </c>
+      <c r="C147" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D147" s="11" t="inlineStr"/>
-      <c r="E147" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E147" s="11" t="inlineStr"/>
       <c r="F147" s="11" t="inlineStr"/>
       <c r="G147" s="11" t="inlineStr"/>
       <c r="H147" s="12" t="inlineStr"/>
@@ -3343,19 +3323,19 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>05:25</t>
+          <t>03:50</t>
         </is>
       </c>
       <c r="B148" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I said, Oh, why is it that this project is having this issue?</t>
-        </is>
-      </c>
-      <c r="C148" s="11" t="inlineStr"/>
+          <t>[Comment] So 11:15 to 11 to 12 to 1:15.</t>
+        </is>
+      </c>
+      <c r="C148" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D148" s="11" t="inlineStr"/>
-      <c r="E148" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E148" s="11" t="inlineStr"/>
       <c r="F148" s="11" t="inlineStr"/>
       <c r="G148" s="11" t="inlineStr"/>
       <c r="H148" s="12" t="inlineStr"/>
@@ -3363,19 +3343,19 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>05:27</t>
+          <t>03:57</t>
         </is>
       </c>
       <c r="B149" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Oh, why is it that we need to carry out this thing?</t>
-        </is>
-      </c>
-      <c r="C149" s="11" t="inlineStr"/>
+          <t>[Comment] Lunchtime.</t>
+        </is>
+      </c>
+      <c r="C149" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D149" s="11" t="inlineStr"/>
-      <c r="E149" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E149" s="11" t="inlineStr"/>
       <c r="F149" s="11" t="inlineStr"/>
       <c r="G149" s="11" t="inlineStr"/>
       <c r="H149" s="12" t="inlineStr"/>
@@ -3383,39 +3363,39 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>05:29</t>
+          <t>03:58</t>
         </is>
       </c>
       <c r="B150" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, for the 5 Ys, it gave me a depth into understanding what I'm doing.</t>
+          <t>[Voluntary Response] No, no. No lunchtime.</t>
         </is>
       </c>
       <c r="C150" s="11" t="inlineStr"/>
       <c r="D150" s="11" t="inlineStr"/>
-      <c r="E150" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F150" s="11" t="inlineStr"/>
+      <c r="E150" s="11" t="inlineStr"/>
+      <c r="F150" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="G150" s="11" t="inlineStr"/>
       <c r="H150" s="12" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>05:32</t>
+          <t>03:59</t>
         </is>
       </c>
       <c r="B151" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So it's something that I would always like to put into practice.</t>
-        </is>
-      </c>
-      <c r="C151" s="11" t="inlineStr"/>
+          <t>[Comment] Oh, really?</t>
+        </is>
+      </c>
+      <c r="C151" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D151" s="11" t="inlineStr"/>
-      <c r="E151" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E151" s="11" t="inlineStr"/>
       <c r="F151" s="11" t="inlineStr"/>
       <c r="G151" s="11" t="inlineStr"/>
       <c r="H151" s="12" t="inlineStr"/>
@@ -3423,39 +3403,39 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>05:34</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="B152" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because, um, I have so many ideas,</t>
+          <t>[Comment] Whoa, whoa, whoa, whoa.</t>
         </is>
       </c>
       <c r="C152" s="11" t="inlineStr"/>
       <c r="D152" s="11" t="inlineStr"/>
-      <c r="E152" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F152" s="11" t="inlineStr"/>
+      <c r="E152" s="11" t="inlineStr"/>
+      <c r="F152" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="G152" s="11" t="inlineStr"/>
       <c r="H152" s="12" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>05:36</t>
+          <t>04:11</t>
         </is>
       </c>
       <c r="B153" s="10" t="inlineStr">
         <is>
-          <t>[Comment] but I just need to define them. Define the problem, define everything.</t>
-        </is>
-      </c>
-      <c r="C153" s="11" t="inlineStr"/>
+          <t>[Comment] Same, yeah.</t>
+        </is>
+      </c>
+      <c r="C153" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D153" s="11" t="inlineStr"/>
-      <c r="E153" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E153" s="11" t="inlineStr"/>
       <c r="F153" s="11" t="inlineStr"/>
       <c r="G153" s="11" t="inlineStr"/>
       <c r="H153" s="12" t="inlineStr"/>
@@ -3463,18 +3443,18 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>05:39</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="B154" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, that was really helpful for me.</t>
+          <t>[Voluntary Response] Uh, I can go.</t>
         </is>
       </c>
       <c r="C154" s="11" t="inlineStr"/>
       <c r="D154" s="11" t="inlineStr"/>
       <c r="E154" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F154" s="11" t="inlineStr"/>
       <c r="G154" s="11" t="inlineStr"/>
@@ -3483,18 +3463,18 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>05:42</t>
+          <t>05:12</t>
         </is>
       </c>
       <c r="B155" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah.</t>
+          <t>[Comment] I, I want to talk about the stage one. I, I, I, I really understood it.</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr"/>
       <c r="D155" s="11" t="inlineStr"/>
       <c r="E155" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F155" s="11" t="inlineStr"/>
       <c r="G155" s="11" t="inlineStr"/>
@@ -3503,292 +3483,292 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>05:52</t>
+          <t>05:14</t>
         </is>
       </c>
       <c r="B156" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I can go.</t>
+          <t>[Comment] Um, for me, this is like my first time coming across.</t>
         </is>
       </c>
       <c r="C156" s="11" t="inlineStr"/>
       <c r="D156" s="11" t="inlineStr"/>
-      <c r="E156" s="11" t="inlineStr"/>
-      <c r="F156" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E156" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F156" s="11" t="inlineStr"/>
       <c r="G156" s="11" t="inlineStr"/>
       <c r="H156" s="12" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>05:53</t>
+          <t>05:16</t>
         </is>
       </c>
       <c r="B157" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Okay.</t>
+          <t>[Comment] Because I've heard about project management, but in this form,</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr"/>
       <c r="D157" s="11" t="inlineStr"/>
-      <c r="E157" s="11" t="inlineStr"/>
-      <c r="F157" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E157" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F157" s="11" t="inlineStr"/>
       <c r="G157" s="11" t="inlineStr"/>
       <c r="H157" s="12" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>05:54</t>
+          <t>05:18</t>
         </is>
       </c>
       <c r="B158" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, I'll go with the first stage.</t>
+          <t>[Comment] I've not really done anything with it, especially with the 5 Ys.</t>
         </is>
       </c>
       <c r="C158" s="11" t="inlineStr"/>
       <c r="D158" s="11" t="inlineStr"/>
-      <c r="E158" s="11" t="inlineStr"/>
-      <c r="F158" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="E158" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F158" s="11" t="inlineStr"/>
       <c r="G158" s="11" t="inlineStr"/>
       <c r="H158" s="12" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>05:20</t>
         </is>
       </c>
       <c r="B159" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Um, for me, the first stage, the 5 Ys</t>
+          <t>[Comment] So it actually, it made me understand a lot about</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr"/>
       <c r="D159" s="11" t="inlineStr"/>
-      <c r="E159" s="11" t="inlineStr"/>
-      <c r="F159" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="E159" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F159" s="11" t="inlineStr"/>
       <c r="G159" s="11" t="inlineStr"/>
       <c r="H159" s="12" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>05:57</t>
+          <t>05:22</t>
         </is>
       </c>
       <c r="B160" s="10" t="inlineStr">
         <is>
-          <t>[Comment] was actually an eye opener, and the SMART goals.</t>
+          <t>[Comment] the project I was working on, you know, prior to coming for this class.</t>
         </is>
       </c>
       <c r="C160" s="11" t="inlineStr"/>
       <c r="D160" s="11" t="inlineStr"/>
-      <c r="E160" s="11" t="inlineStr"/>
-      <c r="F160" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="E160" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F160" s="11" t="inlineStr"/>
       <c r="G160" s="11" t="inlineStr"/>
       <c r="H160" s="12" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>05:59</t>
+          <t>05:24</t>
         </is>
       </c>
       <c r="B161" s="10" t="inlineStr">
         <is>
-          <t>[Comment] It made me realize that some of the goals I had before were not SMART goals.</t>
+          <t>[Comment] Because I've always struggled.</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr"/>
       <c r="D161" s="11" t="inlineStr"/>
-      <c r="E161" s="11" t="inlineStr"/>
-      <c r="F161" s="9" t="n">
+      <c r="E161" s="9" t="n">
         <v>4</v>
       </c>
+      <c r="F161" s="11" t="inlineStr"/>
       <c r="G161" s="11" t="inlineStr"/>
       <c r="H161" s="12" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>05:25</t>
         </is>
       </c>
       <c r="B162" s="10" t="inlineStr">
         <is>
-          <t>[Comment] They were just goals.</t>
+          <t>[Comment] I said, Oh, why is it that this project is having this issue?</t>
         </is>
       </c>
       <c r="C162" s="11" t="inlineStr"/>
       <c r="D162" s="11" t="inlineStr"/>
-      <c r="E162" s="11" t="inlineStr"/>
-      <c r="F162" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="E162" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F162" s="11" t="inlineStr"/>
       <c r="G162" s="11" t="inlineStr"/>
       <c r="H162" s="12" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>06:03</t>
+          <t>05:27</t>
         </is>
       </c>
       <c r="B163" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And it also made me realize that some of my projects,</t>
+          <t>[Comment] Oh, why is it that we need to carry out this thing?</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr"/>
       <c r="D163" s="11" t="inlineStr"/>
-      <c r="E163" s="11" t="inlineStr"/>
-      <c r="F163" s="9" t="n">
+      <c r="E163" s="9" t="n">
         <v>4</v>
       </c>
+      <c r="F163" s="11" t="inlineStr"/>
       <c r="G163" s="11" t="inlineStr"/>
       <c r="H163" s="12" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>05:29</t>
         </is>
       </c>
       <c r="B164" s="10" t="inlineStr">
         <is>
-          <t>[Comment] they don't really have a long-term goal for them.</t>
+          <t>[Comment] So, for the 5 Ys, it gave me a depth into understanding what I'm doing.</t>
         </is>
       </c>
       <c r="C164" s="11" t="inlineStr"/>
       <c r="D164" s="11" t="inlineStr"/>
-      <c r="E164" s="11" t="inlineStr"/>
-      <c r="F164" s="9" t="n">
+      <c r="E164" s="9" t="n">
         <v>4</v>
       </c>
+      <c r="F164" s="11" t="inlineStr"/>
       <c r="G164" s="11" t="inlineStr"/>
       <c r="H164" s="12" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>06:07</t>
+          <t>05:32</t>
         </is>
       </c>
       <c r="B165" s="10" t="inlineStr">
         <is>
-          <t>[Comment] It was just, Okay, I'm working on this.</t>
+          <t>[Comment] So it's something that I would always like to put into practice.</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr"/>
       <c r="D165" s="11" t="inlineStr"/>
-      <c r="E165" s="11" t="inlineStr"/>
-      <c r="F165" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="E165" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F165" s="11" t="inlineStr"/>
       <c r="G165" s="11" t="inlineStr"/>
       <c r="H165" s="12" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>06:09</t>
+          <t>05:34</t>
         </is>
       </c>
       <c r="B166" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I just want to like, achieve this, and then that's it.</t>
+          <t>[Comment] Because, um, I have so many ideas,</t>
         </is>
       </c>
       <c r="C166" s="11" t="inlineStr"/>
       <c r="D166" s="11" t="inlineStr"/>
-      <c r="E166" s="11" t="inlineStr"/>
-      <c r="F166" s="9" t="n">
+      <c r="E166" s="9" t="n">
         <v>4</v>
       </c>
+      <c r="F166" s="11" t="inlineStr"/>
       <c r="G166" s="11" t="inlineStr"/>
       <c r="H166" s="12" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>05:36</t>
         </is>
       </c>
       <c r="B167" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, the 5 Ys helped me to like, understand</t>
+          <t>[Comment] but I just need to define them. Define the problem, define everything.</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr"/>
       <c r="D167" s="11" t="inlineStr"/>
-      <c r="E167" s="11" t="inlineStr"/>
-      <c r="F167" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="E167" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F167" s="11" t="inlineStr"/>
       <c r="G167" s="11" t="inlineStr"/>
       <c r="H167" s="12" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>06:14</t>
+          <t>05:39</t>
         </is>
       </c>
       <c r="B168" s="10" t="inlineStr">
         <is>
-          <t>[Comment] that I needed to go deeper into the why of the project.</t>
+          <t>[Comment] So, that was really helpful for me.</t>
         </is>
       </c>
       <c r="C168" s="11" t="inlineStr"/>
       <c r="D168" s="11" t="inlineStr"/>
-      <c r="E168" s="11" t="inlineStr"/>
-      <c r="F168" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E168" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F168" s="11" t="inlineStr"/>
       <c r="G168" s="11" t="inlineStr"/>
       <c r="H168" s="12" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>06:17</t>
+          <t>05:42</t>
         </is>
       </c>
       <c r="B169" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And also with the SMART goals, I needed to make sure that my goals</t>
+          <t>[Voluntary Response] Yeah.</t>
         </is>
       </c>
       <c r="C169" s="11" t="inlineStr"/>
       <c r="D169" s="11" t="inlineStr"/>
-      <c r="E169" s="11" t="inlineStr"/>
-      <c r="F169" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="E169" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" s="11" t="inlineStr"/>
       <c r="G169" s="11" t="inlineStr"/>
       <c r="H169" s="12" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>05:52</t>
         </is>
       </c>
       <c r="B170" s="10" t="inlineStr">
         <is>
-          <t>[Comment] are SMART goals.</t>
+          <t>[Voluntary Response] I can go.</t>
         </is>
       </c>
       <c r="C170" s="11" t="inlineStr"/>
@@ -3803,19 +3783,19 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>05:53</t>
         </is>
       </c>
       <c r="B171" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, that for me, was a really good takeaway from the first stage.</t>
+          <t>[Comment] Okay.</t>
         </is>
       </c>
       <c r="C171" s="11" t="inlineStr"/>
       <c r="D171" s="11" t="inlineStr"/>
       <c r="E171" s="11" t="inlineStr"/>
       <c r="F171" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G171" s="11" t="inlineStr"/>
       <c r="H171" s="12" t="inlineStr"/>
@@ -3823,292 +3803,292 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>05:54</t>
         </is>
       </c>
       <c r="B172" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I can go.</t>
+          <t>[Comment] So, I'll go with the first stage.</t>
         </is>
       </c>
       <c r="C172" s="11" t="inlineStr"/>
       <c r="D172" s="11" t="inlineStr"/>
       <c r="E172" s="11" t="inlineStr"/>
-      <c r="F172" s="11" t="inlineStr"/>
-      <c r="G172" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F172" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G172" s="11" t="inlineStr"/>
       <c r="H172" s="12" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>06:46</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="B173" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah.</t>
+          <t>[Comment] Um, for me, the first stage, the 5 Ys</t>
         </is>
       </c>
       <c r="C173" s="11" t="inlineStr"/>
       <c r="D173" s="11" t="inlineStr"/>
       <c r="E173" s="11" t="inlineStr"/>
-      <c r="F173" s="11" t="inlineStr"/>
-      <c r="G173" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F173" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G173" s="11" t="inlineStr"/>
       <c r="H173" s="12" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>06:47</t>
+          <t>05:57</t>
         </is>
       </c>
       <c r="B174" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Okay.</t>
+          <t>[Comment] was actually an eye opener, and the SMART goals.</t>
         </is>
       </c>
       <c r="C174" s="11" t="inlineStr"/>
       <c r="D174" s="11" t="inlineStr"/>
       <c r="E174" s="11" t="inlineStr"/>
-      <c r="F174" s="11" t="inlineStr"/>
-      <c r="G174" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F174" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G174" s="11" t="inlineStr"/>
       <c r="H174" s="12" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>06:47</t>
+          <t>05:59</t>
         </is>
       </c>
       <c r="B175" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, for the homework review, uh, I think this first stage one has been an eye-opener.</t>
+          <t>[Comment] It made me realize that some of the goals I had before were not SMART goals.</t>
         </is>
       </c>
       <c r="C175" s="11" t="inlineStr"/>
       <c r="D175" s="11" t="inlineStr"/>
       <c r="E175" s="11" t="inlineStr"/>
-      <c r="F175" s="11" t="inlineStr"/>
-      <c r="G175" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="F175" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G175" s="11" t="inlineStr"/>
       <c r="H175" s="12" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="B176" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh, especially the 5 Ys and the SMART goals.</t>
+          <t>[Comment] They were just goals.</t>
         </is>
       </c>
       <c r="C176" s="11" t="inlineStr"/>
       <c r="D176" s="11" t="inlineStr"/>
       <c r="E176" s="11" t="inlineStr"/>
-      <c r="F176" s="11" t="inlineStr"/>
-      <c r="G176" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F176" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G176" s="11" t="inlineStr"/>
       <c r="H176" s="12" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>06:52</t>
+          <t>06:03</t>
         </is>
       </c>
       <c r="B177" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And what I really liked about it is how we had to connect them.</t>
+          <t>[Comment] And it also made me realize that some of my projects,</t>
         </is>
       </c>
       <c r="C177" s="11" t="inlineStr"/>
       <c r="D177" s="11" t="inlineStr"/>
       <c r="E177" s="11" t="inlineStr"/>
-      <c r="F177" s="11" t="inlineStr"/>
-      <c r="G177" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="F177" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G177" s="11" t="inlineStr"/>
       <c r="H177" s="12" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="B178" s="10" t="inlineStr">
         <is>
-          <t>[Comment] The problem statement,</t>
+          <t>[Comment] they don't really have a long-term goal for them.</t>
         </is>
       </c>
       <c r="C178" s="11" t="inlineStr"/>
       <c r="D178" s="11" t="inlineStr"/>
       <c r="E178" s="11" t="inlineStr"/>
-      <c r="F178" s="11" t="inlineStr"/>
-      <c r="G178" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F178" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G178" s="11" t="inlineStr"/>
       <c r="H178" s="12" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:07</t>
         </is>
       </c>
       <c r="B179" s="10" t="inlineStr">
         <is>
-          <t>[Comment] and then use the 5 Ys to dig deeper to find the root causes.</t>
+          <t>[Comment] It was just, Okay, I'm working on this.</t>
         </is>
       </c>
       <c r="C179" s="11" t="inlineStr"/>
       <c r="D179" s="11" t="inlineStr"/>
       <c r="E179" s="11" t="inlineStr"/>
-      <c r="F179" s="11" t="inlineStr"/>
-      <c r="G179" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="F179" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G179" s="11" t="inlineStr"/>
       <c r="H179" s="12" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>06:58</t>
+          <t>06:09</t>
         </is>
       </c>
       <c r="B180" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And from the root causes, then you come up with the objectives,</t>
+          <t>[Comment] I just want to like, achieve this, and then that's it.</t>
         </is>
       </c>
       <c r="C180" s="11" t="inlineStr"/>
       <c r="D180" s="11" t="inlineStr"/>
       <c r="E180" s="11" t="inlineStr"/>
-      <c r="F180" s="11" t="inlineStr"/>
-      <c r="G180" s="9" t="n">
+      <c r="F180" s="9" t="n">
         <v>4</v>
       </c>
+      <c r="G180" s="11" t="inlineStr"/>
       <c r="H180" s="12" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="B181" s="10" t="inlineStr">
         <is>
-          <t>[Comment] and then using the SMART goals for the objectives.</t>
+          <t>[Comment] So, the 5 Ys helped me to like, understand</t>
         </is>
       </c>
       <c r="C181" s="11" t="inlineStr"/>
       <c r="D181" s="11" t="inlineStr"/>
       <c r="E181" s="11" t="inlineStr"/>
-      <c r="F181" s="11" t="inlineStr"/>
-      <c r="G181" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F181" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G181" s="11" t="inlineStr"/>
       <c r="H181" s="12" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:14</t>
         </is>
       </c>
       <c r="B182" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, it was really a flow.</t>
+          <t>[Comment] that I needed to go deeper into the why of the project.</t>
         </is>
       </c>
       <c r="C182" s="11" t="inlineStr"/>
       <c r="D182" s="11" t="inlineStr"/>
       <c r="E182" s="11" t="inlineStr"/>
-      <c r="F182" s="11" t="inlineStr"/>
-      <c r="G182" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F182" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G182" s="11" t="inlineStr"/>
       <c r="H182" s="12" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>07:03</t>
+          <t>06:17</t>
         </is>
       </c>
       <c r="B183" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And it, it helped me understand that a project is not just</t>
+          <t>[Comment] And also with the SMART goals, I needed to make sure that my goals</t>
         </is>
       </c>
       <c r="C183" s="11" t="inlineStr"/>
       <c r="D183" s="11" t="inlineStr"/>
       <c r="E183" s="11" t="inlineStr"/>
-      <c r="F183" s="11" t="inlineStr"/>
-      <c r="G183" s="9" t="n">
+      <c r="F183" s="9" t="n">
         <v>4</v>
       </c>
+      <c r="G183" s="11" t="inlineStr"/>
       <c r="H183" s="12" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="B184" s="10" t="inlineStr">
         <is>
-          <t>[Comment] something you just get up and say, Oh, I want to do this, then you go do it.</t>
+          <t>[Comment] are SMART goals.</t>
         </is>
       </c>
       <c r="C184" s="11" t="inlineStr"/>
       <c r="D184" s="11" t="inlineStr"/>
       <c r="E184" s="11" t="inlineStr"/>
-      <c r="F184" s="11" t="inlineStr"/>
-      <c r="G184" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="F184" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G184" s="11" t="inlineStr"/>
       <c r="H184" s="12" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>07:08</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="B185" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh, there's always a proper process.</t>
+          <t>[Comment] So, that for me, was a really good takeaway from the first stage.</t>
         </is>
       </c>
       <c r="C185" s="11" t="inlineStr"/>
       <c r="D185" s="11" t="inlineStr"/>
       <c r="E185" s="11" t="inlineStr"/>
-      <c r="F185" s="11" t="inlineStr"/>
-      <c r="G185" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F185" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G185" s="11" t="inlineStr"/>
       <c r="H185" s="12" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>07:09</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And that's why they say planning is very important.</t>
+          <t>[Voluntary Response] I can go.</t>
         </is>
       </c>
       <c r="C186" s="11" t="inlineStr"/>
@@ -4116,19 +4096,19 @@
       <c r="E186" s="11" t="inlineStr"/>
       <c r="F186" s="11" t="inlineStr"/>
       <c r="G186" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H186" s="12" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:46</t>
         </is>
       </c>
       <c r="B187" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because you would have to define your problem correctly,</t>
+          <t>[Comment] Yeah.</t>
         </is>
       </c>
       <c r="C187" s="11" t="inlineStr"/>
@@ -4136,19 +4116,19 @@
       <c r="E187" s="11" t="inlineStr"/>
       <c r="F187" s="11" t="inlineStr"/>
       <c r="G187" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H187" s="12" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>07:13</t>
+          <t>06:47</t>
         </is>
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>[Comment] define your root causes correctly.</t>
+          <t>[Comment] Okay.</t>
         </is>
       </c>
       <c r="C188" s="11" t="inlineStr"/>
@@ -4156,19 +4136,19 @@
       <c r="E188" s="11" t="inlineStr"/>
       <c r="F188" s="11" t="inlineStr"/>
       <c r="G188" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H188" s="12" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>06:47</t>
         </is>
       </c>
       <c r="B189" s="10" t="inlineStr">
         <is>
-          <t>[Comment] From there, you would have your objectives.</t>
+          <t>[Comment] So, for the homework review, uh, I think this first stage one has been an eye-opener.</t>
         </is>
       </c>
       <c r="C189" s="11" t="inlineStr"/>
@@ -4176,19 +4156,19 @@
       <c r="E189" s="11" t="inlineStr"/>
       <c r="F189" s="11" t="inlineStr"/>
       <c r="G189" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H189" s="12" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>07:17</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And with the objectives,</t>
+          <t>[Comment] Uh, especially the 5 Ys and the SMART goals.</t>
         </is>
       </c>
       <c r="C190" s="11" t="inlineStr"/>
@@ -4203,12 +4183,12 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:52</t>
         </is>
       </c>
       <c r="B191" s="10" t="inlineStr">
         <is>
-          <t>[Comment] you can now use your SMART goals for each objective.</t>
+          <t>[Comment] And what I really liked about it is how we had to connect them.</t>
         </is>
       </c>
       <c r="C191" s="11" t="inlineStr"/>
@@ -4216,19 +4196,19 @@
       <c r="E191" s="11" t="inlineStr"/>
       <c r="F191" s="11" t="inlineStr"/>
       <c r="G191" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H191" s="12" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="B192" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, this part of the stage one, it's very important.</t>
+          <t>[Comment] The problem statement,</t>
         </is>
       </c>
       <c r="C192" s="11" t="inlineStr"/>
@@ -4236,19 +4216,19 @@
       <c r="E192" s="11" t="inlineStr"/>
       <c r="F192" s="11" t="inlineStr"/>
       <c r="G192" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H192" s="12" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="B193" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And it's something I definitely will apply to my projects.</t>
+          <t>[Comment] and then use the 5 Ys to dig deeper to find the root causes.</t>
         </is>
       </c>
       <c r="C193" s="11" t="inlineStr"/>
@@ -4263,298 +4243,298 @@
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>06:58</t>
         </is>
       </c>
       <c r="B194" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I can go.</t>
-        </is>
-      </c>
-      <c r="C194" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Comment] And from the root causes, then you come up with the objectives,</t>
+        </is>
+      </c>
+      <c r="C194" s="11" t="inlineStr"/>
       <c r="D194" s="11" t="inlineStr"/>
       <c r="E194" s="11" t="inlineStr"/>
       <c r="F194" s="11" t="inlineStr"/>
-      <c r="G194" s="11" t="inlineStr"/>
+      <c r="G194" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H194" s="12" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="B195" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh.</t>
-        </is>
-      </c>
-      <c r="C195" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Comment] and then using the SMART goals for the objectives.</t>
+        </is>
+      </c>
+      <c r="C195" s="11" t="inlineStr"/>
       <c r="D195" s="11" t="inlineStr"/>
       <c r="E195" s="11" t="inlineStr"/>
       <c r="F195" s="11" t="inlineStr"/>
-      <c r="G195" s="11" t="inlineStr"/>
+      <c r="G195" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H195" s="12" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="B196" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Actually, I also have similar opinions.</t>
-        </is>
-      </c>
-      <c r="C196" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] So, it was really a flow.</t>
+        </is>
+      </c>
+      <c r="C196" s="11" t="inlineStr"/>
       <c r="D196" s="11" t="inlineStr"/>
       <c r="E196" s="11" t="inlineStr"/>
       <c r="F196" s="11" t="inlineStr"/>
-      <c r="G196" s="11" t="inlineStr"/>
+      <c r="G196" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H196" s="12" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:03</t>
         </is>
       </c>
       <c r="B197" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Um, I think stage one also is really interesting to me.</t>
-        </is>
-      </c>
-      <c r="C197" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] And it, it helped me understand that a project is not just</t>
+        </is>
+      </c>
+      <c r="C197" s="11" t="inlineStr"/>
       <c r="D197" s="11" t="inlineStr"/>
       <c r="E197" s="11" t="inlineStr"/>
       <c r="F197" s="11" t="inlineStr"/>
-      <c r="G197" s="11" t="inlineStr"/>
+      <c r="G197" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H197" s="12" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And I can actually, uh, apply these things.</t>
-        </is>
-      </c>
-      <c r="C198" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] something you just get up and say, Oh, I want to do this, then you go do it.</t>
+        </is>
+      </c>
+      <c r="C198" s="11" t="inlineStr"/>
       <c r="D198" s="11" t="inlineStr"/>
       <c r="E198" s="11" t="inlineStr"/>
       <c r="F198" s="11" t="inlineStr"/>
-      <c r="G198" s="11" t="inlineStr"/>
+      <c r="G198" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H198" s="12" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:08</t>
         </is>
       </c>
       <c r="B199" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Like, in the future, if I want to have my own project.</t>
-        </is>
-      </c>
-      <c r="C199" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] Uh, there's always a proper process.</t>
+        </is>
+      </c>
+      <c r="C199" s="11" t="inlineStr"/>
       <c r="D199" s="11" t="inlineStr"/>
       <c r="E199" s="11" t="inlineStr"/>
       <c r="F199" s="11" t="inlineStr"/>
-      <c r="G199" s="11" t="inlineStr"/>
+      <c r="G199" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H199" s="12" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>07:58</t>
+          <t>07:09</t>
         </is>
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Or also in my working experience, like in the next job.</t>
-        </is>
-      </c>
-      <c r="C200" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] And that's why they say planning is very important.</t>
+        </is>
+      </c>
+      <c r="C200" s="11" t="inlineStr"/>
       <c r="D200" s="11" t="inlineStr"/>
       <c r="E200" s="11" t="inlineStr"/>
       <c r="F200" s="11" t="inlineStr"/>
-      <c r="G200" s="11" t="inlineStr"/>
+      <c r="G200" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="H200" s="12" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="B201" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I can use these things to improve my projects.</t>
-        </is>
-      </c>
-      <c r="C201" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] Because you would have to define your problem correctly,</t>
+        </is>
+      </c>
+      <c r="C201" s="11" t="inlineStr"/>
       <c r="D201" s="11" t="inlineStr"/>
       <c r="E201" s="11" t="inlineStr"/>
       <c r="F201" s="11" t="inlineStr"/>
-      <c r="G201" s="11" t="inlineStr"/>
+      <c r="G201" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H201" s="12" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Um, for example, the project that I want to apply to my country,</t>
-        </is>
-      </c>
-      <c r="C202" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] define your root causes correctly.</t>
+        </is>
+      </c>
+      <c r="C202" s="11" t="inlineStr"/>
       <c r="D202" s="11" t="inlineStr"/>
       <c r="E202" s="11" t="inlineStr"/>
       <c r="F202" s="11" t="inlineStr"/>
-      <c r="G202" s="11" t="inlineStr"/>
+      <c r="G202" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H202" s="12" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="B203" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I actually, before I only have a little bit of idea.</t>
-        </is>
-      </c>
-      <c r="C203" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] From there, you would have your objectives.</t>
+        </is>
+      </c>
+      <c r="C203" s="11" t="inlineStr"/>
       <c r="D203" s="11" t="inlineStr"/>
       <c r="E203" s="11" t="inlineStr"/>
       <c r="F203" s="11" t="inlineStr"/>
-      <c r="G203" s="11" t="inlineStr"/>
+      <c r="G203" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H203" s="12" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="B204" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But with the 5 Ys and the SMART goals,</t>
-        </is>
-      </c>
-      <c r="C204" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] And with the objectives,</t>
+        </is>
+      </c>
+      <c r="C204" s="11" t="inlineStr"/>
       <c r="D204" s="11" t="inlineStr"/>
       <c r="E204" s="11" t="inlineStr"/>
       <c r="F204" s="11" t="inlineStr"/>
-      <c r="G204" s="11" t="inlineStr"/>
+      <c r="G204" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H204" s="12" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="B205" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I can actually, like, build it systematically.</t>
-        </is>
-      </c>
-      <c r="C205" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] you can now use your SMART goals for each objective.</t>
+        </is>
+      </c>
+      <c r="C205" s="11" t="inlineStr"/>
       <c r="D205" s="11" t="inlineStr"/>
       <c r="E205" s="11" t="inlineStr"/>
       <c r="F205" s="11" t="inlineStr"/>
-      <c r="G205" s="11" t="inlineStr"/>
+      <c r="G205" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H205" s="12" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="B206" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Um, so it's not just a big idea,</t>
-        </is>
-      </c>
-      <c r="C206" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] So, this part of the stage one, it's very important.</t>
+        </is>
+      </c>
+      <c r="C206" s="11" t="inlineStr"/>
       <c r="D206" s="11" t="inlineStr"/>
       <c r="E206" s="11" t="inlineStr"/>
       <c r="F206" s="11" t="inlineStr"/>
-      <c r="G206" s="11" t="inlineStr"/>
+      <c r="G206" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H206" s="12" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="B207" s="10" t="inlineStr">
         <is>
-          <t>[Comment] but something that I can actually apply to my country.</t>
-        </is>
-      </c>
-      <c r="C207" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] And it's something I definitely will apply to my projects.</t>
+        </is>
+      </c>
+      <c r="C207" s="11" t="inlineStr"/>
       <c r="D207" s="11" t="inlineStr"/>
       <c r="E207" s="11" t="inlineStr"/>
       <c r="F207" s="11" t="inlineStr"/>
-      <c r="G207" s="11" t="inlineStr"/>
+      <c r="G207" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H207" s="12" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>07:49</t>
         </is>
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I'll go next.</t>
-        </is>
-      </c>
-      <c r="C208" s="11" t="inlineStr"/>
-      <c r="D208" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Voluntary Response] I can go.</t>
+        </is>
+      </c>
+      <c r="C208" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D208" s="11" t="inlineStr"/>
       <c r="E208" s="11" t="inlineStr"/>
       <c r="F208" s="11" t="inlineStr"/>
       <c r="G208" s="11" t="inlineStr"/>
@@ -4563,18 +4543,18 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="B209" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah.</t>
-        </is>
-      </c>
-      <c r="C209" s="11" t="inlineStr"/>
-      <c r="D209" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Comment] Uh.</t>
+        </is>
+      </c>
+      <c r="C209" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D209" s="11" t="inlineStr"/>
       <c r="E209" s="11" t="inlineStr"/>
       <c r="F209" s="11" t="inlineStr"/>
       <c r="G209" s="11" t="inlineStr"/>
@@ -4583,18 +4563,18 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh, for me, I think the important things are to understand the problem.</t>
-        </is>
-      </c>
-      <c r="C210" s="11" t="inlineStr"/>
-      <c r="D210" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] Actually, I also have similar opinions.</t>
+        </is>
+      </c>
+      <c r="C210" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D210" s="11" t="inlineStr"/>
       <c r="E210" s="11" t="inlineStr"/>
       <c r="F210" s="11" t="inlineStr"/>
       <c r="G210" s="11" t="inlineStr"/>
@@ -4603,18 +4583,18 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="B211" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And the reason why we need to understand the problem,</t>
-        </is>
-      </c>
-      <c r="C211" s="11" t="inlineStr"/>
-      <c r="D211" s="9" t="n">
+          <t>[Comment] Um, I think stage one also is really interesting to me.</t>
+        </is>
+      </c>
+      <c r="C211" s="9" t="n">
         <v>5</v>
       </c>
+      <c r="D211" s="11" t="inlineStr"/>
       <c r="E211" s="11" t="inlineStr"/>
       <c r="F211" s="11" t="inlineStr"/>
       <c r="G211" s="11" t="inlineStr"/>
@@ -4623,18 +4603,18 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>[Comment] and what we want to solve.</t>
-        </is>
-      </c>
-      <c r="C212" s="11" t="inlineStr"/>
-      <c r="D212" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] And I can actually, uh, apply these things.</t>
+        </is>
+      </c>
+      <c r="C212" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D212" s="11" t="inlineStr"/>
       <c r="E212" s="11" t="inlineStr"/>
       <c r="F212" s="11" t="inlineStr"/>
       <c r="G212" s="11" t="inlineStr"/>
@@ -4643,18 +4623,18 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="B213" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh, so, the 5 Ys</t>
-        </is>
-      </c>
-      <c r="C213" s="11" t="inlineStr"/>
-      <c r="D213" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] Like, in the future, if I want to have my own project.</t>
+        </is>
+      </c>
+      <c r="C213" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D213" s="11" t="inlineStr"/>
       <c r="E213" s="11" t="inlineStr"/>
       <c r="F213" s="11" t="inlineStr"/>
       <c r="G213" s="11" t="inlineStr"/>
@@ -4663,18 +4643,18 @@
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>[Comment] and the problem statement,</t>
-        </is>
-      </c>
-      <c r="C214" s="11" t="inlineStr"/>
-      <c r="D214" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] Or also in my working experience, like in the next job.</t>
+        </is>
+      </c>
+      <c r="C214" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D214" s="11" t="inlineStr"/>
       <c r="E214" s="11" t="inlineStr"/>
       <c r="F214" s="11" t="inlineStr"/>
       <c r="G214" s="11" t="inlineStr"/>
@@ -4683,18 +4663,18 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B215" s="10" t="inlineStr">
         <is>
-          <t>[Comment] uh, it's very important to ensure that the project is realistic,</t>
-        </is>
-      </c>
-      <c r="C215" s="11" t="inlineStr"/>
-      <c r="D215" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] I can use these things to improve my projects.</t>
+        </is>
+      </c>
+      <c r="C215" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D215" s="11" t="inlineStr"/>
       <c r="E215" s="11" t="inlineStr"/>
       <c r="F215" s="11" t="inlineStr"/>
       <c r="G215" s="11" t="inlineStr"/>
@@ -4703,18 +4683,18 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>[Comment] and also to, to make sure that the project is measurable.</t>
-        </is>
-      </c>
-      <c r="C216" s="11" t="inlineStr"/>
-      <c r="D216" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] Um, for example, the project that I want to apply to my country,</t>
+        </is>
+      </c>
+      <c r="C216" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D216" s="11" t="inlineStr"/>
       <c r="E216" s="11" t="inlineStr"/>
       <c r="F216" s="11" t="inlineStr"/>
       <c r="G216" s="11" t="inlineStr"/>
@@ -4723,18 +4703,18 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="B217" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because if it's not measurable, we can't really assess if we achieve our goals.</t>
-        </is>
-      </c>
-      <c r="C217" s="11" t="inlineStr"/>
-      <c r="D217" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] I actually, before I only have a little bit of idea.</t>
+        </is>
+      </c>
+      <c r="C217" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D217" s="11" t="inlineStr"/>
       <c r="E217" s="11" t="inlineStr"/>
       <c r="F217" s="11" t="inlineStr"/>
       <c r="G217" s="11" t="inlineStr"/>
@@ -4743,18 +4723,18 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And also the main problem that we want to address.</t>
-        </is>
-      </c>
-      <c r="C218" s="11" t="inlineStr"/>
-      <c r="D218" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] But with the 5 Ys and the SMART goals,</t>
+        </is>
+      </c>
+      <c r="C218" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D218" s="11" t="inlineStr"/>
       <c r="E218" s="11" t="inlineStr"/>
       <c r="F218" s="11" t="inlineStr"/>
       <c r="G218" s="11" t="inlineStr"/>
@@ -4763,18 +4743,18 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="B219" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, for me, the 5 Ys is actually very practical and helpful.</t>
-        </is>
-      </c>
-      <c r="C219" s="11" t="inlineStr"/>
-      <c r="D219" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] I can actually, like, build it systematically.</t>
+        </is>
+      </c>
+      <c r="C219" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D219" s="11" t="inlineStr"/>
       <c r="E219" s="11" t="inlineStr"/>
       <c r="F219" s="11" t="inlineStr"/>
       <c r="G219" s="11" t="inlineStr"/>
@@ -4783,18 +4763,18 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So I think I can use this in the future as well.</t>
-        </is>
-      </c>
-      <c r="C220" s="11" t="inlineStr"/>
-      <c r="D220" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] Um, so it's not just a big idea,</t>
+        </is>
+      </c>
+      <c r="C220" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D220" s="11" t="inlineStr"/>
       <c r="E220" s="11" t="inlineStr"/>
       <c r="F220" s="11" t="inlineStr"/>
       <c r="G220" s="11" t="inlineStr"/>
@@ -4803,19 +4783,19 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="B221" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Very useful.</t>
-        </is>
-      </c>
-      <c r="C221" s="11" t="inlineStr"/>
+          <t>[Comment] but something that I can actually apply to my country.</t>
+        </is>
+      </c>
+      <c r="C221" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D221" s="11" t="inlineStr"/>
-      <c r="E221" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E221" s="11" t="inlineStr"/>
       <c r="F221" s="11" t="inlineStr"/>
       <c r="G221" s="11" t="inlineStr"/>
       <c r="H221" s="12" t="inlineStr"/>
@@ -4823,39 +4803,39 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Very useful.</t>
+          <t>[Voluntary Response] I'll go next.</t>
         </is>
       </c>
       <c r="C222" s="11" t="inlineStr"/>
-      <c r="D222" s="11" t="inlineStr"/>
+      <c r="D222" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="E222" s="11" t="inlineStr"/>
-      <c r="F222" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F222" s="11" t="inlineStr"/>
       <c r="G222" s="11" t="inlineStr"/>
       <c r="H222" s="12" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="B223" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Thank you.</t>
+          <t>[Comment] Yeah.</t>
         </is>
       </c>
       <c r="C223" s="11" t="inlineStr"/>
-      <c r="D223" s="11" t="inlineStr"/>
-      <c r="E223" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="D223" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E223" s="11" t="inlineStr"/>
       <c r="F223" s="11" t="inlineStr"/>
       <c r="G223" s="11" t="inlineStr"/>
       <c r="H223" s="12" t="inlineStr"/>
@@ -4863,18 +4843,18 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Thank you.</t>
-        </is>
-      </c>
-      <c r="C224" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D224" s="11" t="inlineStr"/>
+          <t>[Comment] Uh, for me, I think the important things are to understand the problem.</t>
+        </is>
+      </c>
+      <c r="C224" s="11" t="inlineStr"/>
+      <c r="D224" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E224" s="11" t="inlineStr"/>
       <c r="F224" s="11" t="inlineStr"/>
       <c r="G224" s="11" t="inlineStr"/>
@@ -4883,52 +4863,52 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="B225" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Thank you, Professor.</t>
+          <t>[Comment] And the reason why we need to understand the problem,</t>
         </is>
       </c>
       <c r="C225" s="11" t="inlineStr"/>
-      <c r="D225" s="11" t="inlineStr"/>
+      <c r="D225" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E225" s="11" t="inlineStr"/>
       <c r="F225" s="11" t="inlineStr"/>
-      <c r="G225" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G225" s="11" t="inlineStr"/>
       <c r="H225" s="12" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Thank you, Professor.</t>
+          <t>[Comment] and what we want to solve.</t>
         </is>
       </c>
       <c r="C226" s="11" t="inlineStr"/>
-      <c r="D226" s="11" t="inlineStr"/>
+      <c r="D226" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E226" s="11" t="inlineStr"/>
-      <c r="F226" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F226" s="11" t="inlineStr"/>
       <c r="G226" s="11" t="inlineStr"/>
       <c r="H226" s="12" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="B227" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Thank you, ma'am.</t>
+          <t>[Comment] Uh, so, the 5 Ys</t>
         </is>
       </c>
       <c r="C227" s="11" t="inlineStr"/>
@@ -4943,98 +4923,98 @@
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah, yeah.</t>
+          <t>[Comment] and the problem statement,</t>
         </is>
       </c>
       <c r="C228" s="11" t="inlineStr"/>
-      <c r="D228" s="11" t="inlineStr"/>
+      <c r="D228" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E228" s="11" t="inlineStr"/>
       <c r="F228" s="11" t="inlineStr"/>
-      <c r="G228" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G228" s="11" t="inlineStr"/>
       <c r="H228" s="12" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="9" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="B229" s="10" t="inlineStr">
         <is>
-          <t>[Comment] They're doing so much in Nigeria right now.</t>
+          <t>[Comment] uh, it's very important to ensure that the project is realistic,</t>
         </is>
       </c>
       <c r="C229" s="11" t="inlineStr"/>
-      <c r="D229" s="11" t="inlineStr"/>
+      <c r="D229" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="E229" s="11" t="inlineStr"/>
       <c r="F229" s="11" t="inlineStr"/>
-      <c r="G229" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G229" s="11" t="inlineStr"/>
       <c r="H229" s="12" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="9" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>[Comment] That's from Korea.</t>
+          <t>[Comment] and also to, to make sure that the project is measurable.</t>
         </is>
       </c>
       <c r="C230" s="11" t="inlineStr"/>
-      <c r="D230" s="11" t="inlineStr"/>
+      <c r="D230" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="E230" s="11" t="inlineStr"/>
       <c r="F230" s="11" t="inlineStr"/>
-      <c r="G230" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G230" s="11" t="inlineStr"/>
       <c r="H230" s="12" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="B231" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] The company has to be like 10 years in the [inaudible].</t>
+          <t>[Comment] Because if it's not measurable, we can't really assess if we achieve our goals.</t>
         </is>
       </c>
       <c r="C231" s="11" t="inlineStr"/>
-      <c r="D231" s="11" t="inlineStr"/>
+      <c r="D231" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E231" s="11" t="inlineStr"/>
       <c r="F231" s="11" t="inlineStr"/>
-      <c r="G231" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="G231" s="11" t="inlineStr"/>
       <c r="H231" s="12" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="9" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Ah, okay. So, so we cannot [inaudible].</t>
-        </is>
-      </c>
-      <c r="C232" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D232" s="11" t="inlineStr"/>
+          <t>[Comment] And also the main problem that we want to address.</t>
+        </is>
+      </c>
+      <c r="C232" s="11" t="inlineStr"/>
+      <c r="D232" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="E232" s="11" t="inlineStr"/>
       <c r="F232" s="11" t="inlineStr"/>
       <c r="G232" s="11" t="inlineStr"/>
@@ -5043,18 +5023,18 @@
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="B233" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I see.</t>
-        </is>
-      </c>
-      <c r="C233" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D233" s="11" t="inlineStr"/>
+          <t>[Comment] So, for me, the 5 Ys is actually very practical and helpful.</t>
+        </is>
+      </c>
+      <c r="C233" s="11" t="inlineStr"/>
+      <c r="D233" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="E233" s="11" t="inlineStr"/>
       <c r="F233" s="11" t="inlineStr"/>
       <c r="G233" s="11" t="inlineStr"/>
@@ -5063,18 +5043,18 @@
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="B234" s="10" t="inlineStr">
         <is>
-          <t>[Comment] His son. Is that Hong?</t>
-        </is>
-      </c>
-      <c r="C234" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D234" s="11" t="inlineStr"/>
+          <t>[Comment] So I think I can use this in the future as well.</t>
+        </is>
+      </c>
+      <c r="C234" s="11" t="inlineStr"/>
+      <c r="D234" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E234" s="11" t="inlineStr"/>
       <c r="F234" s="11" t="inlineStr"/>
       <c r="G234" s="11" t="inlineStr"/>
@@ -5083,19 +5063,19 @@
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="B235" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But from what he's saying, he said he's not them that sends the invitation that I they don't have any business with sending the invitation. No Nypa. The Ministry of Foreign Affairs and the Ministry of Science and Technology.</t>
-        </is>
-      </c>
-      <c r="C235" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Voluntary Response] Very useful.</t>
+        </is>
+      </c>
+      <c r="C235" s="11" t="inlineStr"/>
       <c r="D235" s="11" t="inlineStr"/>
-      <c r="E235" s="11" t="inlineStr"/>
+      <c r="E235" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F235" s="11" t="inlineStr"/>
       <c r="G235" s="11" t="inlineStr"/>
       <c r="H235" s="12" t="inlineStr"/>
@@ -5103,39 +5083,39 @@
     <row r="236">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="B236" s="10" t="inlineStr">
         <is>
-          <t>[Comment] They said it's not even Science and Technology or Nypa.</t>
-        </is>
-      </c>
-      <c r="C236" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Voluntary Response] Very useful.</t>
+        </is>
+      </c>
+      <c r="C236" s="11" t="inlineStr"/>
       <c r="D236" s="11" t="inlineStr"/>
       <c r="E236" s="11" t="inlineStr"/>
-      <c r="F236" s="11" t="inlineStr"/>
+      <c r="F236" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="G236" s="11" t="inlineStr"/>
       <c r="H236" s="12" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="B237" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because I'm I'm supposed to meet him and Professor next month on the 22nd.</t>
-        </is>
-      </c>
-      <c r="C237" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] Thank you.</t>
+        </is>
+      </c>
+      <c r="C237" s="11" t="inlineStr"/>
       <c r="D237" s="11" t="inlineStr"/>
-      <c r="E237" s="11" t="inlineStr"/>
+      <c r="E237" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F237" s="11" t="inlineStr"/>
       <c r="G237" s="11" t="inlineStr"/>
       <c r="H237" s="12" t="inlineStr"/>
@@ -5143,16 +5123,16 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="B238" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So he said it's part of the I think is initiated from our home countries. That is normally sent to Ministry of Finance, not even Science and Technology.</t>
+          <t>[Comment] Thank you.</t>
         </is>
       </c>
       <c r="C238" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D238" s="11" t="inlineStr"/>
       <c r="E238" s="11" t="inlineStr"/>
@@ -5163,58 +5143,58 @@
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>17:29</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="B239" s="10" t="inlineStr">
         <is>
-          <t>[Comment] They they might not even know when they send.</t>
-        </is>
-      </c>
-      <c r="C239" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] Thank you, Professor.</t>
+        </is>
+      </c>
+      <c r="C239" s="11" t="inlineStr"/>
       <c r="D239" s="11" t="inlineStr"/>
       <c r="E239" s="11" t="inlineStr"/>
       <c r="F239" s="11" t="inlineStr"/>
-      <c r="G239" s="11" t="inlineStr"/>
+      <c r="G239" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H239" s="12" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>[Comment] African Development Bank. And it's in partnership with Ministry of Finance of Korea. That they they normally send it to Ministry of Finance of the of the other countries.</t>
-        </is>
-      </c>
-      <c r="C240" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] Thank you, Professor.</t>
+        </is>
+      </c>
+      <c r="C240" s="11" t="inlineStr"/>
       <c r="D240" s="11" t="inlineStr"/>
       <c r="E240" s="11" t="inlineStr"/>
-      <c r="F240" s="11" t="inlineStr"/>
+      <c r="F240" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="G240" s="11" t="inlineStr"/>
       <c r="H240" s="12" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="B241" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Gido. right?</t>
-        </is>
-      </c>
-      <c r="C241" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D241" s="11" t="inlineStr"/>
+          <t>[Comment] Thank you, ma'am.</t>
+        </is>
+      </c>
+      <c r="C241" s="11" t="inlineStr"/>
+      <c r="D241" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E241" s="11" t="inlineStr"/>
       <c r="F241" s="11" t="inlineStr"/>
       <c r="G241" s="11" t="inlineStr"/>
@@ -5223,96 +5203,96 @@
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>[Comment] around September or so.</t>
-        </is>
-      </c>
-      <c r="C242" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Voluntary Response] Yeah, yeah.</t>
+        </is>
+      </c>
+      <c r="C242" s="11" t="inlineStr"/>
       <c r="D242" s="11" t="inlineStr"/>
       <c r="E242" s="11" t="inlineStr"/>
       <c r="F242" s="11" t="inlineStr"/>
-      <c r="G242" s="11" t="inlineStr"/>
+      <c r="G242" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H242" s="12" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="B243" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I think it's July.</t>
-        </is>
-      </c>
-      <c r="C243" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] They're doing so much in Nigeria right now.</t>
+        </is>
+      </c>
+      <c r="C243" s="11" t="inlineStr"/>
       <c r="D243" s="11" t="inlineStr"/>
       <c r="E243" s="11" t="inlineStr"/>
       <c r="F243" s="11" t="inlineStr"/>
-      <c r="G243" s="11" t="inlineStr"/>
+      <c r="G243" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H243" s="12" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] I think it's July.</t>
-        </is>
-      </c>
-      <c r="C244" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] That's from Korea.</t>
+        </is>
+      </c>
+      <c r="C244" s="11" t="inlineStr"/>
       <c r="D244" s="11" t="inlineStr"/>
       <c r="E244" s="11" t="inlineStr"/>
       <c r="F244" s="11" t="inlineStr"/>
-      <c r="G244" s="11" t="inlineStr"/>
+      <c r="G244" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H244" s="12" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="B245" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I I Yeah.</t>
-        </is>
-      </c>
-      <c r="C245" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Question to Professor] The company has to be like 10 years in the [inaudible].</t>
+        </is>
+      </c>
+      <c r="C245" s="11" t="inlineStr"/>
       <c r="D245" s="11" t="inlineStr"/>
       <c r="E245" s="11" t="inlineStr"/>
       <c r="F245" s="11" t="inlineStr"/>
-      <c r="G245" s="11" t="inlineStr"/>
+      <c r="G245" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="H245" s="12" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah, yeah, yeah. I heard that it's gonna be in July. The visit the African Minister's visit.</t>
+          <t>[Question to Professor] Ah, okay. So, so we cannot [inaudible].</t>
         </is>
       </c>
       <c r="C246" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D246" s="11" t="inlineStr"/>
       <c r="E246" s="11" t="inlineStr"/>
@@ -5323,16 +5303,16 @@
     <row r="247">
       <c r="A247" s="9" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="B247" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah, for them, the only thing I mean it's an it's just an invitation because they know how to fast track their own visa. You just need.</t>
+          <t>[Comment] I see.</t>
         </is>
       </c>
       <c r="C247" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D247" s="11" t="inlineStr"/>
       <c r="E247" s="11" t="inlineStr"/>
@@ -5343,16 +5323,16 @@
     <row r="248">
       <c r="A248" s="9" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="B248" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So that that's why that's where I had the challenge. I told him, and he said them and Minister of Science and ICT don't have any anything to do with with that invitation. That the Minister of Finance normally sends it to the Minister of Finance of African countries.</t>
+          <t>[Comment] His son. Is that Hong?</t>
         </is>
       </c>
       <c r="C248" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D248" s="11" t="inlineStr"/>
       <c r="E248" s="11" t="inlineStr"/>
@@ -5363,16 +5343,16 @@
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>19:31</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="B249" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah.</t>
+          <t>[Comment] But from what he's saying, he said he's not them that sends the invitation that I they don't have any business with sending the invitation. No Nypa. The Ministry of Foreign Affairs and the Ministry of Science and Technology.</t>
         </is>
       </c>
       <c r="C249" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D249" s="11" t="inlineStr"/>
       <c r="E249" s="11" t="inlineStr"/>
@@ -5383,16 +5363,16 @@
     <row r="250">
       <c r="A250" s="9" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="B250" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So that we have to find out on our own.</t>
+          <t>[Comment] They said it's not even Science and Technology or Nypa.</t>
         </is>
       </c>
       <c r="C250" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D250" s="11" t="inlineStr"/>
       <c r="E250" s="11" t="inlineStr"/>
@@ -5403,12 +5383,12 @@
     <row r="251">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>19:37</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="B251" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah, I and it's on AI and digital transformation. So I'm wondering why they're only inviting only Ministers of of Finance instead of the relevant ministers.</t>
+          <t>[Comment] Because I'm I'm supposed to meet him and Professor next month on the 22nd.</t>
         </is>
       </c>
       <c r="C251" s="9" t="n">
@@ -5423,16 +5403,16 @@
     <row r="252">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="B252" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah.</t>
+          <t>[Comment] So he said it's part of the I think is initiated from our home countries. That is normally sent to Ministry of Finance, not even Science and Technology.</t>
         </is>
       </c>
       <c r="C252" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D252" s="11" t="inlineStr"/>
       <c r="E252" s="11" t="inlineStr"/>
@@ -5443,16 +5423,16 @@
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="B253" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah.</t>
+          <t>[Comment] They they might not even know when they send.</t>
         </is>
       </c>
       <c r="C253" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D253" s="11" t="inlineStr"/>
       <c r="E253" s="11" t="inlineStr"/>
@@ -5463,16 +5443,16 @@
     <row r="254">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="B254" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But I think he told</t>
+          <t>[Comment] African Development Bank. And it's in partnership with Ministry of Finance of Korea. That they they normally send it to Ministry of Finance of the of the other countries.</t>
         </is>
       </c>
       <c r="C254" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D254" s="11" t="inlineStr"/>
       <c r="E254" s="11" t="inlineStr"/>
@@ -5483,16 +5463,16 @@
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="B255" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But I'll still give it a try because I told my my boss today that they should find out from Ministry of Finance if they received any official letter from from Korea. If if it was this kind of thing, I would have, like, if if it was Costa Rica, I would have tried to, hey, if you guys started, like I would just call my minister or ask your minister or advisors to the minister, do you know if the minister is well acquainted with the Ministry of Finance? If they're well acquainted, from peer to peer, they will say, hey, you know, if you're going to Korea, one of the key projects for me would be this. So if you meet together with the minister of finance, please talk about this. Just that key thing, because we think if those agendas happen, they're going to be one-on-one meetings. Formal meetings.</t>
+          <t>[Comment] Gido. right?</t>
         </is>
       </c>
       <c r="C255" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D255" s="11" t="inlineStr"/>
       <c r="E255" s="11" t="inlineStr"/>
@@ -5503,16 +5483,16 @@
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>23:16</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="B256" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Also, um there are two Nigerians that are coming for the digitology event. Both of them are working in African Development Bank. So these are other and other people that that I want to use because I also already told the that we should schedule a meeting with with them when they arrive for the let's have like even if it's 30 minutes, let's have a meeting together and and discuss on they because for them, they know the areas that you can apply for funds for and it will get easier, easier approval.</t>
+          <t>[Comment] around September or so.</t>
         </is>
       </c>
       <c r="C256" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D256" s="11" t="inlineStr"/>
       <c r="E256" s="11" t="inlineStr"/>
@@ -5523,16 +5503,16 @@
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>30:44</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="B257" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah, I have some ongoing and pending.</t>
+          <t>[Comment] I think it's July.</t>
         </is>
       </c>
       <c r="C257" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D257" s="11" t="inlineStr"/>
       <c r="E257" s="11" t="inlineStr"/>
@@ -5543,16 +5523,16 @@
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>30:46</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B258" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Okay.</t>
+          <t>[Question to Professor] I think it's July.</t>
         </is>
       </c>
       <c r="C258" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D258" s="11" t="inlineStr"/>
       <c r="E258" s="11" t="inlineStr"/>
@@ -5563,16 +5543,16 @@
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>30:49</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="B259" s="10" t="inlineStr">
         <is>
-          <t>[Comment] because I initiated direct discussion with the DG of the NDTI to introduce the NTS adoption concept and to gauge his.</t>
+          <t>[Comment] I I Yeah.</t>
         </is>
       </c>
       <c r="C259" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D259" s="11" t="inlineStr"/>
       <c r="E259" s="11" t="inlineStr"/>
@@ -5583,16 +5563,16 @@
     <row r="260">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>30:59</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="B260" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Institutional interest.</t>
+          <t>[Comment] Yeah, yeah, yeah. I heard that it's gonna be in July. The visit the African Minister's visit.</t>
         </is>
       </c>
       <c r="C260" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D260" s="11" t="inlineStr"/>
       <c r="E260" s="11" t="inlineStr"/>
@@ -5603,16 +5583,16 @@
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>31:02</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="B261" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So the DG expressed optimism that the collaboration will solve both NBTIS operational problem and Nigeria's broader R&amp;D coordination challenge.</t>
+          <t>[Comment] Yeah, for them, the only thing I mean it's an it's just an invitation because they know how to fast track their own visa. You just need.</t>
         </is>
       </c>
       <c r="C261" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D261" s="11" t="inlineStr"/>
       <c r="E261" s="11" t="inlineStr"/>
@@ -5623,16 +5603,16 @@
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>31:13</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="B262" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So also the supervising director, I I discussed with him. So he the he confirmed ministry level relevance and undertook to escalate also to the DG of NBTI.</t>
+          <t>[Comment] So that that's why that's where I had the challenge. I told him, and he said them and Minister of Science and ICT don't have any anything to do with with that invitation. That the Minister of Finance normally sends it to the Minister of Finance of African countries.</t>
         </is>
       </c>
       <c r="C262" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D262" s="11" t="inlineStr"/>
       <c r="E262" s="11" t="inlineStr"/>
@@ -5643,16 +5623,16 @@
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>34:45</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="B263" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I identify FMS the Federal Ministry of Innovation, Science and Technology as a primary institutional owner of the proposed collaboration.</t>
+          <t>[Comment] Yeah.</t>
         </is>
       </c>
       <c r="C263" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D263" s="11" t="inlineStr"/>
       <c r="E263" s="11" t="inlineStr"/>
@@ -5663,16 +5643,16 @@
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>34:54</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="B264" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Who are the holders of the econ mandate executive for the five authority.</t>
+          <t>[Comment] So that we have to find out on our own.</t>
         </is>
       </c>
       <c r="C264" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D264" s="11" t="inlineStr"/>
       <c r="E264" s="11" t="inlineStr"/>
@@ -5683,16 +5663,16 @@
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>34:58</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="B265" s="10" t="inlineStr">
         <is>
-          <t>[Comment] budgetary authority.</t>
+          <t>[Comment] Yeah, I and it's on AI and digital transformation. So I'm wondering why they're only inviting only Ministers of of Finance instead of the relevant ministers.</t>
         </is>
       </c>
       <c r="C265" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D265" s="11" t="inlineStr"/>
       <c r="E265" s="11" t="inlineStr"/>
@@ -5703,16 +5683,16 @@
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>35:13</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="B266" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Maybe it depends on the level of collaboration they had with-</t>
+          <t>[Comment] Yeah.</t>
         </is>
       </c>
       <c r="C266" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D266" s="11" t="inlineStr"/>
       <c r="E266" s="11" t="inlineStr"/>
@@ -5723,7 +5703,7 @@
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>36:48</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="B267" s="10" t="inlineStr">
@@ -5731,11 +5711,11 @@
           <t>[Comment] Yeah.</t>
         </is>
       </c>
-      <c r="C267" s="11" t="inlineStr"/>
+      <c r="C267" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D267" s="11" t="inlineStr"/>
-      <c r="E267" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E267" s="11" t="inlineStr"/>
       <c r="F267" s="11" t="inlineStr"/>
       <c r="G267" s="11" t="inlineStr"/>
       <c r="H267" s="12" t="inlineStr"/>
@@ -5743,19 +5723,19 @@
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>36:54</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="B268" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Supply side that's the Korean side.</t>
-        </is>
-      </c>
-      <c r="C268" s="11" t="inlineStr"/>
+          <t>[Comment] But I think he told</t>
+        </is>
+      </c>
+      <c r="C268" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D268" s="11" t="inlineStr"/>
-      <c r="E268" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="E268" s="11" t="inlineStr"/>
       <c r="F268" s="11" t="inlineStr"/>
       <c r="G268" s="11" t="inlineStr"/>
       <c r="H268" s="12" t="inlineStr"/>
@@ -5763,16 +5743,16 @@
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>41:12</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="B269" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because it</t>
+          <t>[Comment] But I'll still give it a try because I told my my boss today that they should find out from Ministry of Finance if they received any official letter from from Korea. If if it was this kind of thing, I would have, like, if if it was Costa Rica, I would have tried to, hey, if you guys started, like I would just call my minister or ask your minister or advisors to the minister, do you know if the minister is well acquainted with the Ministry of Finance? If they're well acquainted, from peer to peer, they will say, hey, you know, if you're going to Korea, one of the key projects for me would be this. So if you meet together with the minister of finance, please talk about this. Just that key thing, because we think if those agendas happen, they're going to be one-on-one meetings. Formal meetings.</t>
         </is>
       </c>
       <c r="C269" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D269" s="11" t="inlineStr"/>
       <c r="E269" s="11" t="inlineStr"/>
@@ -5783,16 +5763,16 @@
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>41:17</t>
+          <t>23:16</t>
         </is>
       </c>
       <c r="B270" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah, from they sort of they give a conducive environment for for development of startups where they develop their</t>
+          <t>[Comment] Also, um there are two Nigerians that are coming for the digitology event. Both of them are working in African Development Bank. So these are other and other people that that I want to use because I also already told the that we should schedule a meeting with with them when they arrive for the let's have like even if it's 30 minutes, let's have a meeting together and and discuss on they because for them, they know the areas that you can apply for funds for and it will get easier, easier approval.</t>
         </is>
       </c>
       <c r="C270" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D270" s="11" t="inlineStr"/>
       <c r="E270" s="11" t="inlineStr"/>
@@ -5803,16 +5783,16 @@
     <row r="271">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>43:31</t>
+          <t>30:44</t>
         </is>
       </c>
       <c r="B271" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I'm looking at it from the angle that like A3, like even the what she explained earlier today, that so many startups, they they</t>
+          <t>[Voluntary Response] Yeah, I have some ongoing and pending.</t>
         </is>
       </c>
       <c r="C271" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D271" s="11" t="inlineStr"/>
       <c r="E271" s="11" t="inlineStr"/>
@@ -5823,7 +5803,7 @@
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>45:00</t>
+          <t>30:46</t>
         </is>
       </c>
       <c r="B272" s="10" t="inlineStr">
@@ -5843,16 +5823,16 @@
     <row r="273">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>50:13</t>
+          <t>30:49</t>
         </is>
       </c>
       <c r="B273" s="10" t="inlineStr">
         <is>
-          <t>[Comment] [inaudible] synthesis.</t>
+          <t>[Comment] because I initiated direct discussion with the DG of the NDTI to introduce the NTS adoption concept and to gauge his.</t>
         </is>
       </c>
       <c r="C273" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D273" s="11" t="inlineStr"/>
       <c r="E273" s="11" t="inlineStr"/>
@@ -5863,16 +5843,16 @@
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>50:27</t>
+          <t>30:59</t>
         </is>
       </c>
       <c r="B274" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Okay. Uh for me, uh I input the contextual intelligence uh I have uh one ongoing which is benchmarking for AI globally.</t>
+          <t>[Comment] Institutional interest.</t>
         </is>
       </c>
       <c r="C274" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D274" s="11" t="inlineStr"/>
       <c r="E274" s="11" t="inlineStr"/>
@@ -5883,16 +5863,16 @@
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>50:39</t>
+          <t>31:02</t>
         </is>
       </c>
       <c r="B275" s="10" t="inlineStr">
         <is>
-          <t>[Comment] and validate.</t>
+          <t>[Comment] So the DG expressed optimism that the collaboration will solve both NBTIS operational problem and Nigeria's broader R&amp;D coordination challenge.</t>
         </is>
       </c>
       <c r="C275" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D275" s="11" t="inlineStr"/>
       <c r="E275" s="11" t="inlineStr"/>
@@ -5903,16 +5883,16 @@
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>50:40</t>
+          <t>31:13</t>
         </is>
       </c>
       <c r="B276" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah.</t>
+          <t>[Comment] So also the supervising director, I I discussed with him. So he the he confirmed ministry level relevance and undertook to escalate also to the DG of NBTI.</t>
         </is>
       </c>
       <c r="C276" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D276" s="11" t="inlineStr"/>
       <c r="E276" s="11" t="inlineStr"/>
@@ -5923,16 +5903,16 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>51:09</t>
+          <t>34:45</t>
         </is>
       </c>
       <c r="B277" s="10" t="inlineStr">
         <is>
-          <t>[Comment] It's totally different.</t>
+          <t>[Comment] I identify FMS the Federal Ministry of Innovation, Science and Technology as a primary institutional owner of the proposed collaboration.</t>
         </is>
       </c>
       <c r="C277" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D277" s="11" t="inlineStr"/>
       <c r="E277" s="11" t="inlineStr"/>
@@ -5943,36 +5923,36 @@
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>51:18</t>
+          <t>34:54</t>
         </is>
       </c>
       <c r="B278" s="10" t="inlineStr">
         <is>
-          <t>[Comment] The person is still to bring the minister of Science and Technology to, because it wouldn't only focus on NTIS then, because so many other things will speak of.</t>
-        </is>
-      </c>
-      <c r="C278" s="11" t="inlineStr"/>
+          <t>[Question to Professor] Who are the holders of the econ mandate executive for the five authority.</t>
+        </is>
+      </c>
+      <c r="C278" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D278" s="11" t="inlineStr"/>
       <c r="E278" s="11" t="inlineStr"/>
       <c r="F278" s="11" t="inlineStr"/>
-      <c r="G278" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="G278" s="11" t="inlineStr"/>
       <c r="H278" s="12" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>51:19</t>
+          <t>34:58</t>
         </is>
       </c>
       <c r="B279" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So I tried kinda to find the which one is the use the business division that they will approach.</t>
+          <t>[Comment] budgetary authority.</t>
         </is>
       </c>
       <c r="C279" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D279" s="11" t="inlineStr"/>
       <c r="E279" s="11" t="inlineStr"/>
@@ -5983,12 +5963,12 @@
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>51:27</t>
+          <t>35:13</t>
         </is>
       </c>
       <c r="B280" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So maybe after I get the that information, I will</t>
+          <t>[Comment] Maybe it depends on the level of collaboration they had with-</t>
         </is>
       </c>
       <c r="C280" s="9" t="n">
@@ -6003,19 +5983,19 @@
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>51:31</t>
+          <t>36:48</t>
         </is>
       </c>
       <c r="B281" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah, try to match my my problem statement. So uh but uh up till now I haven't still get the the result. So I put it in can be. For the for the use case targeted. The business side.</t>
-        </is>
-      </c>
-      <c r="C281" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] Yeah.</t>
+        </is>
+      </c>
+      <c r="C281" s="11" t="inlineStr"/>
       <c r="D281" s="11" t="inlineStr"/>
-      <c r="E281" s="11" t="inlineStr"/>
+      <c r="E281" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F281" s="11" t="inlineStr"/>
       <c r="G281" s="11" t="inlineStr"/>
       <c r="H281" s="12" t="inlineStr"/>
@@ -6023,19 +6003,19 @@
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>51:45</t>
+          <t>36:54</t>
         </is>
       </c>
       <c r="B282" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And for the stakeholder engagement,</t>
-        </is>
-      </c>
-      <c r="C282" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] Supply side that's the Korean side.</t>
+        </is>
+      </c>
+      <c r="C282" s="11" t="inlineStr"/>
       <c r="D282" s="11" t="inlineStr"/>
-      <c r="E282" s="11" t="inlineStr"/>
+      <c r="E282" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="F282" s="11" t="inlineStr"/>
       <c r="G282" s="11" t="inlineStr"/>
       <c r="H282" s="12" t="inlineStr"/>
@@ -6043,19 +6023,19 @@
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>51:46</t>
+          <t>41:12</t>
         </is>
       </c>
       <c r="B283" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Well.</t>
-        </is>
-      </c>
-      <c r="C283" s="11" t="inlineStr"/>
+          <t>[Comment] Because it</t>
+        </is>
+      </c>
+      <c r="C283" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D283" s="11" t="inlineStr"/>
-      <c r="E283" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E283" s="11" t="inlineStr"/>
       <c r="F283" s="11" t="inlineStr"/>
       <c r="G283" s="11" t="inlineStr"/>
       <c r="H283" s="12" t="inlineStr"/>
@@ -6063,16 +6043,16 @@
     <row r="284">
       <c r="A284" s="9" t="inlineStr">
         <is>
-          <t>51:50</t>
+          <t>41:17</t>
         </is>
       </c>
       <c r="B284" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Ah yeah, actually it's two.</t>
+          <t>[Voluntary Response] Yeah, from they sort of they give a conducive environment for for development of startups where they develop their</t>
         </is>
       </c>
       <c r="C284" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D284" s="11" t="inlineStr"/>
       <c r="E284" s="11" t="inlineStr"/>
@@ -6083,16 +6063,16 @@
     <row r="285">
       <c r="A285" s="9" t="inlineStr">
         <is>
-          <t>51:55</t>
+          <t>43:31</t>
         </is>
       </c>
       <c r="B285" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah. Next to help my statement.</t>
+          <t>[Voluntary Response] I'm looking at it from the angle that like A3, like even the what she explained earlier today, that so many startups, they they</t>
         </is>
       </c>
       <c r="C285" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D285" s="11" t="inlineStr"/>
       <c r="E285" s="11" t="inlineStr"/>
@@ -6103,19 +6083,19 @@
     <row r="286">
       <c r="A286" s="9" t="inlineStr">
         <is>
-          <t>51:56</t>
+          <t>45:00</t>
         </is>
       </c>
       <c r="B286" s="10" t="inlineStr">
         <is>
-          <t>[Comment] It's.</t>
-        </is>
-      </c>
-      <c r="C286" s="11" t="inlineStr"/>
+          <t>[Comment] Okay.</t>
+        </is>
+      </c>
+      <c r="C286" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D286" s="11" t="inlineStr"/>
-      <c r="E286" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="E286" s="11" t="inlineStr"/>
       <c r="F286" s="11" t="inlineStr"/>
       <c r="G286" s="11" t="inlineStr"/>
       <c r="H286" s="12" t="inlineStr"/>
@@ -6123,16 +6103,16 @@
     <row r="287">
       <c r="A287" s="9" t="inlineStr">
         <is>
-          <t>51:59</t>
+          <t>50:13</t>
         </is>
       </c>
       <c r="B287" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And for uh for the stakeholder engagement, confirm legal clearance from BRI legal team for collaboration. In term of the, let's say I go with uh either either either partner, toorus, Moai or blah blah blah. Uh so it is also uh in uh pending.</t>
+          <t>[Comment] [inaudible] synthesis.</t>
         </is>
       </c>
       <c r="C287" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D287" s="11" t="inlineStr"/>
       <c r="E287" s="11" t="inlineStr"/>
@@ -6143,12 +6123,12 @@
     <row r="288">
       <c r="A288" s="9" t="inlineStr">
         <is>
-          <t>52:24</t>
+          <t>50:27</t>
         </is>
       </c>
       <c r="B288" s="10" t="inlineStr">
         <is>
-          <t>[Comment] In term after we get the TTS model can uh is it legal to to to be deployed to deploy in?</t>
+          <t>[Comment] Okay. Uh for me, uh I input the contextual intelligence uh I have uh one ongoing which is benchmarking for AI globally.</t>
         </is>
       </c>
       <c r="C288" s="9" t="n">
@@ -6163,16 +6143,16 @@
     <row r="289">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>52:35</t>
+          <t>50:39</t>
         </is>
       </c>
       <c r="B289" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Oh yeah, yeah, yeah. I I put it also.</t>
+          <t>[Comment] and validate.</t>
         </is>
       </c>
       <c r="C289" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D289" s="11" t="inlineStr"/>
       <c r="E289" s="11" t="inlineStr"/>
@@ -6183,16 +6163,16 @@
     <row r="290">
       <c r="A290" s="9" t="inlineStr">
         <is>
-          <t>52:38</t>
+          <t>50:40</t>
         </is>
       </c>
       <c r="B290" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh and next I move to the technology scouting.</t>
+          <t>[Voluntary Response] Yeah.</t>
         </is>
       </c>
       <c r="C290" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D290" s="11" t="inlineStr"/>
       <c r="E290" s="11" t="inlineStr"/>
@@ -6203,12 +6183,12 @@
     <row r="291">
       <c r="A291" s="9" t="inlineStr">
         <is>
-          <t>52:57</t>
+          <t>51:09</t>
         </is>
       </c>
       <c r="B291" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Uh Professor Yun, she also already replied.</t>
+          <t>[Comment] It's totally different.</t>
         </is>
       </c>
       <c r="C291" s="9" t="n">
@@ -6223,36 +6203,36 @@
     <row r="292">
       <c r="A292" s="9" t="inlineStr">
         <is>
-          <t>53:01</t>
+          <t>51:18</t>
         </is>
       </c>
       <c r="B292" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And now this, I actually I put it in the maybe I can just jump, jump.</t>
-        </is>
-      </c>
-      <c r="C292" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] The person is still to bring the minister of Science and Technology to, because it wouldn't only focus on NTIS then, because so many other things will speak of.</t>
+        </is>
+      </c>
+      <c r="C292" s="11" t="inlineStr"/>
       <c r="D292" s="11" t="inlineStr"/>
       <c r="E292" s="11" t="inlineStr"/>
       <c r="F292" s="11" t="inlineStr"/>
-      <c r="G292" s="11" t="inlineStr"/>
+      <c r="G292" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="H292" s="12" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="9" t="inlineStr">
         <is>
-          <t>53:07</t>
+          <t>51:19</t>
         </is>
       </c>
       <c r="B293" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Jump, jump.</t>
+          <t>[Comment] So I tried kinda to find the which one is the use the business division that they will approach.</t>
         </is>
       </c>
       <c r="C293" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D293" s="11" t="inlineStr"/>
       <c r="E293" s="11" t="inlineStr"/>
@@ -6263,16 +6243,16 @@
     <row r="294">
       <c r="A294" s="9" t="inlineStr">
         <is>
-          <t>53:40</t>
+          <t>51:27</t>
         </is>
       </c>
       <c r="B294" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Exactly. But to to to watering down, maybe I will put the Koika and I will try to explain them. Uh actually, there will be, I can, sorry, uh I can approach the Koika. But still you need to also show the the the BRI uh must have so some need also.</t>
+          <t>[Comment] So maybe after I get the that information, I will</t>
         </is>
       </c>
       <c r="C294" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D294" s="11" t="inlineStr"/>
       <c r="E294" s="11" t="inlineStr"/>
@@ -6283,16 +6263,16 @@
     <row r="295">
       <c r="A295" s="9" t="inlineStr">
         <is>
-          <t>54:04</t>
+          <t>51:31</t>
         </is>
       </c>
       <c r="B295" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah, that that's so that's time.</t>
+          <t>[Comment] Yeah, try to match my my problem statement. So uh but uh up till now I haven't still get the the result. So I put it in can be. For the for the use case targeted. The business side.</t>
         </is>
       </c>
       <c r="C295" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D295" s="11" t="inlineStr"/>
       <c r="E295" s="11" t="inlineStr"/>
@@ -6303,16 +6283,16 @@
     <row r="296">
       <c r="A296" s="9" t="inlineStr">
         <is>
-          <t>54:07</t>
+          <t>51:45</t>
         </is>
       </c>
       <c r="B296" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yes, the commitment and I and that's kind of the thing that I want to to to approach to them, to to the to the</t>
+          <t>[Comment] And for the stakeholder engagement,</t>
         </is>
       </c>
       <c r="C296" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D296" s="11" t="inlineStr"/>
       <c r="E296" s="11" t="inlineStr"/>
@@ -6323,19 +6303,19 @@
     <row r="297">
       <c r="A297" s="9" t="inlineStr">
         <is>
-          <t>54:21</t>
+          <t>51:46</t>
         </is>
       </c>
       <c r="B297" s="10" t="inlineStr">
         <is>
-          <t>[Comment] That's why I'm uh before</t>
-        </is>
-      </c>
-      <c r="C297" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Voluntary Response] Well.</t>
+        </is>
+      </c>
+      <c r="C297" s="11" t="inlineStr"/>
       <c r="D297" s="11" t="inlineStr"/>
-      <c r="E297" s="11" t="inlineStr"/>
+      <c r="E297" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F297" s="11" t="inlineStr"/>
       <c r="G297" s="11" t="inlineStr"/>
       <c r="H297" s="12" t="inlineStr"/>
@@ -6343,16 +6323,16 @@
     <row r="298">
       <c r="A298" s="9" t="inlineStr">
         <is>
-          <t>54:35</t>
+          <t>51:50</t>
         </is>
       </c>
       <c r="B298" s="10" t="inlineStr">
         <is>
-          <t>[Comment] No, yeah, yeah.</t>
+          <t>[Comment] Ah yeah, actually it's two.</t>
         </is>
       </c>
       <c r="C298" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D298" s="11" t="inlineStr"/>
       <c r="E298" s="11" t="inlineStr"/>
@@ -6363,16 +6343,16 @@
     <row r="299">
       <c r="A299" s="9" t="inlineStr">
         <is>
-          <t>54:37</t>
+          <t>51:55</t>
         </is>
       </c>
       <c r="B299" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But I mean, uh in term So but in term to I replay more to the Professor Yuan.</t>
+          <t>[Comment] Yeah. Next to help my statement.</t>
         </is>
       </c>
       <c r="C299" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D299" s="11" t="inlineStr"/>
       <c r="E299" s="11" t="inlineStr"/>
@@ -6383,19 +6363,19 @@
     <row r="300">
       <c r="A300" s="9" t="inlineStr">
         <is>
-          <t>54:45</t>
+          <t>51:56</t>
         </is>
       </c>
       <c r="B300" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yun, Professor Yun, I have to at least I think I need to state the budget. So you you see</t>
-        </is>
-      </c>
-      <c r="C300" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] It's.</t>
+        </is>
+      </c>
+      <c r="C300" s="11" t="inlineStr"/>
       <c r="D300" s="11" t="inlineStr"/>
-      <c r="E300" s="11" t="inlineStr"/>
+      <c r="E300" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F300" s="11" t="inlineStr"/>
       <c r="G300" s="11" t="inlineStr"/>
       <c r="H300" s="12" t="inlineStr"/>
@@ -6403,16 +6383,16 @@
     <row r="301">
       <c r="A301" s="9" t="inlineStr">
         <is>
-          <t>55:11</t>
+          <t>51:59</t>
         </is>
       </c>
       <c r="B301" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] So I will try to communicate with them and then I will try to escalate it to his boss or her boss.</t>
+          <t>[Comment] And for uh for the stakeholder engagement, confirm legal clearance from BRI legal team for collaboration. In term of the, let's say I go with uh either either either partner, toorus, Moai or blah blah blah. Uh so it is also uh in uh pending.</t>
         </is>
       </c>
       <c r="C301" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D301" s="11" t="inlineStr"/>
       <c r="E301" s="11" t="inlineStr"/>
@@ -6423,16 +6403,16 @@
     <row r="302">
       <c r="A302" s="9" t="inlineStr">
         <is>
-          <t>56:05</t>
+          <t>52:24</t>
         </is>
       </c>
       <c r="B302" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah.</t>
+          <t>[Comment] In term after we get the TTS model can uh is it legal to to to be deployed to deploy in?</t>
         </is>
       </c>
       <c r="C302" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D302" s="11" t="inlineStr"/>
       <c r="E302" s="11" t="inlineStr"/>
@@ -6443,18 +6423,18 @@
     <row r="303">
       <c r="A303" s="9" t="inlineStr">
         <is>
-          <t>56:12</t>
+          <t>52:35</t>
         </is>
       </c>
       <c r="B303" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh, I will just share my experience. Actually, I tried to approach one of the, uh, in charge in [inaudible] I will not mention names of course. I just asked her if, um, for the project that I want to propose, is it possible to be granted using the Korean Fund because one of my friends worked on a project and that project was granted by the Korean Fund. So, uh, I just asked her if it's possible. And she said that, um, for the Korean Fund, um, they are only granting projects that is between the Korean government and the Indonesian government. So, if your project is from your institution, for example, your research center, and you will ask for a grant, if the counterpart of the fund is the Korean company, it's possible. But if it's not and you're just asking for a fund for your personal project, it's not possible. But if you have, uh, for example, you work in a research center and then your research center will ask for a fund and the fund is from the Korean government, but then your counterpart, for example, in the research center is from Korea, then it's possible. But she mentioned that as far as I know, this is from the perspective of this person that I talked to, she said that it has to be a government-to-government transaction to avail a Korean fund, not from a personal or individual. So, I don't know if that is really the case or maybe it depends on the agency. So that's why, um, if you are, if you will just approach a person, they might give you, uh, a different answer.</t>
-        </is>
-      </c>
-      <c r="C303" s="11" t="inlineStr"/>
-      <c r="D303" s="9" t="n">
-        <v>1</v>
-      </c>
+          <t>[Comment] Oh yeah, yeah, yeah. I I put it also.</t>
+        </is>
+      </c>
+      <c r="C303" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D303" s="11" t="inlineStr"/>
       <c r="E303" s="11" t="inlineStr"/>
       <c r="F303" s="11" t="inlineStr"/>
       <c r="G303" s="11" t="inlineStr"/>
@@ -6463,16 +6443,16 @@
     <row r="304">
       <c r="A304" s="9" t="inlineStr">
         <is>
-          <t>60:06</t>
+          <t>52:38</t>
         </is>
       </c>
       <c r="B304" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Okay. Okay. I got it. So I think it's fair that it is, yeah, if I think my company should give uh a demo first for that just to impress the Indonesian partner.</t>
+          <t>[Comment] Uh and next I move to the technology scouting.</t>
         </is>
       </c>
       <c r="C304" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D304" s="11" t="inlineStr"/>
       <c r="E304" s="11" t="inlineStr"/>
@@ -6483,16 +6463,16 @@
     <row r="305">
       <c r="A305" s="9" t="inlineStr">
         <is>
-          <t>60:29</t>
+          <t>52:57</t>
         </is>
       </c>
       <c r="B305" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yes, right.</t>
+          <t>[Voluntary Response] Uh Professor Yun, she also already replied.</t>
         </is>
       </c>
       <c r="C305" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D305" s="11" t="inlineStr"/>
       <c r="E305" s="11" t="inlineStr"/>
@@ -6503,18 +6483,18 @@
     <row r="306">
       <c r="A306" s="9" t="inlineStr">
         <is>
-          <t>60:35</t>
+          <t>53:01</t>
         </is>
       </c>
       <c r="B306" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Okay. Ma'am.</t>
-        </is>
-      </c>
-      <c r="C306" s="11" t="inlineStr"/>
-      <c r="D306" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Comment] And now this, I actually I put it in the maybe I can just jump, jump.</t>
+        </is>
+      </c>
+      <c r="C306" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D306" s="11" t="inlineStr"/>
       <c r="E306" s="11" t="inlineStr"/>
       <c r="F306" s="11" t="inlineStr"/>
       <c r="G306" s="11" t="inlineStr"/>
@@ -6523,18 +6503,18 @@
     <row r="307">
       <c r="A307" s="9" t="inlineStr">
         <is>
-          <t>60:36</t>
+          <t>53:07</t>
         </is>
       </c>
       <c r="B307" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Yes, ma'am. I actually I don't want to add anything because our agenda is fixed already. But uh earlier, uh you told that if they're having the meeting, if we should uh provide to them the the time and then the the duration, right? So the agenda is 1 hour long. So when they're having the meeting, should we like put the time, for example, 30 minutes for the presentation, then 10 minutes for Q&amp;A something like that?</t>
-        </is>
-      </c>
-      <c r="C307" s="11" t="inlineStr"/>
-      <c r="D307" s="9" t="n">
-        <v>6</v>
-      </c>
+          <t>[Comment] Jump, jump.</t>
+        </is>
+      </c>
+      <c r="C307" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D307" s="11" t="inlineStr"/>
       <c r="E307" s="11" t="inlineStr"/>
       <c r="F307" s="11" t="inlineStr"/>
       <c r="G307" s="11" t="inlineStr"/>
@@ -6543,98 +6523,98 @@
     <row r="308">
       <c r="A308" s="9" t="inlineStr">
         <is>
-          <t>61:54</t>
+          <t>53:40</t>
         </is>
       </c>
       <c r="B308" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Ma'am.</t>
-        </is>
-      </c>
-      <c r="C308" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] Exactly. But to to to watering down, maybe I will put the Koika and I will try to explain them. Uh actually, there will be, I can, sorry, uh I can approach the Koika. But still you need to also show the the the BRI uh must have so some need also.</t>
+        </is>
+      </c>
+      <c r="C308" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="D308" s="11" t="inlineStr"/>
       <c r="E308" s="11" t="inlineStr"/>
-      <c r="F308" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F308" s="11" t="inlineStr"/>
       <c r="G308" s="11" t="inlineStr"/>
       <c r="H308" s="12" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="9" t="inlineStr">
         <is>
-          <t>61:56</t>
+          <t>54:04</t>
         </is>
       </c>
       <c r="B309" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yes, ma'am. Uh, earlier this year, I did my internship in a company called [inaudible]. Uh, it is a Korean company, uh, also. So, uh, I asked one of my supervisor in there who are, who is Korean. So I asked him like, is there any like fund for like students to do like research for their final project or something? So he told me that actually Korea has a lot of funding, uh, but it's not for like international students. It's only for Korean students. Yeah, so I don't know why. So, uh, I didn't push it further because like I thought like, yeah, it's only for Korean students and I'm not Korean. So yeah.</t>
-        </is>
-      </c>
-      <c r="C309" s="11" t="inlineStr"/>
+          <t>[Comment] Yeah, that that's so that's time.</t>
+        </is>
+      </c>
+      <c r="C309" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D309" s="11" t="inlineStr"/>
       <c r="E309" s="11" t="inlineStr"/>
-      <c r="F309" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F309" s="11" t="inlineStr"/>
       <c r="G309" s="11" t="inlineStr"/>
       <c r="H309" s="12" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="9" t="inlineStr">
         <is>
-          <t>62:00</t>
+          <t>54:07</t>
         </is>
       </c>
       <c r="B310" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Um, I think no, ma'am. I think it's good already. I just want to clarify for number four because if we confirm with them that we are meeting with them already. Do we still need to send the invitation to them or can we just have the meeting right away since it's already confirmed?</t>
-        </is>
-      </c>
-      <c r="C310" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] Yes, the commitment and I and that's kind of the thing that I want to to to approach to them, to to the to the</t>
+        </is>
+      </c>
+      <c r="C310" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D310" s="11" t="inlineStr"/>
       <c r="E310" s="11" t="inlineStr"/>
-      <c r="F310" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="F310" s="11" t="inlineStr"/>
       <c r="G310" s="11" t="inlineStr"/>
       <c r="H310" s="12" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="9" t="inlineStr">
         <is>
-          <t>63:06</t>
+          <t>54:21</t>
         </is>
       </c>
       <c r="B311" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Oh, is it?</t>
-        </is>
-      </c>
-      <c r="C311" s="11" t="inlineStr"/>
+          <t>[Comment] That's why I'm uh before</t>
+        </is>
+      </c>
+      <c r="C311" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D311" s="11" t="inlineStr"/>
       <c r="E311" s="11" t="inlineStr"/>
-      <c r="F311" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F311" s="11" t="inlineStr"/>
       <c r="G311" s="11" t="inlineStr"/>
       <c r="H311" s="12" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="9" t="inlineStr">
         <is>
-          <t>63:17</t>
+          <t>54:35</t>
         </is>
       </c>
       <c r="B312" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] No, ma'am. I did not send the email yet. Because I told you that my partner actually haven't given me a response when will be the meeting so I think I should send it when they actually give a response.</t>
-        </is>
-      </c>
-      <c r="C312" s="11" t="inlineStr"/>
-      <c r="D312" s="9" t="n">
-        <v>6</v>
-      </c>
+          <t>[Comment] No, yeah, yeah.</t>
+        </is>
+      </c>
+      <c r="C312" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D312" s="11" t="inlineStr"/>
       <c r="E312" s="11" t="inlineStr"/>
       <c r="F312" s="11" t="inlineStr"/>
       <c r="G312" s="11" t="inlineStr"/>
@@ -6643,56 +6623,56 @@
     <row r="313">
       <c r="A313" s="9" t="inlineStr">
         <is>
-          <t>64:08</t>
+          <t>54:37</t>
         </is>
       </c>
       <c r="B313" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Uh, no, ma'am. I also still need to work on it.</t>
-        </is>
-      </c>
-      <c r="C313" s="11" t="inlineStr"/>
+          <t>[Comment] But I mean, uh in term So but in term to I replay more to the Professor Yuan.</t>
+        </is>
+      </c>
+      <c r="C313" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D313" s="11" t="inlineStr"/>
       <c r="E313" s="11" t="inlineStr"/>
       <c r="F313" s="11" t="inlineStr"/>
-      <c r="G313" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G313" s="11" t="inlineStr"/>
       <c r="H313" s="12" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="9" t="inlineStr">
         <is>
-          <t>64:28</t>
+          <t>54:45</t>
         </is>
       </c>
       <c r="B314" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Okay, ma'am.</t>
-        </is>
-      </c>
-      <c r="C314" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] Yun, Professor Yun, I have to at least I think I need to state the budget. So you you see</t>
+        </is>
+      </c>
+      <c r="C314" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="D314" s="11" t="inlineStr"/>
       <c r="E314" s="11" t="inlineStr"/>
-      <c r="F314" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F314" s="11" t="inlineStr"/>
       <c r="G314" s="11" t="inlineStr"/>
       <c r="H314" s="12" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="9" t="inlineStr">
         <is>
-          <t>64:36</t>
+          <t>55:11</t>
         </is>
       </c>
       <c r="B315" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yes, ma'am.</t>
+          <t>[Voluntary Response] So I will try to communicate with them and then I will try to escalate it to his boss or her boss.</t>
         </is>
       </c>
       <c r="C315" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D315" s="11" t="inlineStr"/>
       <c r="E315" s="11" t="inlineStr"/>
@@ -6703,39 +6683,39 @@
     <row r="316">
       <c r="A316" s="9" t="inlineStr">
         <is>
-          <t>64:39</t>
+          <t>56:05</t>
         </is>
       </c>
       <c r="B316" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] No, ma'am. I haven't tried to, uh, approach anybody.</t>
-        </is>
-      </c>
-      <c r="C316" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] Yeah.</t>
+        </is>
+      </c>
+      <c r="C316" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D316" s="11" t="inlineStr"/>
       <c r="E316" s="11" t="inlineStr"/>
       <c r="F316" s="11" t="inlineStr"/>
-      <c r="G316" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G316" s="11" t="inlineStr"/>
       <c r="H316" s="12" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="9" t="inlineStr">
         <is>
-          <t>64:59</t>
+          <t>56:12</t>
         </is>
       </c>
       <c r="B317" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yes, ma'am.</t>
+          <t>[Comment] Uh, I will just share my experience. Actually, I tried to approach one of the, uh, in charge in [inaudible] I will not mention names of course. I just asked her if, um, for the project that I want to propose, is it possible to be granted using the Korean Fund because one of my friends worked on a project and that project was granted by the Korean Fund. So, uh, I just asked her if it's possible. And she said that, um, for the Korean Fund, um, they are only granting projects that is between the Korean government and the Indonesian government. So, if your project is from your institution, for example, your research center, and you will ask for a grant, if the counterpart of the fund is the Korean company, it's possible. But if it's not and you're just asking for a fund for your personal project, it's not possible. But if you have, uh, for example, you work in a research center and then your research center will ask for a fund and the fund is from the Korean government, but then your counterpart, for example, in the research center is from Korea, then it's possible. But she mentioned that as far as I know, this is from the perspective of this person that I talked to, she said that it has to be a government-to-government transaction to avail a Korean fund, not from a personal or individual. So, I don't know if that is really the case or maybe it depends on the agency. So that's why, um, if you are, if you will just approach a person, they might give you, uh, a different answer.</t>
         </is>
       </c>
       <c r="C317" s="11" t="inlineStr"/>
-      <c r="D317" s="11" t="inlineStr"/>
-      <c r="E317" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="D317" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E317" s="11" t="inlineStr"/>
       <c r="F317" s="11" t="inlineStr"/>
       <c r="G317" s="11" t="inlineStr"/>
       <c r="H317" s="12" t="inlineStr"/>
@@ -6743,38 +6723,38 @@
     <row r="318">
       <c r="A318" s="9" t="inlineStr">
         <is>
-          <t>66:18</t>
+          <t>60:06</t>
         </is>
       </c>
       <c r="B318" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Okay, thank you.</t>
-        </is>
-      </c>
-      <c r="C318" s="11" t="inlineStr"/>
+          <t>[Comment] Okay. Okay. I got it. So I think it's fair that it is, yeah, if I think my company should give uh a demo first for that just to impress the Indonesian partner.</t>
+        </is>
+      </c>
+      <c r="C318" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="D318" s="11" t="inlineStr"/>
       <c r="E318" s="11" t="inlineStr"/>
       <c r="F318" s="11" t="inlineStr"/>
-      <c r="G318" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G318" s="11" t="inlineStr"/>
       <c r="H318" s="12" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="9" t="inlineStr">
         <is>
-          <t>66:28</t>
+          <t>60:29</t>
         </is>
       </c>
       <c r="B319" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I think Stephen.</t>
-        </is>
-      </c>
-      <c r="C319" s="11" t="inlineStr"/>
-      <c r="D319" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Voluntary Response] Yes, right.</t>
+        </is>
+      </c>
+      <c r="C319" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D319" s="11" t="inlineStr"/>
       <c r="E319" s="11" t="inlineStr"/>
       <c r="F319" s="11" t="inlineStr"/>
       <c r="G319" s="11" t="inlineStr"/>
@@ -6783,152 +6763,152 @@
     <row r="320">
       <c r="A320" s="9" t="inlineStr">
         <is>
-          <t>66:36</t>
+          <t>60:35</t>
         </is>
       </c>
       <c r="B320" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah, uh, I think number one was just to do the scanning about the contextual intelligence about data data graph.</t>
+          <t>[Voluntary Response] Okay. Ma'am.</t>
         </is>
       </c>
       <c r="C320" s="11" t="inlineStr"/>
-      <c r="D320" s="11" t="inlineStr"/>
+      <c r="D320" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="E320" s="11" t="inlineStr"/>
       <c r="F320" s="11" t="inlineStr"/>
-      <c r="G320" s="9" t="n">
-        <v>5</v>
-      </c>
+      <c r="G320" s="11" t="inlineStr"/>
       <c r="H320" s="12" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="9" t="inlineStr">
         <is>
-          <t>66:49</t>
+          <t>60:36</t>
         </is>
       </c>
       <c r="B321" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] My main activities here were I was only the one.</t>
+          <t>[Question to Professor] Yes, ma'am. I actually I don't want to add anything because our agenda is fixed already. But uh earlier, uh you told that if they're having the meeting, if we should uh provide to them the the time and then the the duration, right? So the agenda is 1 hour long. So when they're having the meeting, should we like put the time, for example, 30 minutes for the presentation, then 10 minutes for Q&amp;A something like that?</t>
         </is>
       </c>
       <c r="C321" s="11" t="inlineStr"/>
-      <c r="D321" s="11" t="inlineStr"/>
+      <c r="D321" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="E321" s="11" t="inlineStr"/>
       <c r="F321" s="11" t="inlineStr"/>
-      <c r="G321" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G321" s="11" t="inlineStr"/>
       <c r="H321" s="12" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="9" t="inlineStr">
         <is>
-          <t>66:57</t>
+          <t>61:54</t>
         </is>
       </c>
       <c r="B322" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Have any issues?</t>
+          <t>[Voluntary Response] Ma'am.</t>
         </is>
       </c>
       <c r="C322" s="11" t="inlineStr"/>
       <c r="D322" s="11" t="inlineStr"/>
       <c r="E322" s="11" t="inlineStr"/>
-      <c r="F322" s="11" t="inlineStr"/>
-      <c r="G322" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F322" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G322" s="11" t="inlineStr"/>
       <c r="H322" s="12" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="9" t="inlineStr">
         <is>
-          <t>66:59</t>
+          <t>61:56</t>
         </is>
       </c>
       <c r="B323" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] If you go by operational steps here, in this part, you automatically look for something to do.</t>
+          <t>[Comment] Yes, ma'am. Uh, earlier this year, I did my internship in a company called [inaudible]. Uh, it is a Korean company, uh, also. So, uh, I asked one of my supervisor in there who are, who is Korean. So I asked him like, is there any like fund for like students to do like research for their final project or something? So he told me that actually Korea has a lot of funding, uh, but it's not for like international students. It's only for Korean students. Yeah, so I don't know why. So, uh, I didn't push it further because like I thought like, yeah, it's only for Korean students and I'm not Korean. So yeah.</t>
         </is>
       </c>
       <c r="C323" s="11" t="inlineStr"/>
       <c r="D323" s="11" t="inlineStr"/>
       <c r="E323" s="11" t="inlineStr"/>
-      <c r="F323" s="11" t="inlineStr"/>
-      <c r="G323" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="F323" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G323" s="11" t="inlineStr"/>
       <c r="H323" s="12" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
-          <t>67:06</t>
+          <t>62:00</t>
         </is>
       </c>
       <c r="B324" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And then.</t>
+          <t>[Question to Professor] Um, I think no, ma'am. I think it's good already. I just want to clarify for number four because if we confirm with them that we are meeting with them already. Do we still need to send the invitation to them or can we just have the meeting right away since it's already confirmed?</t>
         </is>
       </c>
       <c r="C324" s="11" t="inlineStr"/>
       <c r="D324" s="11" t="inlineStr"/>
       <c r="E324" s="11" t="inlineStr"/>
-      <c r="F324" s="11" t="inlineStr"/>
-      <c r="G324" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F324" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G324" s="11" t="inlineStr"/>
       <c r="H324" s="12" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="9" t="inlineStr">
         <is>
-          <t>67:07</t>
+          <t>63:06</t>
         </is>
       </c>
       <c r="B325" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And then I also review the the the policy gap, we have currently, it was also there.</t>
+          <t>[Question to Professor] Oh, is it?</t>
         </is>
       </c>
       <c r="C325" s="11" t="inlineStr"/>
       <c r="D325" s="11" t="inlineStr"/>
       <c r="E325" s="11" t="inlineStr"/>
-      <c r="F325" s="11" t="inlineStr"/>
-      <c r="G325" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="F325" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G325" s="11" t="inlineStr"/>
       <c r="H325" s="12" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="9" t="inlineStr">
         <is>
-          <t>67:14</t>
+          <t>63:17</t>
         </is>
       </c>
       <c r="B326" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And I also analyzing the the the the the the the</t>
+          <t>[Voluntary Response] No, ma'am. I did not send the email yet. Because I told you that my partner actually haven't given me a response when will be the meeting so I think I should send it when they actually give a response.</t>
         </is>
       </c>
       <c r="C326" s="11" t="inlineStr"/>
-      <c r="D326" s="11" t="inlineStr"/>
+      <c r="D326" s="9" t="n">
+        <v>6</v>
+      </c>
       <c r="E326" s="11" t="inlineStr"/>
       <c r="F326" s="11" t="inlineStr"/>
-      <c r="G326" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G326" s="11" t="inlineStr"/>
       <c r="H326" s="12" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="9" t="inlineStr">
         <is>
-          <t>67:21</t>
+          <t>64:08</t>
         </is>
       </c>
       <c r="B327" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Detail?</t>
+          <t>[Voluntary Response] Uh, no, ma'am. I also still need to work on it.</t>
         </is>
       </c>
       <c r="C327" s="11" t="inlineStr"/>
@@ -6943,52 +6923,52 @@
     <row r="328">
       <c r="A328" s="9" t="inlineStr">
         <is>
-          <t>67:22</t>
+          <t>64:28</t>
         </is>
       </c>
       <c r="B328" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Okay.</t>
+          <t>[Voluntary Response] Okay, ma'am.</t>
         </is>
       </c>
       <c r="C328" s="11" t="inlineStr"/>
       <c r="D328" s="11" t="inlineStr"/>
       <c r="E328" s="11" t="inlineStr"/>
-      <c r="F328" s="11" t="inlineStr"/>
-      <c r="G328" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F328" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G328" s="11" t="inlineStr"/>
       <c r="H328" s="12" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="9" t="inlineStr">
         <is>
-          <t>67:27</t>
+          <t>64:36</t>
         </is>
       </c>
       <c r="B329" s="10" t="inlineStr">
         <is>
-          <t>[Comment] For me, I thought it's an activity.</t>
-        </is>
-      </c>
-      <c r="C329" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] Yes, ma'am.</t>
+        </is>
+      </c>
+      <c r="C329" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="D329" s="11" t="inlineStr"/>
       <c r="E329" s="11" t="inlineStr"/>
       <c r="F329" s="11" t="inlineStr"/>
-      <c r="G329" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G329" s="11" t="inlineStr"/>
       <c r="H329" s="12" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="9" t="inlineStr">
         <is>
-          <t>67:36</t>
+          <t>64:39</t>
         </is>
       </c>
       <c r="B330" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Okay.</t>
+          <t>[Voluntary Response] No, ma'am. I haven't tried to, uh, approach anybody.</t>
         </is>
       </c>
       <c r="C330" s="11" t="inlineStr"/>
@@ -6996,39 +6976,39 @@
       <c r="E330" s="11" t="inlineStr"/>
       <c r="F330" s="11" t="inlineStr"/>
       <c r="G330" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H330" s="12" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="9" t="inlineStr">
         <is>
-          <t>67:41</t>
+          <t>64:59</t>
         </is>
       </c>
       <c r="B331" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Identify the new</t>
+          <t>[Voluntary Response] Yes, ma'am.</t>
         </is>
       </c>
       <c r="C331" s="11" t="inlineStr"/>
       <c r="D331" s="11" t="inlineStr"/>
-      <c r="E331" s="11" t="inlineStr"/>
+      <c r="E331" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="F331" s="11" t="inlineStr"/>
-      <c r="G331" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G331" s="11" t="inlineStr"/>
       <c r="H331" s="12" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="9" t="inlineStr">
         <is>
-          <t>68:14</t>
+          <t>66:18</t>
         </is>
       </c>
       <c r="B332" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] So I'm going for the stakeholders engagement.</t>
+          <t>[Voluntary Response] Okay, thank you.</t>
         </is>
       </c>
       <c r="C332" s="11" t="inlineStr"/>
@@ -7036,39 +7016,39 @@
       <c r="E332" s="11" t="inlineStr"/>
       <c r="F332" s="11" t="inlineStr"/>
       <c r="G332" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H332" s="12" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="9" t="inlineStr">
         <is>
-          <t>68:23</t>
+          <t>66:28</t>
         </is>
       </c>
       <c r="B333" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah, I got it from that side.</t>
+          <t>[Comment] I think Stephen.</t>
         </is>
       </c>
       <c r="C333" s="11" t="inlineStr"/>
-      <c r="D333" s="11" t="inlineStr"/>
+      <c r="D333" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E333" s="11" t="inlineStr"/>
       <c r="F333" s="11" t="inlineStr"/>
-      <c r="G333" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G333" s="11" t="inlineStr"/>
       <c r="H333" s="12" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="9" t="inlineStr">
         <is>
-          <t>68:26</t>
+          <t>66:36</t>
         </is>
       </c>
       <c r="B334" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] That is mapping the institutional mandates.</t>
+          <t>[Voluntary Response] Yeah, uh, I think number one was just to do the scanning about the contextual intelligence about data data graph.</t>
         </is>
       </c>
       <c r="C334" s="11" t="inlineStr"/>
@@ -7076,19 +7056,19 @@
       <c r="E334" s="11" t="inlineStr"/>
       <c r="F334" s="11" t="inlineStr"/>
       <c r="G334" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H334" s="12" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="9" t="inlineStr">
         <is>
-          <t>68:29</t>
+          <t>66:49</t>
         </is>
       </c>
       <c r="B335" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I need to consult the rural ICT department, and this is the division manager Charles Tambo.</t>
+          <t>[Voluntary Response] My main activities here were I was only the one.</t>
         </is>
       </c>
       <c r="C335" s="11" t="inlineStr"/>
@@ -7096,19 +7076,19 @@
       <c r="E335" s="11" t="inlineStr"/>
       <c r="F335" s="11" t="inlineStr"/>
       <c r="G335" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H335" s="12" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="9" t="inlineStr">
         <is>
-          <t>68:36</t>
+          <t>66:57</t>
         </is>
       </c>
       <c r="B336" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I saw I think you saw the email, I got a problem.</t>
+          <t>[Comment] Have any issues?</t>
         </is>
       </c>
       <c r="C336" s="11" t="inlineStr"/>
@@ -7116,19 +7096,19 @@
       <c r="E336" s="11" t="inlineStr"/>
       <c r="F336" s="11" t="inlineStr"/>
       <c r="G336" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H336" s="12" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="9" t="inlineStr">
         <is>
-          <t>68:40</t>
+          <t>66:59</t>
         </is>
       </c>
       <c r="B337" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Uh and then I validate it just to align with the the technical specifications.</t>
+          <t>[Voluntary Response] If you go by operational steps here, in this part, you automatically look for something to do.</t>
         </is>
       </c>
       <c r="C337" s="11" t="inlineStr"/>
@@ -7136,19 +7116,19 @@
       <c r="E337" s="11" t="inlineStr"/>
       <c r="F337" s="11" t="inlineStr"/>
       <c r="G337" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H337" s="12" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="9" t="inlineStr">
         <is>
-          <t>68:48</t>
+          <t>67:06</t>
         </is>
       </c>
       <c r="B338" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And then I go to technology coaching.</t>
+          <t>[Voluntary Response] And then.</t>
         </is>
       </c>
       <c r="C338" s="11" t="inlineStr"/>
@@ -7156,19 +7136,19 @@
       <c r="E338" s="11" t="inlineStr"/>
       <c r="F338" s="11" t="inlineStr"/>
       <c r="G338" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H338" s="12" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="9" t="inlineStr">
         <is>
-          <t>68:52</t>
+          <t>67:07</t>
         </is>
       </c>
       <c r="B339" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] So this is the here in Korea I've searched, and in fact, it's the</t>
+          <t>[Voluntary Response] And then I also review the the the policy gap, we have currently, it was also there.</t>
         </is>
       </c>
       <c r="C339" s="11" t="inlineStr"/>
@@ -7183,12 +7163,12 @@
     <row r="340">
       <c r="A340" s="9" t="inlineStr">
         <is>
-          <t>69:24</t>
+          <t>67:14</t>
         </is>
       </c>
       <c r="B340" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But what I saw from the website.</t>
+          <t>[Voluntary Response] And I also analyzing the the the the the the the</t>
         </is>
       </c>
       <c r="C340" s="11" t="inlineStr"/>
@@ -7203,398 +7183,398 @@
     <row r="341">
       <c r="A341" s="9" t="inlineStr">
         <is>
-          <t>70:00</t>
+          <t>67:21</t>
         </is>
       </c>
       <c r="B341" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And then, uh, Kisa has the source of the regression and whatever, we're gonna mark from there.</t>
-        </is>
-      </c>
-      <c r="C341" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Question to Professor] Detail?</t>
+        </is>
+      </c>
+      <c r="C341" s="11" t="inlineStr"/>
       <c r="D341" s="11" t="inlineStr"/>
       <c r="E341" s="11" t="inlineStr"/>
       <c r="F341" s="11" t="inlineStr"/>
-      <c r="G341" s="11" t="inlineStr"/>
+      <c r="G341" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H341" s="12" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="9" t="inlineStr">
         <is>
-          <t>70:09</t>
+          <t>67:22</t>
         </is>
       </c>
       <c r="B342" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And then I go to technology exploitation.</t>
-        </is>
-      </c>
-      <c r="C342" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Voluntary Response] Okay.</t>
+        </is>
+      </c>
+      <c r="C342" s="11" t="inlineStr"/>
       <c r="D342" s="11" t="inlineStr"/>
       <c r="E342" s="11" t="inlineStr"/>
       <c r="F342" s="11" t="inlineStr"/>
-      <c r="G342" s="11" t="inlineStr"/>
+      <c r="G342" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H342" s="12" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="9" t="inlineStr">
         <is>
-          <t>70:20</t>
+          <t>67:27</t>
         </is>
       </c>
       <c r="B343" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah, this is ongoing. that's what he told me.</t>
-        </is>
-      </c>
-      <c r="C343" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] For me, I thought it's an activity.</t>
+        </is>
+      </c>
+      <c r="C343" s="11" t="inlineStr"/>
       <c r="D343" s="11" t="inlineStr"/>
       <c r="E343" s="11" t="inlineStr"/>
       <c r="F343" s="11" t="inlineStr"/>
-      <c r="G343" s="11" t="inlineStr"/>
+      <c r="G343" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H343" s="12" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="9" t="inlineStr">
         <is>
-          <t>70:23</t>
+          <t>67:36</t>
         </is>
       </c>
       <c r="B344" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So assessing the context of</t>
-        </is>
-      </c>
-      <c r="C344" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Voluntary Response] Okay.</t>
+        </is>
+      </c>
+      <c r="C344" s="11" t="inlineStr"/>
       <c r="D344" s="11" t="inlineStr"/>
       <c r="E344" s="11" t="inlineStr"/>
       <c r="F344" s="11" t="inlineStr"/>
-      <c r="G344" s="11" t="inlineStr"/>
+      <c r="G344" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H344" s="12" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="9" t="inlineStr">
         <is>
-          <t>70:55</t>
+          <t>67:41</t>
         </is>
       </c>
       <c r="B345" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And then I will after discussing with the lady did you because, you know, I</t>
-        </is>
-      </c>
-      <c r="C345" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] Identify the new</t>
+        </is>
+      </c>
+      <c r="C345" s="11" t="inlineStr"/>
       <c r="D345" s="11" t="inlineStr"/>
       <c r="E345" s="11" t="inlineStr"/>
       <c r="F345" s="11" t="inlineStr"/>
-      <c r="G345" s="11" t="inlineStr"/>
+      <c r="G345" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H345" s="12" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="9" t="inlineStr">
         <is>
-          <t>71:18</t>
+          <t>68:14</t>
         </is>
       </c>
       <c r="B346" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I really added the company for</t>
-        </is>
-      </c>
-      <c r="C346" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Voluntary Response] So I'm going for the stakeholders engagement.</t>
+        </is>
+      </c>
+      <c r="C346" s="11" t="inlineStr"/>
       <c r="D346" s="11" t="inlineStr"/>
       <c r="E346" s="11" t="inlineStr"/>
       <c r="F346" s="11" t="inlineStr"/>
-      <c r="G346" s="11" t="inlineStr"/>
+      <c r="G346" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H346" s="12" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="9" t="inlineStr">
         <is>
-          <t>71:20</t>
+          <t>68:23</t>
         </is>
       </c>
       <c r="B347" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Or any other</t>
-        </is>
-      </c>
-      <c r="C347" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Voluntary Response] Yeah, I got it from that side.</t>
+        </is>
+      </c>
+      <c r="C347" s="11" t="inlineStr"/>
       <c r="D347" s="11" t="inlineStr"/>
       <c r="E347" s="11" t="inlineStr"/>
       <c r="F347" s="11" t="inlineStr"/>
-      <c r="G347" s="11" t="inlineStr"/>
+      <c r="G347" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H347" s="12" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="9" t="inlineStr">
         <is>
-          <t>71:21</t>
+          <t>68:26</t>
         </is>
       </c>
       <c r="B348" s="10" t="inlineStr">
         <is>
-          <t>[Comment] They had what they call mobile security.</t>
-        </is>
-      </c>
-      <c r="C348" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Voluntary Response] That is mapping the institutional mandates.</t>
+        </is>
+      </c>
+      <c r="C348" s="11" t="inlineStr"/>
       <c r="D348" s="11" t="inlineStr"/>
       <c r="E348" s="11" t="inlineStr"/>
       <c r="F348" s="11" t="inlineStr"/>
-      <c r="G348" s="11" t="inlineStr"/>
+      <c r="G348" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H348" s="12" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="9" t="inlineStr">
         <is>
-          <t>71:23</t>
+          <t>68:29</t>
         </is>
       </c>
       <c r="B349" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But I saw it is on the like after download and you have it on the your smartphone. That's why I need</t>
-        </is>
-      </c>
-      <c r="C349" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Voluntary Response] I need to consult the rural ICT department, and this is the division manager Charles Tambo.</t>
+        </is>
+      </c>
+      <c r="C349" s="11" t="inlineStr"/>
       <c r="D349" s="11" t="inlineStr"/>
       <c r="E349" s="11" t="inlineStr"/>
       <c r="F349" s="11" t="inlineStr"/>
-      <c r="G349" s="11" t="inlineStr"/>
+      <c r="G349" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H349" s="12" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="9" t="inlineStr">
         <is>
-          <t>71:31</t>
+          <t>68:36</t>
         </is>
       </c>
       <c r="B350" s="10" t="inlineStr">
         <is>
-          <t>[Comment] It's good but in terms of my, you know, at the end of the day you need to think about the context of your country. That's why I said this is well good developed countries where everyone has an idea of smart for</t>
-        </is>
-      </c>
-      <c r="C350" s="9" t="n">
-        <v>6</v>
-      </c>
+          <t>[Voluntary Response] I saw I think you saw the email, I got a problem.</t>
+        </is>
+      </c>
+      <c r="C350" s="11" t="inlineStr"/>
       <c r="D350" s="11" t="inlineStr"/>
       <c r="E350" s="11" t="inlineStr"/>
       <c r="F350" s="11" t="inlineStr"/>
-      <c r="G350" s="11" t="inlineStr"/>
+      <c r="G350" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H350" s="12" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="9" t="inlineStr">
         <is>
-          <t>72:01</t>
+          <t>68:40</t>
         </is>
       </c>
       <c r="B351" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Okay.</t>
-        </is>
-      </c>
-      <c r="C351" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Voluntary Response] Uh and then I validate it just to align with the the technical specifications.</t>
+        </is>
+      </c>
+      <c r="C351" s="11" t="inlineStr"/>
       <c r="D351" s="11" t="inlineStr"/>
       <c r="E351" s="11" t="inlineStr"/>
       <c r="F351" s="11" t="inlineStr"/>
-      <c r="G351" s="11" t="inlineStr"/>
+      <c r="G351" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H351" s="12" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="9" t="inlineStr">
         <is>
-          <t>72:47</t>
+          <t>68:48</t>
         </is>
       </c>
       <c r="B352" s="10" t="inlineStr">
         <is>
-          <t>[Comment] DIY was misleaded by the because I'm here in Korea and I had the SK that is doing that. That's maybe I find myself and I found them.</t>
-        </is>
-      </c>
-      <c r="C352" s="9" t="n">
-        <v>6</v>
-      </c>
+          <t>[Voluntary Response] And then I go to technology coaching.</t>
+        </is>
+      </c>
+      <c r="C352" s="11" t="inlineStr"/>
       <c r="D352" s="11" t="inlineStr"/>
       <c r="E352" s="11" t="inlineStr"/>
       <c r="F352" s="11" t="inlineStr"/>
-      <c r="G352" s="11" t="inlineStr"/>
+      <c r="G352" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H352" s="12" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="9" t="inlineStr">
         <is>
-          <t>73:39</t>
+          <t>68:52</t>
         </is>
       </c>
       <c r="B353" s="10" t="inlineStr">
         <is>
-          <t>[Comment] [laughter]</t>
-        </is>
-      </c>
-      <c r="C353" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Voluntary Response] So this is the here in Korea I've searched, and in fact, it's the</t>
+        </is>
+      </c>
+      <c r="C353" s="11" t="inlineStr"/>
       <c r="D353" s="11" t="inlineStr"/>
       <c r="E353" s="11" t="inlineStr"/>
       <c r="F353" s="11" t="inlineStr"/>
-      <c r="G353" s="11" t="inlineStr"/>
+      <c r="G353" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H353" s="12" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="9" t="inlineStr">
         <is>
-          <t>74:25</t>
+          <t>69:24</t>
         </is>
       </c>
       <c r="B354" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Other things are most impending process, all activities, I think I see</t>
-        </is>
-      </c>
-      <c r="C354" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] But what I saw from the website.</t>
+        </is>
+      </c>
+      <c r="C354" s="11" t="inlineStr"/>
       <c r="D354" s="11" t="inlineStr"/>
       <c r="E354" s="11" t="inlineStr"/>
       <c r="F354" s="11" t="inlineStr"/>
-      <c r="G354" s="11" t="inlineStr"/>
+      <c r="G354" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H354" s="12" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="9" t="inlineStr">
         <is>
-          <t>75:07</t>
+          <t>70:00</t>
         </is>
       </c>
       <c r="B355" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So if like they say brainstorm,</t>
-        </is>
-      </c>
-      <c r="C355" s="11" t="inlineStr"/>
+          <t>[Comment] And then, uh, Kisa has the source of the regression and whatever, we're gonna mark from there.</t>
+        </is>
+      </c>
+      <c r="C355" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D355" s="11" t="inlineStr"/>
       <c r="E355" s="11" t="inlineStr"/>
       <c r="F355" s="11" t="inlineStr"/>
-      <c r="G355" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G355" s="11" t="inlineStr"/>
       <c r="H355" s="12" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="9" t="inlineStr">
         <is>
-          <t>76:15</t>
+          <t>70:09</t>
         </is>
       </c>
       <c r="B356" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah, my ICT already, I have to.</t>
-        </is>
-      </c>
-      <c r="C356" s="11" t="inlineStr"/>
+          <t>[Comment] And then I go to technology exploitation.</t>
+        </is>
+      </c>
+      <c r="C356" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D356" s="11" t="inlineStr"/>
       <c r="E356" s="11" t="inlineStr"/>
       <c r="F356" s="11" t="inlineStr"/>
-      <c r="G356" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G356" s="11" t="inlineStr"/>
       <c r="H356" s="12" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="9" t="inlineStr">
         <is>
-          <t>76:22</t>
+          <t>70:20</t>
         </is>
       </c>
       <c r="B357" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I try to benchmark on the other countries.</t>
-        </is>
-      </c>
-      <c r="C357" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] Yeah, this is ongoing. that's what he told me.</t>
+        </is>
+      </c>
+      <c r="C357" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D357" s="11" t="inlineStr"/>
       <c r="E357" s="11" t="inlineStr"/>
       <c r="F357" s="11" t="inlineStr"/>
-      <c r="G357" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G357" s="11" t="inlineStr"/>
       <c r="H357" s="12" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="9" t="inlineStr">
         <is>
-          <t>77:05</t>
+          <t>70:23</t>
         </is>
       </c>
       <c r="B358" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I think the PPT I shared in the evening.</t>
-        </is>
-      </c>
-      <c r="C358" s="11" t="inlineStr"/>
+          <t>[Comment] So assessing the context of</t>
+        </is>
+      </c>
+      <c r="C358" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="D358" s="11" t="inlineStr"/>
       <c r="E358" s="11" t="inlineStr"/>
       <c r="F358" s="11" t="inlineStr"/>
-      <c r="G358" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G358" s="11" t="inlineStr"/>
       <c r="H358" s="12" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="9" t="inlineStr">
         <is>
-          <t>77:14</t>
+          <t>70:55</t>
         </is>
       </c>
       <c r="B359" s="10" t="inlineStr">
         <is>
-          <t>[Comment] The US, Europe, Asia.</t>
-        </is>
-      </c>
-      <c r="C359" s="11" t="inlineStr"/>
+          <t>[Comment] And then I will after discussing with the lady did you because, you know, I</t>
+        </is>
+      </c>
+      <c r="C359" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="D359" s="11" t="inlineStr"/>
       <c r="E359" s="11" t="inlineStr"/>
       <c r="F359" s="11" t="inlineStr"/>
-      <c r="G359" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G359" s="11" t="inlineStr"/>
       <c r="H359" s="12" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="9" t="inlineStr">
         <is>
-          <t>77:26</t>
+          <t>71:18</t>
         </is>
       </c>
       <c r="B360" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yes, professor.</t>
-        </is>
-      </c>
-      <c r="C360" s="11" t="inlineStr"/>
-      <c r="D360" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Voluntary Response] I really added the company for</t>
+        </is>
+      </c>
+      <c r="C360" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D360" s="11" t="inlineStr"/>
       <c r="E360" s="11" t="inlineStr"/>
       <c r="F360" s="11" t="inlineStr"/>
       <c r="G360" s="11" t="inlineStr"/>
@@ -7603,18 +7583,18 @@
     <row r="361">
       <c r="A361" s="9" t="inlineStr">
         <is>
-          <t>77:29</t>
+          <t>71:20</t>
         </is>
       </c>
       <c r="B361" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Yeah, thank you, professor.</t>
-        </is>
-      </c>
-      <c r="C361" s="11" t="inlineStr"/>
-      <c r="D361" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Comment] Or any other</t>
+        </is>
+      </c>
+      <c r="C361" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D361" s="11" t="inlineStr"/>
       <c r="E361" s="11" t="inlineStr"/>
       <c r="F361" s="11" t="inlineStr"/>
       <c r="G361" s="11" t="inlineStr"/>
@@ -7623,18 +7603,18 @@
     <row r="362">
       <c r="A362" s="9" t="inlineStr">
         <is>
-          <t>77:30</t>
+          <t>71:21</t>
         </is>
       </c>
       <c r="B362" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Um, after I knew the information that Chilaka already make uh similar of our project, I consultation with Professor Park. So there are there are a lot of data that I have to fulfill. So now it's already completed.</t>
-        </is>
-      </c>
-      <c r="C362" s="11" t="inlineStr"/>
-      <c r="D362" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] They had what they call mobile security.</t>
+        </is>
+      </c>
+      <c r="C362" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D362" s="11" t="inlineStr"/>
       <c r="E362" s="11" t="inlineStr"/>
       <c r="F362" s="11" t="inlineStr"/>
       <c r="G362" s="11" t="inlineStr"/>
@@ -7643,18 +7623,18 @@
     <row r="363">
       <c r="A363" s="9" t="inlineStr">
         <is>
-          <t>77:45</t>
+          <t>71:23</t>
         </is>
       </c>
       <c r="B363" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Um, uh first time I put a socio-economic data collections like I put uh collected poverty. I already make a map also.</t>
-        </is>
-      </c>
-      <c r="C363" s="11" t="inlineStr"/>
-      <c r="D363" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] But I saw it is on the like after download and you have it on the your smartphone. That's why I need</t>
+        </is>
+      </c>
+      <c r="C363" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D363" s="11" t="inlineStr"/>
       <c r="E363" s="11" t="inlineStr"/>
       <c r="F363" s="11" t="inlineStr"/>
       <c r="G363" s="11" t="inlineStr"/>
@@ -7663,18 +7643,18 @@
     <row r="364">
       <c r="A364" s="9" t="inlineStr">
         <is>
-          <t>77:53</t>
+          <t>71:31</t>
         </is>
       </c>
       <c r="B364" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Where is the poverty and also the electricity access uh and uh</t>
-        </is>
-      </c>
-      <c r="C364" s="11" t="inlineStr"/>
-      <c r="D364" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] It's good but in terms of my, you know, at the end of the day you need to think about the context of your country. That's why I said this is well good developed countries where everyone has an idea of smart for</t>
+        </is>
+      </c>
+      <c r="C364" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D364" s="11" t="inlineStr"/>
       <c r="E364" s="11" t="inlineStr"/>
       <c r="F364" s="11" t="inlineStr"/>
       <c r="G364" s="11" t="inlineStr"/>
@@ -7683,18 +7663,18 @@
     <row r="365">
       <c r="A365" s="9" t="inlineStr">
         <is>
-          <t>78:02</t>
+          <t>72:01</t>
         </is>
       </c>
       <c r="B365" s="10" t="inlineStr">
         <is>
-          <t>[Comment] uh the regulations, uh infrastructure and regulatory scans.</t>
-        </is>
-      </c>
-      <c r="C365" s="11" t="inlineStr"/>
-      <c r="D365" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] Okay.</t>
+        </is>
+      </c>
+      <c r="C365" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D365" s="11" t="inlineStr"/>
       <c r="E365" s="11" t="inlineStr"/>
       <c r="F365" s="11" t="inlineStr"/>
       <c r="G365" s="11" t="inlineStr"/>
@@ -7703,18 +7683,18 @@
     <row r="366">
       <c r="A366" s="9" t="inlineStr">
         <is>
-          <t>78:09</t>
+          <t>72:47</t>
         </is>
       </c>
       <c r="B366" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So um I put it also the demographic the demographic data.</t>
-        </is>
-      </c>
-      <c r="C366" s="11" t="inlineStr"/>
-      <c r="D366" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] DIY was misleaded by the because I'm here in Korea and I had the SK that is doing that. That's maybe I find myself and I found them.</t>
+        </is>
+      </c>
+      <c r="C366" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D366" s="11" t="inlineStr"/>
       <c r="E366" s="11" t="inlineStr"/>
       <c r="F366" s="11" t="inlineStr"/>
       <c r="G366" s="11" t="inlineStr"/>
@@ -7723,18 +7703,18 @@
     <row r="367">
       <c r="A367" s="9" t="inlineStr">
         <is>
-          <t>78:15</t>
+          <t>73:39</t>
         </is>
       </c>
       <c r="B367" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh the last time I told the professor is the data is already completed that I have to design the uh the design to give to the Infinithill.</t>
-        </is>
-      </c>
-      <c r="C367" s="11" t="inlineStr"/>
-      <c r="D367" s="9" t="n">
-        <v>5</v>
-      </c>
+          <t>[Comment] [laughter]</t>
+        </is>
+      </c>
+      <c r="C367" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D367" s="11" t="inlineStr"/>
       <c r="E367" s="11" t="inlineStr"/>
       <c r="F367" s="11" t="inlineStr"/>
       <c r="G367" s="11" t="inlineStr"/>
@@ -7743,18 +7723,18 @@
     <row r="368">
       <c r="A368" s="9" t="inlineStr">
         <is>
-          <t>78:27</t>
+          <t>74:25</t>
         </is>
       </c>
       <c r="B368" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Uh. So the data that I have to fulfill um already completed for the demographical, socio-economic and also</t>
-        </is>
-      </c>
-      <c r="C368" s="11" t="inlineStr"/>
-      <c r="D368" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Comment] Other things are most impending process, all activities, I think I see</t>
+        </is>
+      </c>
+      <c r="C368" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D368" s="11" t="inlineStr"/>
       <c r="E368" s="11" t="inlineStr"/>
       <c r="F368" s="11" t="inlineStr"/>
       <c r="G368" s="11" t="inlineStr"/>
@@ -7763,117 +7743,117 @@
     <row r="369">
       <c r="A369" s="9" t="inlineStr">
         <is>
-          <t>78:34</t>
+          <t>75:07</t>
         </is>
       </c>
       <c r="B369" s="10" t="inlineStr">
         <is>
-          <t>[Comment] It is actually same here.</t>
+          <t>[Comment] So if like they say brainstorm,</t>
         </is>
       </c>
       <c r="C369" s="11" t="inlineStr"/>
-      <c r="D369" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="D369" s="11" t="inlineStr"/>
       <c r="E369" s="11" t="inlineStr"/>
       <c r="F369" s="11" t="inlineStr"/>
-      <c r="G369" s="11" t="inlineStr"/>
+      <c r="G369" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H369" s="12" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="9" t="inlineStr">
         <is>
-          <t>78:37</t>
+          <t>76:15</t>
         </is>
       </c>
       <c r="B370" s="10" t="inlineStr">
         <is>
-          <t>[Comment] But uh uh not all I put in here. I already make a report to professor.</t>
+          <t>[Comment] Yeah, my ICT already, I have to.</t>
         </is>
       </c>
       <c r="C370" s="11" t="inlineStr"/>
-      <c r="D370" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="D370" s="11" t="inlineStr"/>
       <c r="E370" s="11" t="inlineStr"/>
       <c r="F370" s="11" t="inlineStr"/>
-      <c r="G370" s="11" t="inlineStr"/>
+      <c r="G370" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H370" s="12" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="9" t="inlineStr">
         <is>
-          <t>78:45</t>
+          <t>76:22</t>
         </is>
       </c>
       <c r="B371" s="10" t="inlineStr">
         <is>
-          <t>[Comment] And also after that um uh the professor wants me to make kind of the designs to give to Infinithill Lab.</t>
+          <t>[Voluntary Response] I try to benchmark on the other countries.</t>
         </is>
       </c>
       <c r="C371" s="11" t="inlineStr"/>
-      <c r="D371" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="D371" s="11" t="inlineStr"/>
       <c r="E371" s="11" t="inlineStr"/>
       <c r="F371" s="11" t="inlineStr"/>
-      <c r="G371" s="11" t="inlineStr"/>
+      <c r="G371" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H371" s="12" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="9" t="inlineStr">
         <is>
-          <t>79:03</t>
+          <t>77:05</t>
         </is>
       </c>
       <c r="B372" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Infinithill Lab.</t>
+          <t>[Comment] I think the PPT I shared in the evening.</t>
         </is>
       </c>
       <c r="C372" s="11" t="inlineStr"/>
-      <c r="D372" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="D372" s="11" t="inlineStr"/>
       <c r="E372" s="11" t="inlineStr"/>
       <c r="F372" s="11" t="inlineStr"/>
-      <c r="G372" s="11" t="inlineStr"/>
+      <c r="G372" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H372" s="12" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="9" t="inlineStr">
         <is>
-          <t>79:04</t>
+          <t>77:14</t>
         </is>
       </c>
       <c r="B373" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Infinity Village.</t>
+          <t>[Comment] The US, Europe, Asia.</t>
         </is>
       </c>
       <c r="C373" s="11" t="inlineStr"/>
-      <c r="D373" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="D373" s="11" t="inlineStr"/>
       <c r="E373" s="11" t="inlineStr"/>
       <c r="F373" s="11" t="inlineStr"/>
-      <c r="G373" s="11" t="inlineStr"/>
+      <c r="G373" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H373" s="12" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="9" t="inlineStr">
         <is>
-          <t>79:05</t>
+          <t>77:26</t>
         </is>
       </c>
       <c r="B374" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And the Infinity Energy, Infinity Energy.</t>
+          <t>[Voluntary Response] Yes, professor.</t>
         </is>
       </c>
       <c r="C374" s="11" t="inlineStr"/>
       <c r="D374" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E374" s="11" t="inlineStr"/>
       <c r="F374" s="11" t="inlineStr"/>
@@ -7883,12 +7863,12 @@
     <row r="375">
       <c r="A375" s="9" t="inlineStr">
         <is>
-          <t>79:15</t>
+          <t>77:29</t>
         </is>
       </c>
       <c r="B375" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Um uh</t>
+          <t>[Voluntary Response] Yeah, thank you, professor.</t>
         </is>
       </c>
       <c r="C375" s="11" t="inlineStr"/>
@@ -7903,17 +7883,17 @@
     <row r="376">
       <c r="A376" s="9" t="inlineStr">
         <is>
-          <t>80:52</t>
+          <t>77:30</t>
         </is>
       </c>
       <c r="B376" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Uh as for uh Indonesian sides, I already talk also the PLNs.</t>
+          <t>[Comment] Um, after I knew the information that Chilaka already make uh similar of our project, I consultation with Professor Park. So there are there are a lot of data that I have to fulfill. So now it's already completed.</t>
         </is>
       </c>
       <c r="C376" s="11" t="inlineStr"/>
       <c r="D376" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E376" s="11" t="inlineStr"/>
       <c r="F376" s="11" t="inlineStr"/>
@@ -7923,17 +7903,17 @@
     <row r="377">
       <c r="A377" s="9" t="inlineStr">
         <is>
-          <t>81:08</t>
+          <t>77:45</t>
         </is>
       </c>
       <c r="B377" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Uh, because uh, uh, this, uh, that area has a, uh, equator area, so they, they will get a lot of energy from the solar.</t>
+          <t>[Comment] Um, uh first time I put a socio-economic data collections like I put uh collected poverty. I already make a map also.</t>
         </is>
       </c>
       <c r="C377" s="11" t="inlineStr"/>
       <c r="D377" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E377" s="11" t="inlineStr"/>
       <c r="F377" s="11" t="inlineStr"/>
@@ -7943,17 +7923,17 @@
     <row r="378">
       <c r="A378" s="9" t="inlineStr">
         <is>
-          <t>81:21</t>
+          <t>77:53</t>
         </is>
       </c>
       <c r="B378" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And also, uh, there are a lot of uh.</t>
+          <t>[Comment] Where is the poverty and also the electricity access uh and uh</t>
         </is>
       </c>
       <c r="C378" s="11" t="inlineStr"/>
       <c r="D378" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E378" s="11" t="inlineStr"/>
       <c r="F378" s="11" t="inlineStr"/>
@@ -7963,17 +7943,17 @@
     <row r="379">
       <c r="A379" s="9" t="inlineStr">
         <is>
-          <t>81:28</t>
+          <t>78:02</t>
         </is>
       </c>
       <c r="B379" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] So, uh,</t>
+          <t>[Comment] uh the regulations, uh infrastructure and regulatory scans.</t>
         </is>
       </c>
       <c r="C379" s="11" t="inlineStr"/>
       <c r="D379" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E379" s="11" t="inlineStr"/>
       <c r="F379" s="11" t="inlineStr"/>
@@ -7983,17 +7963,17 @@
     <row r="380">
       <c r="A380" s="9" t="inlineStr">
         <is>
-          <t>81:30</t>
+          <t>78:09</t>
         </is>
       </c>
       <c r="B380" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] uh, the, uh, PLN prefer to</t>
+          <t>[Comment] So um I put it also the demographic the demographic data.</t>
         </is>
       </c>
       <c r="C380" s="11" t="inlineStr"/>
       <c r="D380" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E380" s="11" t="inlineStr"/>
       <c r="F380" s="11" t="inlineStr"/>
@@ -8003,17 +7983,17 @@
     <row r="381">
       <c r="A381" s="9" t="inlineStr">
         <is>
-          <t>81:33</t>
+          <t>78:15</t>
         </is>
       </c>
       <c r="B381" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] uh, put the pilot project in the, uh, entity.</t>
+          <t>[Comment] Uh the last time I told the professor is the data is already completed that I have to design the uh the design to give to the Infinithill.</t>
         </is>
       </c>
       <c r="C381" s="11" t="inlineStr"/>
       <c r="D381" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E381" s="11" t="inlineStr"/>
       <c r="F381" s="11" t="inlineStr"/>
@@ -8023,17 +8003,17 @@
     <row r="382">
       <c r="A382" s="9" t="inlineStr">
         <is>
-          <t>81:36</t>
+          <t>78:27</t>
         </is>
       </c>
       <c r="B382" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And also, um, previously I already contacted the, the director of energy there.</t>
+          <t>[Comment] Uh. So the data that I have to fulfill um already completed for the demographical, socio-economic and also</t>
         </is>
       </c>
       <c r="C382" s="11" t="inlineStr"/>
       <c r="D382" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E382" s="11" t="inlineStr"/>
       <c r="F382" s="11" t="inlineStr"/>
@@ -8043,17 +8023,17 @@
     <row r="383">
       <c r="A383" s="9" t="inlineStr">
         <is>
-          <t>81:57</t>
+          <t>78:34</t>
         </is>
       </c>
       <c r="B383" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because I don't have, I didn't review your.</t>
+          <t>[Comment] It is actually same here.</t>
         </is>
       </c>
       <c r="C383" s="11" t="inlineStr"/>
       <c r="D383" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E383" s="11" t="inlineStr"/>
       <c r="F383" s="11" t="inlineStr"/>
@@ -8063,17 +8043,17 @@
     <row r="384">
       <c r="A384" s="9" t="inlineStr">
         <is>
-          <t>82:14</t>
+          <t>78:37</t>
         </is>
       </c>
       <c r="B384" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Ah, okay.</t>
+          <t>[Comment] But uh uh not all I put in here. I already make a report to professor.</t>
         </is>
       </c>
       <c r="C384" s="11" t="inlineStr"/>
       <c r="D384" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E384" s="11" t="inlineStr"/>
       <c r="F384" s="11" t="inlineStr"/>
@@ -8083,17 +8063,17 @@
     <row r="385">
       <c r="A385" s="9" t="inlineStr">
         <is>
-          <t>82:30</t>
+          <t>78:45</t>
         </is>
       </c>
       <c r="B385" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Yeah, uh, uh.</t>
+          <t>[Comment] And also after that um uh the professor wants me to make kind of the designs to give to Infinithill Lab.</t>
         </is>
       </c>
       <c r="C385" s="11" t="inlineStr"/>
       <c r="D385" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E385" s="11" t="inlineStr"/>
       <c r="F385" s="11" t="inlineStr"/>
@@ -8103,17 +8083,17 @@
     <row r="386">
       <c r="A386" s="9" t="inlineStr">
         <is>
-          <t>82:58</t>
+          <t>79:03</t>
         </is>
       </c>
       <c r="B386" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And then, uh the person, uh will be the pilot project. So, uh,</t>
+          <t>[Voluntary Response] Infinithill Lab.</t>
         </is>
       </c>
       <c r="C386" s="11" t="inlineStr"/>
       <c r="D386" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E386" s="11" t="inlineStr"/>
       <c r="F386" s="11" t="inlineStr"/>
@@ -8123,17 +8103,17 @@
     <row r="387">
       <c r="A387" s="9" t="inlineStr">
         <is>
-          <t>83:09</t>
+          <t>79:04</t>
         </is>
       </c>
       <c r="B387" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Also the, the, the the area of solar PV. Okay.</t>
+          <t>[Voluntary Response] Infinity Village.</t>
         </is>
       </c>
       <c r="C387" s="11" t="inlineStr"/>
       <c r="D387" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E387" s="11" t="inlineStr"/>
       <c r="F387" s="11" t="inlineStr"/>
@@ -8143,238 +8123,238 @@
     <row r="388">
       <c r="A388" s="9" t="inlineStr">
         <is>
-          <t>84:14</t>
+          <t>79:05</t>
         </is>
       </c>
       <c r="B388" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] At the demand side you need to prove if the</t>
+          <t>[Voluntary Response] And the Infinity Energy, Infinity Energy.</t>
         </is>
       </c>
       <c r="C388" s="11" t="inlineStr"/>
-      <c r="D388" s="11" t="inlineStr"/>
+      <c r="D388" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E388" s="11" t="inlineStr"/>
       <c r="F388" s="11" t="inlineStr"/>
-      <c r="G388" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G388" s="11" t="inlineStr"/>
       <c r="H388" s="12" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="9" t="inlineStr">
         <is>
-          <t>84:19</t>
+          <t>79:15</t>
         </is>
       </c>
       <c r="B389" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] the problem you are talking about</t>
+          <t>[Comment] Um uh</t>
         </is>
       </c>
       <c r="C389" s="11" t="inlineStr"/>
-      <c r="D389" s="11" t="inlineStr"/>
+      <c r="D389" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="E389" s="11" t="inlineStr"/>
       <c r="F389" s="11" t="inlineStr"/>
-      <c r="G389" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G389" s="11" t="inlineStr"/>
       <c r="H389" s="12" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="9" t="inlineStr">
         <is>
-          <t>84:21</t>
+          <t>80:52</t>
         </is>
       </c>
       <c r="B390" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] is real, is is it real to be invested by the</t>
+          <t>[Voluntary Response] Uh as for uh Indonesian sides, I already talk also the PLNs.</t>
         </is>
       </c>
       <c r="C390" s="11" t="inlineStr"/>
-      <c r="D390" s="11" t="inlineStr"/>
+      <c r="D390" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E390" s="11" t="inlineStr"/>
       <c r="F390" s="11" t="inlineStr"/>
-      <c r="G390" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G390" s="11" t="inlineStr"/>
       <c r="H390" s="12" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="9" t="inlineStr">
         <is>
-          <t>84:29</t>
+          <t>81:08</t>
         </is>
       </c>
       <c r="B391" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] maybe even demand, is it the real problem that the government can invest money or Somebody.</t>
+          <t>[Voluntary Response] Uh, because uh, uh, this, uh, that area has a, uh, equator area, so they, they will get a lot of energy from the solar.</t>
         </is>
       </c>
       <c r="C391" s="11" t="inlineStr"/>
-      <c r="D391" s="11" t="inlineStr"/>
+      <c r="D391" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E391" s="11" t="inlineStr"/>
       <c r="F391" s="11" t="inlineStr"/>
-      <c r="G391" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G391" s="11" t="inlineStr"/>
       <c r="H391" s="12" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="9" t="inlineStr">
         <is>
-          <t>84:35</t>
+          <t>81:21</t>
         </is>
       </c>
       <c r="B392" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Any donor? That's the demand side.</t>
+          <t>[Voluntary Response] And also, uh, there are a lot of uh.</t>
         </is>
       </c>
       <c r="C392" s="11" t="inlineStr"/>
-      <c r="D392" s="11" t="inlineStr"/>
+      <c r="D392" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E392" s="11" t="inlineStr"/>
       <c r="F392" s="11" t="inlineStr"/>
-      <c r="G392" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G392" s="11" t="inlineStr"/>
       <c r="H392" s="12" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="9" t="inlineStr">
         <is>
-          <t>84:37</t>
+          <t>81:28</t>
         </is>
       </c>
       <c r="B393" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] You need to show that they calculate the mathematics, the loopholes in the policies and whatever.</t>
+          <t>[Voluntary Response] So, uh,</t>
         </is>
       </c>
       <c r="C393" s="11" t="inlineStr"/>
-      <c r="D393" s="11" t="inlineStr"/>
+      <c r="D393" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="E393" s="11" t="inlineStr"/>
       <c r="F393" s="11" t="inlineStr"/>
-      <c r="G393" s="9" t="n">
-        <v>4</v>
-      </c>
+      <c r="G393" s="11" t="inlineStr"/>
       <c r="H393" s="12" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="9" t="inlineStr">
         <is>
-          <t>84:43</t>
+          <t>81:30</t>
         </is>
       </c>
       <c r="B394" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] And then on the supply side,</t>
+          <t>[Voluntary Response] uh, the, uh, PLN prefer to</t>
         </is>
       </c>
       <c r="C394" s="11" t="inlineStr"/>
-      <c r="D394" s="11" t="inlineStr"/>
+      <c r="D394" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E394" s="11" t="inlineStr"/>
       <c r="F394" s="11" t="inlineStr"/>
-      <c r="G394" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G394" s="11" t="inlineStr"/>
       <c r="H394" s="12" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="9" t="inlineStr">
         <is>
-          <t>84:45</t>
+          <t>81:33</t>
         </is>
       </c>
       <c r="B395" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] I think</t>
+          <t>[Voluntary Response] uh, put the pilot project in the, uh, entity.</t>
         </is>
       </c>
       <c r="C395" s="11" t="inlineStr"/>
-      <c r="D395" s="11" t="inlineStr"/>
+      <c r="D395" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E395" s="11" t="inlineStr"/>
       <c r="F395" s="11" t="inlineStr"/>
-      <c r="G395" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G395" s="11" t="inlineStr"/>
       <c r="H395" s="12" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="9" t="inlineStr">
         <is>
-          <t>84:47</t>
+          <t>81:36</t>
         </is>
       </c>
       <c r="B396" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] this is the</t>
+          <t>[Voluntary Response] And also, um, previously I already contacted the, the director of energy there.</t>
         </is>
       </c>
       <c r="C396" s="11" t="inlineStr"/>
-      <c r="D396" s="11" t="inlineStr"/>
+      <c r="D396" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E396" s="11" t="inlineStr"/>
       <c r="F396" s="11" t="inlineStr"/>
-      <c r="G396" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G396" s="11" t="inlineStr"/>
       <c r="H396" s="12" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="9" t="inlineStr">
         <is>
-          <t>84:51</t>
+          <t>81:57</t>
         </is>
       </c>
       <c r="B397" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] the the one who going to give you the the solution.</t>
+          <t>[Comment] Because I don't have, I didn't review your.</t>
         </is>
       </c>
       <c r="C397" s="11" t="inlineStr"/>
-      <c r="D397" s="11" t="inlineStr"/>
+      <c r="D397" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E397" s="11" t="inlineStr"/>
       <c r="F397" s="11" t="inlineStr"/>
-      <c r="G397" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="G397" s="11" t="inlineStr"/>
       <c r="H397" s="12" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="9" t="inlineStr">
         <is>
-          <t>84:57</t>
+          <t>82:14</t>
         </is>
       </c>
       <c r="B398" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Is is is the</t>
+          <t>[Voluntary Response] Ah, okay.</t>
         </is>
       </c>
       <c r="C398" s="11" t="inlineStr"/>
-      <c r="D398" s="11" t="inlineStr"/>
+      <c r="D398" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="E398" s="11" t="inlineStr"/>
       <c r="F398" s="11" t="inlineStr"/>
-      <c r="G398" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="G398" s="11" t="inlineStr"/>
       <c r="H398" s="12" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="9" t="inlineStr">
         <is>
-          <t>85:09</t>
+          <t>82:30</t>
         </is>
       </c>
       <c r="B399" s="10" t="inlineStr">
         <is>
-          <t>[Comment] that's how I understand it.</t>
-        </is>
-      </c>
-      <c r="C399" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D399" s="11" t="inlineStr"/>
+          <t>[Comment] Yeah, uh, uh.</t>
+        </is>
+      </c>
+      <c r="C399" s="11" t="inlineStr"/>
+      <c r="D399" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="E399" s="11" t="inlineStr"/>
       <c r="F399" s="11" t="inlineStr"/>
       <c r="G399" s="11" t="inlineStr"/>
@@ -8383,18 +8363,18 @@
     <row r="400">
       <c r="A400" s="9" t="inlineStr">
         <is>
-          <t>85:22</t>
+          <t>82:58</t>
         </is>
       </c>
       <c r="B400" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] preliminary synthesis because it is the opportunity generation.</t>
-        </is>
-      </c>
-      <c r="C400" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D400" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] And then, uh the person, uh will be the pilot project. So, uh,</t>
+        </is>
+      </c>
+      <c r="C400" s="11" t="inlineStr"/>
+      <c r="D400" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E400" s="11" t="inlineStr"/>
       <c r="F400" s="11" t="inlineStr"/>
       <c r="G400" s="11" t="inlineStr"/>
@@ -8403,18 +8383,18 @@
     <row r="401">
       <c r="A401" s="9" t="inlineStr">
         <is>
-          <t>85:36</t>
+          <t>83:09</t>
         </is>
       </c>
       <c r="B401" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] The last part or one to three?</t>
-        </is>
-      </c>
-      <c r="C401" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="D401" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] Also the, the, the the area of solar PV. Okay.</t>
+        </is>
+      </c>
+      <c r="C401" s="11" t="inlineStr"/>
+      <c r="D401" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="E401" s="11" t="inlineStr"/>
       <c r="F401" s="11" t="inlineStr"/>
       <c r="G401" s="11" t="inlineStr"/>
@@ -8423,12 +8403,12 @@
     <row r="402">
       <c r="A402" s="9" t="inlineStr">
         <is>
-          <t>87:56</t>
+          <t>84:14</t>
         </is>
       </c>
       <c r="B402" s="10" t="inlineStr">
         <is>
-          <t>[Comment] So, trial version.</t>
+          <t>[Voluntary Response] At the demand side you need to prove if the</t>
         </is>
       </c>
       <c r="C402" s="11" t="inlineStr"/>
@@ -8436,39 +8416,39 @@
       <c r="E402" s="11" t="inlineStr"/>
       <c r="F402" s="11" t="inlineStr"/>
       <c r="G402" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H402" s="12" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="9" t="inlineStr">
         <is>
-          <t>87:57</t>
+          <t>84:19</t>
         </is>
       </c>
       <c r="B403" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Hmm.</t>
-        </is>
-      </c>
-      <c r="C403" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Voluntary Response] the problem you are talking about</t>
+        </is>
+      </c>
+      <c r="C403" s="11" t="inlineStr"/>
       <c r="D403" s="11" t="inlineStr"/>
       <c r="E403" s="11" t="inlineStr"/>
       <c r="F403" s="11" t="inlineStr"/>
-      <c r="G403" s="11" t="inlineStr"/>
+      <c r="G403" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H403" s="12" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="9" t="inlineStr">
         <is>
-          <t>87:58</t>
+          <t>84:21</t>
         </is>
       </c>
       <c r="B404" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Trial, trial version.</t>
+          <t>[Voluntary Response] is real, is is it real to be invested by the</t>
         </is>
       </c>
       <c r="C404" s="11" t="inlineStr"/>
@@ -8476,59 +8456,59 @@
       <c r="E404" s="11" t="inlineStr"/>
       <c r="F404" s="11" t="inlineStr"/>
       <c r="G404" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H404" s="12" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="9" t="inlineStr">
         <is>
-          <t>89:31</t>
+          <t>84:29</t>
         </is>
       </c>
       <c r="B405" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] You said summer, meaning we continue the project in summer?</t>
-        </is>
-      </c>
-      <c r="C405" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Voluntary Response] maybe even demand, is it the real problem that the government can invest money or Somebody.</t>
+        </is>
+      </c>
+      <c r="C405" s="11" t="inlineStr"/>
       <c r="D405" s="11" t="inlineStr"/>
       <c r="E405" s="11" t="inlineStr"/>
       <c r="F405" s="11" t="inlineStr"/>
-      <c r="G405" s="11" t="inlineStr"/>
+      <c r="G405" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="H405" s="12" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="9" t="inlineStr">
         <is>
-          <t>89:36</t>
+          <t>84:35</t>
         </is>
       </c>
       <c r="B406" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] You think there's no rest vacation?</t>
-        </is>
-      </c>
-      <c r="C406" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Voluntary Response] Any donor? That's the demand side.</t>
+        </is>
+      </c>
+      <c r="C406" s="11" t="inlineStr"/>
       <c r="D406" s="11" t="inlineStr"/>
       <c r="E406" s="11" t="inlineStr"/>
       <c r="F406" s="11" t="inlineStr"/>
-      <c r="G406" s="11" t="inlineStr"/>
+      <c r="G406" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H406" s="12" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="9" t="inlineStr">
         <is>
-          <t>89:41</t>
+          <t>84:37</t>
         </is>
       </c>
       <c r="B407" s="10" t="inlineStr">
         <is>
-          <t>[Comment] July, August.</t>
+          <t>[Voluntary Response] You need to show that they calculate the mathematics, the loopholes in the policies and whatever.</t>
         </is>
       </c>
       <c r="C407" s="11" t="inlineStr"/>
@@ -8536,19 +8516,19 @@
       <c r="E407" s="11" t="inlineStr"/>
       <c r="F407" s="11" t="inlineStr"/>
       <c r="G407" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H407" s="12" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="9" t="inlineStr">
         <is>
-          <t>89:49</t>
+          <t>84:43</t>
         </is>
       </c>
       <c r="B408" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] Summer?</t>
+          <t>[Voluntary Response] And then on the supply side,</t>
         </is>
       </c>
       <c r="C408" s="11" t="inlineStr"/>
@@ -8563,12 +8543,12 @@
     <row r="409">
       <c r="A409" s="9" t="inlineStr">
         <is>
-          <t>90:00</t>
+          <t>84:45</t>
         </is>
       </c>
       <c r="B409" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I forgot.</t>
+          <t>[Voluntary Response] I think</t>
         </is>
       </c>
       <c r="C409" s="11" t="inlineStr"/>
@@ -8576,39 +8556,39 @@
       <c r="E409" s="11" t="inlineStr"/>
       <c r="F409" s="11" t="inlineStr"/>
       <c r="G409" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H409" s="12" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="9" t="inlineStr">
         <is>
-          <t>90:01</t>
+          <t>84:47</t>
         </is>
       </c>
       <c r="B410" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because for me I already buy the ticket to</t>
-        </is>
-      </c>
-      <c r="C410" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Voluntary Response] this is the</t>
+        </is>
+      </c>
+      <c r="C410" s="11" t="inlineStr"/>
       <c r="D410" s="11" t="inlineStr"/>
       <c r="E410" s="11" t="inlineStr"/>
       <c r="F410" s="11" t="inlineStr"/>
-      <c r="G410" s="11" t="inlineStr"/>
+      <c r="G410" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H410" s="12" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="9" t="inlineStr">
         <is>
-          <t>90:03</t>
+          <t>84:51</t>
         </is>
       </c>
       <c r="B411" s="10" t="inlineStr">
         <is>
-          <t>[Comment] I forgot.</t>
+          <t>[Voluntary Response] the the one who going to give you the the solution.</t>
         </is>
       </c>
       <c r="C411" s="11" t="inlineStr"/>
@@ -8616,45 +8596,45 @@
       <c r="E411" s="11" t="inlineStr"/>
       <c r="F411" s="11" t="inlineStr"/>
       <c r="G411" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H411" s="12" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="9" t="inlineStr">
         <is>
-          <t>90:05</t>
+          <t>84:57</t>
         </is>
       </c>
       <c r="B412" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Because for me I already buy the ticket to</t>
-        </is>
-      </c>
-      <c r="C412" s="9" t="n">
-        <v>4</v>
-      </c>
+          <t>[Voluntary Response] Is is is the</t>
+        </is>
+      </c>
+      <c r="C412" s="11" t="inlineStr"/>
       <c r="D412" s="11" t="inlineStr"/>
       <c r="E412" s="11" t="inlineStr"/>
       <c r="F412" s="11" t="inlineStr"/>
-      <c r="G412" s="11" t="inlineStr"/>
+      <c r="G412" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H412" s="12" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="9" t="inlineStr">
         <is>
-          <t>90:10</t>
+          <t>85:09</t>
         </is>
       </c>
       <c r="B413" s="10" t="inlineStr">
         <is>
-          <t>[Comment] They know.</t>
-        </is>
-      </c>
-      <c r="C413" s="11" t="inlineStr"/>
-      <c r="D413" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Comment] that's how I understand it.</t>
+        </is>
+      </c>
+      <c r="C413" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D413" s="11" t="inlineStr"/>
       <c r="E413" s="11" t="inlineStr"/>
       <c r="F413" s="11" t="inlineStr"/>
       <c r="G413" s="11" t="inlineStr"/>
@@ -8663,19 +8643,19 @@
     <row r="414">
       <c r="A414" s="9" t="inlineStr">
         <is>
-          <t>90:12</t>
+          <t>85:22</t>
         </is>
       </c>
       <c r="B414" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] We we inform, right?</t>
-        </is>
-      </c>
-      <c r="C414" s="11" t="inlineStr"/>
+          <t>[Voluntary Response] preliminary synthesis because it is the opportunity generation.</t>
+        </is>
+      </c>
+      <c r="C414" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D414" s="11" t="inlineStr"/>
-      <c r="E414" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="E414" s="11" t="inlineStr"/>
       <c r="F414" s="11" t="inlineStr"/>
       <c r="G414" s="11" t="inlineStr"/>
       <c r="H414" s="12" t="inlineStr"/>
@@ -8683,16 +8663,16 @@
     <row r="415">
       <c r="A415" s="9" t="inlineStr">
         <is>
-          <t>90:22</t>
+          <t>85:36</t>
         </is>
       </c>
       <c r="B415" s="10" t="inlineStr">
         <is>
-          <t>[Comment] 20, 21 days.</t>
+          <t>[Question to Professor] The last part or one to three?</t>
         </is>
       </c>
       <c r="C415" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D415" s="11" t="inlineStr"/>
       <c r="E415" s="11" t="inlineStr"/>
@@ -8703,36 +8683,36 @@
     <row r="416">
       <c r="A416" s="9" t="inlineStr">
         <is>
-          <t>90:24</t>
+          <t>87:56</t>
         </is>
       </c>
       <c r="B416" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Outside of the country.</t>
-        </is>
-      </c>
-      <c r="C416" s="9" t="n">
-        <v>3</v>
-      </c>
+          <t>[Comment] So, trial version.</t>
+        </is>
+      </c>
+      <c r="C416" s="11" t="inlineStr"/>
       <c r="D416" s="11" t="inlineStr"/>
       <c r="E416" s="11" t="inlineStr"/>
       <c r="F416" s="11" t="inlineStr"/>
-      <c r="G416" s="11" t="inlineStr"/>
+      <c r="G416" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H416" s="12" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="9" t="inlineStr">
         <is>
-          <t>90:32</t>
+          <t>87:57</t>
         </is>
       </c>
       <c r="B417" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Two weeks and two weeks.</t>
+          <t>[Comment] Hmm.</t>
         </is>
       </c>
       <c r="C417" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D417" s="11" t="inlineStr"/>
       <c r="E417" s="11" t="inlineStr"/>
@@ -8743,12 +8723,12 @@
     <row r="418">
       <c r="A418" s="9" t="inlineStr">
         <is>
-          <t>90:38</t>
+          <t>87:58</t>
         </is>
       </c>
       <c r="B418" s="10" t="inlineStr">
         <is>
-          <t>[Comment] No problem.</t>
+          <t>[Comment] Trial, trial version.</t>
         </is>
       </c>
       <c r="C418" s="11" t="inlineStr"/>
@@ -8763,16 +8743,16 @@
     <row r="419">
       <c r="A419" s="9" t="inlineStr">
         <is>
-          <t>91:03</t>
+          <t>89:31</t>
         </is>
       </c>
       <c r="B419" s="10" t="inlineStr">
         <is>
-          <t>[Comment] Maybe just you give it myself, uh, because I planned uh to go with the higher boss during my visit in Indonesia.</t>
+          <t>[Question to Professor] You said summer, meaning we continue the project in summer?</t>
         </is>
       </c>
       <c r="C419" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D419" s="11" t="inlineStr"/>
       <c r="E419" s="11" t="inlineStr"/>
@@ -8783,16 +8763,16 @@
     <row r="420">
       <c r="A420" s="9" t="inlineStr">
         <is>
-          <t>92:54</t>
+          <t>89:36</t>
         </is>
       </c>
       <c r="B420" s="10" t="inlineStr">
         <is>
-          <t>[Voluntary Response] Five.</t>
+          <t>[Question to Professor] You think there's no rest vacation?</t>
         </is>
       </c>
       <c r="C420" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D420" s="11" t="inlineStr"/>
       <c r="E420" s="11" t="inlineStr"/>
@@ -8803,12 +8783,12 @@
     <row r="421">
       <c r="A421" s="9" t="inlineStr">
         <is>
-          <t>92:56</t>
+          <t>89:41</t>
         </is>
       </c>
       <c r="B421" s="10" t="inlineStr">
         <is>
-          <t>[Comment] 10 minutes.</t>
+          <t>[Comment] July, August.</t>
         </is>
       </c>
       <c r="C421" s="11" t="inlineStr"/>
@@ -8823,387 +8803,1427 @@
     <row r="422">
       <c r="A422" s="9" t="inlineStr">
         <is>
-          <t>92:57</t>
+          <t>89:49</t>
         </is>
       </c>
       <c r="B422" s="10" t="inlineStr">
         <is>
-          <t>[Comment] 10 minutes, okay.</t>
-        </is>
-      </c>
-      <c r="C422" s="9" t="n">
-        <v>2</v>
-      </c>
+          <t>[Question to Professor] Summer?</t>
+        </is>
+      </c>
+      <c r="C422" s="11" t="inlineStr"/>
       <c r="D422" s="11" t="inlineStr"/>
       <c r="E422" s="11" t="inlineStr"/>
       <c r="F422" s="11" t="inlineStr"/>
-      <c r="G422" s="11" t="inlineStr"/>
+      <c r="G422" s="9" t="n">
+        <v>3</v>
+      </c>
       <c r="H422" s="12" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="9" t="inlineStr">
         <is>
-          <t>92:58</t>
+          <t>90:00</t>
         </is>
       </c>
       <c r="B423" s="10" t="inlineStr">
         <is>
-          <t>[Comment] That that that'll be good.</t>
+          <t>[Comment] I forgot.</t>
         </is>
       </c>
       <c r="C423" s="11" t="inlineStr"/>
-      <c r="D423" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="D423" s="11" t="inlineStr"/>
       <c r="E423" s="11" t="inlineStr"/>
       <c r="F423" s="11" t="inlineStr"/>
-      <c r="G423" s="11" t="inlineStr"/>
+      <c r="G423" s="9" t="n">
+        <v>2</v>
+      </c>
       <c r="H423" s="12" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="9" t="inlineStr">
         <is>
-          <t>92:59</t>
+          <t>90:01</t>
         </is>
       </c>
       <c r="B424" s="10" t="inlineStr">
         <is>
-          <t>[Question to Professor] What are we doing?</t>
-        </is>
-      </c>
-      <c r="C424" s="11" t="inlineStr"/>
+          <t>[Comment] Because for me I already buy the ticket to</t>
+        </is>
+      </c>
+      <c r="C424" s="9" t="n">
+        <v>4</v>
+      </c>
       <c r="D424" s="11" t="inlineStr"/>
-      <c r="E424" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="E424" s="11" t="inlineStr"/>
       <c r="F424" s="11" t="inlineStr"/>
       <c r="G424" s="11" t="inlineStr"/>
       <c r="H424" s="12" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="B425" s="14" t="inlineStr">
+      <c r="A425" s="9" t="inlineStr">
+        <is>
+          <t>90:03</t>
+        </is>
+      </c>
+      <c r="B425" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] I forgot.</t>
+        </is>
+      </c>
+      <c r="C425" s="11" t="inlineStr"/>
+      <c r="D425" s="11" t="inlineStr"/>
+      <c r="E425" s="11" t="inlineStr"/>
+      <c r="F425" s="11" t="inlineStr"/>
+      <c r="G425" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H425" s="12" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="9" t="inlineStr">
+        <is>
+          <t>90:05</t>
+        </is>
+      </c>
+      <c r="B426" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Because for me I already buy the ticket to</t>
+        </is>
+      </c>
+      <c r="C426" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D426" s="11" t="inlineStr"/>
+      <c r="E426" s="11" t="inlineStr"/>
+      <c r="F426" s="11" t="inlineStr"/>
+      <c r="G426" s="11" t="inlineStr"/>
+      <c r="H426" s="12" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="9" t="inlineStr">
+        <is>
+          <t>90:10</t>
+        </is>
+      </c>
+      <c r="B427" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] They know.</t>
+        </is>
+      </c>
+      <c r="C427" s="11" t="inlineStr"/>
+      <c r="D427" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E427" s="11" t="inlineStr"/>
+      <c r="F427" s="11" t="inlineStr"/>
+      <c r="G427" s="11" t="inlineStr"/>
+      <c r="H427" s="12" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="9" t="inlineStr">
+        <is>
+          <t>90:12</t>
+        </is>
+      </c>
+      <c r="B428" s="10" t="inlineStr">
+        <is>
+          <t>[Question to Professor] We we inform, right?</t>
+        </is>
+      </c>
+      <c r="C428" s="11" t="inlineStr"/>
+      <c r="D428" s="11" t="inlineStr"/>
+      <c r="E428" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F428" s="11" t="inlineStr"/>
+      <c r="G428" s="11" t="inlineStr"/>
+      <c r="H428" s="12" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="9" t="inlineStr">
+        <is>
+          <t>90:22</t>
+        </is>
+      </c>
+      <c r="B429" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] 20, 21 days.</t>
+        </is>
+      </c>
+      <c r="C429" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D429" s="11" t="inlineStr"/>
+      <c r="E429" s="11" t="inlineStr"/>
+      <c r="F429" s="11" t="inlineStr"/>
+      <c r="G429" s="11" t="inlineStr"/>
+      <c r="H429" s="12" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="9" t="inlineStr">
+        <is>
+          <t>90:24</t>
+        </is>
+      </c>
+      <c r="B430" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Outside of the country.</t>
+        </is>
+      </c>
+      <c r="C430" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D430" s="11" t="inlineStr"/>
+      <c r="E430" s="11" t="inlineStr"/>
+      <c r="F430" s="11" t="inlineStr"/>
+      <c r="G430" s="11" t="inlineStr"/>
+      <c r="H430" s="12" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="9" t="inlineStr">
+        <is>
+          <t>90:32</t>
+        </is>
+      </c>
+      <c r="B431" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Two weeks and two weeks.</t>
+        </is>
+      </c>
+      <c r="C431" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D431" s="11" t="inlineStr"/>
+      <c r="E431" s="11" t="inlineStr"/>
+      <c r="F431" s="11" t="inlineStr"/>
+      <c r="G431" s="11" t="inlineStr"/>
+      <c r="H431" s="12" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="9" t="inlineStr">
+        <is>
+          <t>90:38</t>
+        </is>
+      </c>
+      <c r="B432" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] No problem.</t>
+        </is>
+      </c>
+      <c r="C432" s="11" t="inlineStr"/>
+      <c r="D432" s="11" t="inlineStr"/>
+      <c r="E432" s="11" t="inlineStr"/>
+      <c r="F432" s="11" t="inlineStr"/>
+      <c r="G432" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H432" s="12" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="9" t="inlineStr">
+        <is>
+          <t>91:03</t>
+        </is>
+      </c>
+      <c r="B433" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Maybe just you give it myself, uh, because I planned uh to go with the higher boss during my visit in Indonesia.</t>
+        </is>
+      </c>
+      <c r="C433" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D433" s="11" t="inlineStr"/>
+      <c r="E433" s="11" t="inlineStr"/>
+      <c r="F433" s="11" t="inlineStr"/>
+      <c r="G433" s="11" t="inlineStr"/>
+      <c r="H433" s="12" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="9" t="inlineStr">
+        <is>
+          <t>92:54</t>
+        </is>
+      </c>
+      <c r="B434" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Five.</t>
+        </is>
+      </c>
+      <c r="C434" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D434" s="11" t="inlineStr"/>
+      <c r="E434" s="11" t="inlineStr"/>
+      <c r="F434" s="11" t="inlineStr"/>
+      <c r="G434" s="11" t="inlineStr"/>
+      <c r="H434" s="12" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="9" t="inlineStr">
+        <is>
+          <t>92:56</t>
+        </is>
+      </c>
+      <c r="B435" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] 10 minutes.</t>
+        </is>
+      </c>
+      <c r="C435" s="11" t="inlineStr"/>
+      <c r="D435" s="11" t="inlineStr"/>
+      <c r="E435" s="11" t="inlineStr"/>
+      <c r="F435" s="11" t="inlineStr"/>
+      <c r="G435" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H435" s="12" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="9" t="inlineStr">
+        <is>
+          <t>92:57</t>
+        </is>
+      </c>
+      <c r="B436" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] 10 minutes, okay.</t>
+        </is>
+      </c>
+      <c r="C436" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D436" s="11" t="inlineStr"/>
+      <c r="E436" s="11" t="inlineStr"/>
+      <c r="F436" s="11" t="inlineStr"/>
+      <c r="G436" s="11" t="inlineStr"/>
+      <c r="H436" s="12" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="9" t="inlineStr">
+        <is>
+          <t>92:58</t>
+        </is>
+      </c>
+      <c r="B437" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] That that that'll be good.</t>
+        </is>
+      </c>
+      <c r="C437" s="11" t="inlineStr"/>
+      <c r="D437" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E437" s="11" t="inlineStr"/>
+      <c r="F437" s="11" t="inlineStr"/>
+      <c r="G437" s="11" t="inlineStr"/>
+      <c r="H437" s="12" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="9" t="inlineStr">
+        <is>
+          <t>92:59</t>
+        </is>
+      </c>
+      <c r="B438" s="10" t="inlineStr">
+        <is>
+          <t>[Question to Professor] What are we doing?</t>
+        </is>
+      </c>
+      <c r="C438" s="11" t="inlineStr"/>
+      <c r="D438" s="11" t="inlineStr"/>
+      <c r="E438" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F438" s="11" t="inlineStr"/>
+      <c r="G438" s="11" t="inlineStr"/>
+      <c r="H438" s="12" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="9" t="inlineStr">
+        <is>
+          <t>100:51</t>
+        </is>
+      </c>
+      <c r="B439" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Because the difference between</t>
+        </is>
+      </c>
+      <c r="C439" s="11" t="inlineStr"/>
+      <c r="D439" s="11" t="inlineStr"/>
+      <c r="E439" s="11" t="inlineStr"/>
+      <c r="F439" s="11" t="inlineStr"/>
+      <c r="G439" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H439" s="12" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="9" t="inlineStr">
+        <is>
+          <t>101:27</t>
+        </is>
+      </c>
+      <c r="B440" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] The measure.</t>
+        </is>
+      </c>
+      <c r="C440" s="11" t="inlineStr"/>
+      <c r="D440" s="11" t="inlineStr"/>
+      <c r="E440" s="11" t="inlineStr"/>
+      <c r="F440" s="11" t="inlineStr"/>
+      <c r="G440" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H440" s="12" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="9" t="inlineStr">
+        <is>
+          <t>101:33</t>
+        </is>
+      </c>
+      <c r="B441" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] 90-60-90.</t>
+        </is>
+      </c>
+      <c r="C441" s="11" t="inlineStr"/>
+      <c r="D441" s="11" t="inlineStr"/>
+      <c r="E441" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F441" s="11" t="inlineStr"/>
+      <c r="G441" s="11" t="inlineStr"/>
+      <c r="H441" s="12" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="9" t="inlineStr">
+        <is>
+          <t>101:38</t>
+        </is>
+      </c>
+      <c r="B442" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] The measurement.</t>
+        </is>
+      </c>
+      <c r="C442" s="11" t="inlineStr"/>
+      <c r="D442" s="11" t="inlineStr"/>
+      <c r="E442" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F442" s="11" t="inlineStr"/>
+      <c r="G442" s="11" t="inlineStr"/>
+      <c r="H442" s="12" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="9" t="inlineStr">
+        <is>
+          <t>101:39</t>
+        </is>
+      </c>
+      <c r="B443" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] 90-60-90.</t>
+        </is>
+      </c>
+      <c r="C443" s="11" t="inlineStr"/>
+      <c r="D443" s="11" t="inlineStr"/>
+      <c r="E443" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F443" s="11" t="inlineStr"/>
+      <c r="G443" s="11" t="inlineStr"/>
+      <c r="H443" s="12" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="9" t="inlineStr">
+        <is>
+          <t>101:41</t>
+        </is>
+      </c>
+      <c r="B444" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] How they use it, how they use it.</t>
+        </is>
+      </c>
+      <c r="C444" s="11" t="inlineStr"/>
+      <c r="D444" s="11" t="inlineStr"/>
+      <c r="E444" s="11" t="inlineStr"/>
+      <c r="F444" s="11" t="inlineStr"/>
+      <c r="G444" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H444" s="12" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="9" t="inlineStr">
+        <is>
+          <t>101:52</t>
+        </is>
+      </c>
+      <c r="B445" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] 90-60-90.</t>
+        </is>
+      </c>
+      <c r="C445" s="11" t="inlineStr"/>
+      <c r="D445" s="11" t="inlineStr"/>
+      <c r="E445" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F445" s="11" t="inlineStr"/>
+      <c r="G445" s="11" t="inlineStr"/>
+      <c r="H445" s="12" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="9" t="inlineStr">
+        <is>
+          <t>103:58</t>
+        </is>
+      </c>
+      <c r="B446" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] One is the foundation over the other.</t>
+        </is>
+      </c>
+      <c r="C446" s="11" t="inlineStr"/>
+      <c r="D446" s="11" t="inlineStr"/>
+      <c r="E446" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F446" s="11" t="inlineStr"/>
+      <c r="G446" s="11" t="inlineStr"/>
+      <c r="H446" s="12" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="9" t="inlineStr">
+        <is>
+          <t>105:35</t>
+        </is>
+      </c>
+      <c r="B447" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Ah, the good thing that this is the number one or number two.</t>
+        </is>
+      </c>
+      <c r="C447" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D447" s="11" t="inlineStr"/>
+      <c r="E447" s="11" t="inlineStr"/>
+      <c r="F447" s="11" t="inlineStr"/>
+      <c r="G447" s="11" t="inlineStr"/>
+      <c r="H447" s="12" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="9" t="inlineStr">
+        <is>
+          <t>105:41</t>
+        </is>
+      </c>
+      <c r="B448" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] No, the PDF.</t>
+        </is>
+      </c>
+      <c r="C448" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D448" s="11" t="inlineStr"/>
+      <c r="E448" s="11" t="inlineStr"/>
+      <c r="F448" s="11" t="inlineStr"/>
+      <c r="G448" s="11" t="inlineStr"/>
+      <c r="H448" s="12" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="9" t="inlineStr">
+        <is>
+          <t>105:44</t>
+        </is>
+      </c>
+      <c r="B449" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] the PTA you have brought it.</t>
+        </is>
+      </c>
+      <c r="C449" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D449" s="11" t="inlineStr"/>
+      <c r="E449" s="11" t="inlineStr"/>
+      <c r="F449" s="11" t="inlineStr"/>
+      <c r="G449" s="11" t="inlineStr"/>
+      <c r="H449" s="12" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="9" t="inlineStr">
+        <is>
+          <t>105:45</t>
+        </is>
+      </c>
+      <c r="B450" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] I think I'm gonna get the feedback from your side.</t>
+        </is>
+      </c>
+      <c r="C450" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D450" s="11" t="inlineStr"/>
+      <c r="E450" s="11" t="inlineStr"/>
+      <c r="F450" s="11" t="inlineStr"/>
+      <c r="G450" s="11" t="inlineStr"/>
+      <c r="H450" s="12" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="9" t="inlineStr">
+        <is>
+          <t>105:48</t>
+        </is>
+      </c>
+      <c r="B451" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Because for them, I did it the way I was expecting from there.</t>
+        </is>
+      </c>
+      <c r="C451" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D451" s="11" t="inlineStr"/>
+      <c r="E451" s="11" t="inlineStr"/>
+      <c r="F451" s="11" t="inlineStr"/>
+      <c r="G451" s="11" t="inlineStr"/>
+      <c r="H451" s="12" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="9" t="inlineStr">
+        <is>
+          <t>105:53</t>
+        </is>
+      </c>
+      <c r="B452" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] And then the other side also I'm trying to match it.</t>
+        </is>
+      </c>
+      <c r="C452" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D452" s="11" t="inlineStr"/>
+      <c r="E452" s="11" t="inlineStr"/>
+      <c r="F452" s="11" t="inlineStr"/>
+      <c r="G452" s="11" t="inlineStr"/>
+      <c r="H452" s="12" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="9" t="inlineStr">
+        <is>
+          <t>110:57</t>
+        </is>
+      </c>
+      <c r="B453" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Okay. If the the the location of the solar pv is near to the location and there is no electricity.</t>
+        </is>
+      </c>
+      <c r="C453" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D453" s="11" t="inlineStr"/>
+      <c r="E453" s="11" t="inlineStr"/>
+      <c r="F453" s="11" t="inlineStr"/>
+      <c r="G453" s="11" t="inlineStr"/>
+      <c r="H453" s="12" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="9" t="inlineStr">
+        <is>
+          <t>111:08</t>
+        </is>
+      </c>
+      <c r="B454" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] So after after we give more capacity uh in the in the in the past it could be give them the electricity and also the power.</t>
+        </is>
+      </c>
+      <c r="C454" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D454" s="11" t="inlineStr"/>
+      <c r="E454" s="11" t="inlineStr"/>
+      <c r="F454" s="11" t="inlineStr"/>
+      <c r="G454" s="11" t="inlineStr"/>
+      <c r="H454" s="12" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="9" t="inlineStr">
+        <is>
+          <t>120:00</t>
+        </is>
+      </c>
+      <c r="B455" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] create a little bit with Caesar.</t>
+        </is>
+      </c>
+      <c r="C455" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D455" s="11" t="inlineStr"/>
+      <c r="E455" s="11" t="inlineStr"/>
+      <c r="F455" s="11" t="inlineStr"/>
+      <c r="G455" s="11" t="inlineStr"/>
+      <c r="H455" s="12" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="9" t="inlineStr">
+        <is>
+          <t>130:09</t>
+        </is>
+      </c>
+      <c r="B456" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Okay, then.</t>
+        </is>
+      </c>
+      <c r="C456" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D456" s="11" t="inlineStr"/>
+      <c r="E456" s="11" t="inlineStr"/>
+      <c r="F456" s="11" t="inlineStr"/>
+      <c r="G456" s="11" t="inlineStr"/>
+      <c r="H456" s="12" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="9" t="inlineStr">
+        <is>
+          <t>130:10</t>
+        </is>
+      </c>
+      <c r="B457" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Okay, thank you.</t>
+        </is>
+      </c>
+      <c r="C457" s="11" t="inlineStr"/>
+      <c r="D457" s="11" t="inlineStr"/>
+      <c r="E457" s="11" t="inlineStr"/>
+      <c r="F457" s="11" t="inlineStr"/>
+      <c r="G457" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H457" s="12" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="9" t="inlineStr">
+        <is>
+          <t>130:15</t>
+        </is>
+      </c>
+      <c r="B458" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Alameda.</t>
+        </is>
+      </c>
+      <c r="C458" s="11" t="inlineStr"/>
+      <c r="D458" s="11" t="inlineStr"/>
+      <c r="E458" s="11" t="inlineStr"/>
+      <c r="F458" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G458" s="11" t="inlineStr"/>
+      <c r="H458" s="12" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="9" t="inlineStr">
+        <is>
+          <t>130:16</t>
+        </is>
+      </c>
+      <c r="B459" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Alameda.</t>
+        </is>
+      </c>
+      <c r="C459" s="11" t="inlineStr"/>
+      <c r="D459" s="11" t="inlineStr"/>
+      <c r="E459" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F459" s="11" t="inlineStr"/>
+      <c r="G459" s="11" t="inlineStr"/>
+      <c r="H459" s="12" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="9" t="inlineStr">
+        <is>
+          <t>130:24</t>
+        </is>
+      </c>
+      <c r="B460" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Yo.</t>
+        </is>
+      </c>
+      <c r="C460" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D460" s="11" t="inlineStr"/>
+      <c r="E460" s="11" t="inlineStr"/>
+      <c r="F460" s="11" t="inlineStr"/>
+      <c r="G460" s="11" t="inlineStr"/>
+      <c r="H460" s="12" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="9" t="inlineStr">
+        <is>
+          <t>130:28</t>
+        </is>
+      </c>
+      <c r="B461" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] Sí.</t>
+        </is>
+      </c>
+      <c r="C461" s="11" t="inlineStr"/>
+      <c r="D461" s="11" t="inlineStr"/>
+      <c r="E461" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F461" s="11" t="inlineStr"/>
+      <c r="G461" s="11" t="inlineStr"/>
+      <c r="H461" s="12" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="9" t="inlineStr">
+        <is>
+          <t>131:05</t>
+        </is>
+      </c>
+      <c r="B462" s="10" t="inlineStr">
+        <is>
+          <t>[Voluntary Response] I sent you it email me.</t>
+        </is>
+      </c>
+      <c r="C462" s="11" t="inlineStr"/>
+      <c r="D462" s="11" t="inlineStr"/>
+      <c r="E462" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F462" s="11" t="inlineStr"/>
+      <c r="G462" s="11" t="inlineStr"/>
+      <c r="H462" s="12" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="9" t="inlineStr">
+        <is>
+          <t>131:10</t>
+        </is>
+      </c>
+      <c r="B463" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] He's going to perhaps to just the things but also that people next week maybe if if I if you get your feedback then the next</t>
+        </is>
+      </c>
+      <c r="C463" s="11" t="inlineStr"/>
+      <c r="D463" s="11" t="inlineStr"/>
+      <c r="E463" s="11" t="inlineStr"/>
+      <c r="F463" s="11" t="inlineStr"/>
+      <c r="G463" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H463" s="12" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="9" t="inlineStr">
+        <is>
+          <t>131:35</t>
+        </is>
+      </c>
+      <c r="B464" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Okay, maybe Friday.</t>
+        </is>
+      </c>
+      <c r="C464" s="11" t="inlineStr"/>
+      <c r="D464" s="11" t="inlineStr"/>
+      <c r="E464" s="11" t="inlineStr"/>
+      <c r="F464" s="11" t="inlineStr"/>
+      <c r="G464" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H464" s="12" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="9" t="inlineStr">
+        <is>
+          <t>131:36</t>
+        </is>
+      </c>
+      <c r="B465" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] So that maybe the next presentation might be our last. It might not be because you can just Yeah, yeah, yeah.</t>
+        </is>
+      </c>
+      <c r="C465" s="11" t="inlineStr"/>
+      <c r="D465" s="11" t="inlineStr"/>
+      <c r="E465" s="11" t="inlineStr"/>
+      <c r="F465" s="11" t="inlineStr"/>
+      <c r="G465" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H465" s="12" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="9" t="inlineStr">
+        <is>
+          <t>132:16</t>
+        </is>
+      </c>
+      <c r="B466" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] The first two slides the first two slides is from your comment.</t>
+        </is>
+      </c>
+      <c r="C466" s="11" t="inlineStr"/>
+      <c r="D466" s="11" t="inlineStr"/>
+      <c r="E466" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F466" s="11" t="inlineStr"/>
+      <c r="G466" s="11" t="inlineStr"/>
+      <c r="H466" s="12" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="9" t="inlineStr">
+        <is>
+          <t>132:20</t>
+        </is>
+      </c>
+      <c r="B467" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Like uh the problem the Y Y3.</t>
+        </is>
+      </c>
+      <c r="C467" s="11" t="inlineStr"/>
+      <c r="D467" s="11" t="inlineStr"/>
+      <c r="E467" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F467" s="11" t="inlineStr"/>
+      <c r="G467" s="11" t="inlineStr"/>
+      <c r="H467" s="12" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="9" t="inlineStr">
+        <is>
+          <t>132:23</t>
+        </is>
+      </c>
+      <c r="B468" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] I did it. I changed it to problem statement kind of.</t>
+        </is>
+      </c>
+      <c r="C468" s="11" t="inlineStr"/>
+      <c r="D468" s="11" t="inlineStr"/>
+      <c r="E468" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F468" s="11" t="inlineStr"/>
+      <c r="G468" s="11" t="inlineStr"/>
+      <c r="H468" s="12" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="9" t="inlineStr">
+        <is>
+          <t>132:26</t>
+        </is>
+      </c>
+      <c r="B469" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] And then the comparison between the why the other countries.</t>
+        </is>
+      </c>
+      <c r="C469" s="11" t="inlineStr"/>
+      <c r="D469" s="11" t="inlineStr"/>
+      <c r="E469" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F469" s="11" t="inlineStr"/>
+      <c r="G469" s="11" t="inlineStr"/>
+      <c r="H469" s="12" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="9" t="inlineStr">
+        <is>
+          <t>132:31</t>
+        </is>
+      </c>
+      <c r="B470" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] Because I did like it's like a a table.</t>
+        </is>
+      </c>
+      <c r="C470" s="11" t="inlineStr"/>
+      <c r="D470" s="11" t="inlineStr"/>
+      <c r="E470" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F470" s="11" t="inlineStr"/>
+      <c r="G470" s="11" t="inlineStr"/>
+      <c r="H470" s="12" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="9" t="inlineStr">
+        <is>
+          <t>132:37</t>
+        </is>
+      </c>
+      <c r="B471" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] I did the Estonia, Japan, UK, US.</t>
+        </is>
+      </c>
+      <c r="C471" s="11" t="inlineStr"/>
+      <c r="D471" s="11" t="inlineStr"/>
+      <c r="E471" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F471" s="11" t="inlineStr"/>
+      <c r="G471" s="11" t="inlineStr"/>
+      <c r="H471" s="12" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="9" t="inlineStr">
+        <is>
+          <t>132:42</t>
+        </is>
+      </c>
+      <c r="B472" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] But the good thing I saw because for me as I as you said from the practice of Rwanda.</t>
+        </is>
+      </c>
+      <c r="C472" s="11" t="inlineStr"/>
+      <c r="D472" s="11" t="inlineStr"/>
+      <c r="E472" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F472" s="11" t="inlineStr"/>
+      <c r="G472" s="11" t="inlineStr"/>
+      <c r="H472" s="12" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="9" t="inlineStr">
+        <is>
+          <t>132:48</t>
+        </is>
+      </c>
+      <c r="B473" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] We link I link with the what? With the SIM card.</t>
+        </is>
+      </c>
+      <c r="C473" s="11" t="inlineStr"/>
+      <c r="D473" s="11" t="inlineStr"/>
+      <c r="E473" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F473" s="11" t="inlineStr"/>
+      <c r="G473" s="11" t="inlineStr"/>
+      <c r="H473" s="12" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="9" t="inlineStr">
+        <is>
+          <t>132:50</t>
+        </is>
+      </c>
+      <c r="B474" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] But you may find some countries they don't link.</t>
+        </is>
+      </c>
+      <c r="C474" s="11" t="inlineStr"/>
+      <c r="D474" s="11" t="inlineStr"/>
+      <c r="E474" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F474" s="11" t="inlineStr"/>
+      <c r="G474" s="11" t="inlineStr"/>
+      <c r="H474" s="12" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="9" t="inlineStr">
+        <is>
+          <t>132:52</t>
+        </is>
+      </c>
+      <c r="B475" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] So that's you can see that the scores how I attracted it.</t>
+        </is>
+      </c>
+      <c r="C475" s="11" t="inlineStr"/>
+      <c r="D475" s="11" t="inlineStr"/>
+      <c r="E475" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F475" s="11" t="inlineStr"/>
+      <c r="G475" s="11" t="inlineStr"/>
+      <c r="H475" s="12" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="9" t="inlineStr">
+        <is>
+          <t>133:09</t>
+        </is>
+      </c>
+      <c r="B476" s="10" t="inlineStr">
+        <is>
+          <t>[Comment] So for the the leg up to take I do have it.</t>
+        </is>
+      </c>
+      <c r="C476" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D476" s="11" t="inlineStr"/>
+      <c r="E476" s="11" t="inlineStr"/>
+      <c r="F476" s="11" t="inlineStr"/>
+      <c r="G476" s="11" t="inlineStr"/>
+      <c r="H476" s="12" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="B477" s="14" t="inlineStr">
         <is>
           <t>TOTAL (sum of scores)</t>
         </is>
       </c>
-      <c r="C425" s="15" t="n">
-        <v>410</v>
-      </c>
-      <c r="D425" s="15" t="n">
+      <c r="C477" s="15" t="n">
+        <v>452</v>
+      </c>
+      <c r="D477" s="15" t="n">
         <v>165</v>
       </c>
-      <c r="E425" s="15" t="n">
-        <v>81</v>
-      </c>
-      <c r="F425" s="15" t="n">
-        <v>81</v>
-      </c>
-      <c r="G425" s="15" t="n">
-        <v>232</v>
-      </c>
-      <c r="H425" s="16" t="n"/>
-    </row>
-    <row r="426">
-      <c r="B426" s="17" t="inlineStr">
+      <c r="E477" s="15" t="n">
+        <v>140</v>
+      </c>
+      <c r="F477" s="15" t="n">
+        <v>83</v>
+      </c>
+      <c r="G477" s="15" t="n">
+        <v>254</v>
+      </c>
+      <c r="H477" s="16" t="n"/>
+    </row>
+    <row r="478">
+      <c r="B478" s="17" t="inlineStr">
         <is>
           <t>Max possible (n_opp × 6)</t>
         </is>
       </c>
-      <c r="C426" s="18" t="n">
-        <v>708</v>
-      </c>
-      <c r="D426" s="18" t="n">
+      <c r="C478" s="18" t="n">
+        <v>780</v>
+      </c>
+      <c r="D478" s="18" t="n">
         <v>294</v>
       </c>
-      <c r="E426" s="18" t="n">
-        <v>150</v>
-      </c>
-      <c r="F426" s="18" t="n">
-        <v>168</v>
-      </c>
-      <c r="G426" s="18" t="n">
-        <v>456</v>
-      </c>
-      <c r="H426" s="12" t="n"/>
-    </row>
-    <row r="427">
-      <c r="B427" s="19" t="inlineStr">
+      <c r="E478" s="18" t="n">
+        <v>258</v>
+      </c>
+      <c r="F478" s="18" t="n">
+        <v>174</v>
+      </c>
+      <c r="G478" s="18" t="n">
+        <v>498</v>
+      </c>
+      <c r="H478" s="12" t="n"/>
+    </row>
+    <row r="479">
+      <c r="B479" s="19" t="inlineStr">
         <is>
           <t>% Grade (max 7.5%)</t>
         </is>
       </c>
-      <c r="C427" s="20" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="D427" s="20" t="n">
+      <c r="C479" s="20" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="D479" s="20" t="n">
         <v>4.21</v>
       </c>
-      <c r="E427" s="20" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="F427" s="20" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="G427" s="20" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="H427" s="21" t="n"/>
-    </row>
-    <row r="429">
-      <c r="A429" s="7" t="inlineStr">
+      <c r="E479" s="20" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="F479" s="20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="G479" s="20" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H479" s="21" t="n"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="7" t="inlineStr">
         <is>
           <t>RESUMEN COMPONENTE A — COMPARATIVA DOS ESCENARIOS</t>
         </is>
       </c>
     </row>
-    <row r="430">
-      <c r="A430" s="8" t="inlineStr">
+    <row r="482">
+      <c r="A482" s="8" t="inlineStr">
         <is>
           <t>Escenario A: literal del silabo (solo calidad promedio). Escenario B: igual + bonus por cantidad de contribuciones (5-14:+0.5  15-29:+1.0  30+:+1.5)</t>
         </is>
       </c>
     </row>
-    <row r="432">
-      <c r="A432" s="4" t="inlineStr">
+    <row r="484">
+      <c r="A484" s="4" t="inlineStr">
         <is>
           <t>Student</t>
         </is>
       </c>
-      <c r="B432" s="4" t="inlineStr">
+      <c r="B484" s="4" t="inlineStr">
         <is>
           <t>Prep (7.5)</t>
         </is>
       </c>
-      <c r="C432" s="4" t="inlineStr">
+      <c r="C484" s="4" t="inlineStr">
         <is>
           <t>Att (5)</t>
         </is>
       </c>
-      <c r="D432" s="4" t="inlineStr">
+      <c r="D484" s="4" t="inlineStr">
         <is>
           <t>─ Esc A ─</t>
         </is>
       </c>
-      <c r="E432" s="4" t="inlineStr">
+      <c r="E484" s="4" t="inlineStr">
         <is>
           <t>Part A</t>
         </is>
       </c>
-      <c r="F432" s="4" t="inlineStr">
+      <c r="F484" s="4" t="inlineStr">
         <is>
           <t>TOTAL A</t>
         </is>
       </c>
-      <c r="G432" s="4" t="inlineStr">
+      <c r="G484" s="4" t="inlineStr">
         <is>
           <t>% A</t>
         </is>
       </c>
-      <c r="H432" s="4" t="inlineStr">
+      <c r="H484" s="4" t="inlineStr">
         <is>
           <t>─ Esc B ─</t>
         </is>
       </c>
-      <c r="I432" s="4" t="inlineStr">
+      <c r="I484" s="4" t="inlineStr">
         <is>
           <t>Part B (+bonus)</t>
         </is>
       </c>
-      <c r="J432" s="4" t="inlineStr">
+      <c r="J484" s="4" t="inlineStr">
         <is>
           <t>TOTAL B</t>
         </is>
       </c>
-      <c r="K432" s="4" t="inlineStr">
+      <c r="K484" s="4" t="inlineStr">
         <is>
           <t>% B</t>
         </is>
       </c>
     </row>
-    <row r="433">
-      <c r="A433" s="22" t="inlineStr">
+    <row r="485">
+      <c r="A485" s="22" t="inlineStr">
         <is>
           <t>Aryang</t>
         </is>
       </c>
-      <c r="B433" s="23" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="C433" s="23" t="n">
+      <c r="B485" s="23" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="C485" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="D433" s="9" t="inlineStr"/>
-      <c r="E433" s="23" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="F433" s="24" t="n">
-        <v>12.58</v>
-      </c>
-      <c r="G433" s="25" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="H433" s="9" t="inlineStr"/>
-      <c r="I433" s="9" t="inlineStr">
-        <is>
-          <t>5.84 (+1.5)</t>
-        </is>
-      </c>
-      <c r="J433" s="20" t="n">
-        <v>14.08</v>
-      </c>
-      <c r="K433" s="25" t="n">
-        <v>70.40000000000001</v>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" s="22" t="inlineStr">
+      <c r="D485" s="9" t="inlineStr"/>
+      <c r="E485" s="23" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="F485" s="24" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="G485" s="25" t="n">
+        <v>63</v>
+      </c>
+      <c r="H485" s="9" t="inlineStr"/>
+      <c r="I485" s="9" t="inlineStr">
+        <is>
+          <t>5.85 (+1.5)</t>
+        </is>
+      </c>
+      <c r="J485" s="20" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="K485" s="25" t="n">
+        <v>70.5</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="22" t="inlineStr">
         <is>
           <t>Mega</t>
         </is>
       </c>
-      <c r="B434" s="23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="C434" s="23" t="n">
+      <c r="B486" s="23" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="C486" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="D434" s="9" t="inlineStr"/>
-      <c r="E434" s="23" t="n">
+      <c r="D486" s="9" t="inlineStr"/>
+      <c r="E486" s="23" t="n">
         <v>4.21</v>
       </c>
-      <c r="F434" s="24" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="G434" s="25" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="H434" s="9" t="inlineStr"/>
-      <c r="I434" s="9" t="inlineStr">
+      <c r="F486" s="24" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="G486" s="25" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="H486" s="9" t="inlineStr"/>
+      <c r="I486" s="9" t="inlineStr">
         <is>
           <t>5.71 (+1.5)</t>
         </is>
       </c>
-      <c r="J434" s="20" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="K434" s="25" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" s="22" t="inlineStr">
+      <c r="J486" s="20" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="K486" s="25" t="n">
+        <v>67.2</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="22" t="inlineStr">
         <is>
           <t>Chilaka</t>
         </is>
       </c>
-      <c r="B435" s="23" t="n">
+      <c r="B487" s="23" t="n">
         <v>2.27</v>
       </c>
-      <c r="C435" s="23" t="n">
+      <c r="C487" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="D435" s="9" t="inlineStr"/>
-      <c r="E435" s="23" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="F435" s="24" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="G435" s="25" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="H435" s="9" t="inlineStr"/>
-      <c r="I435" s="9" t="inlineStr">
-        <is>
-          <t>5.05 (+1.0)</t>
-        </is>
-      </c>
-      <c r="J435" s="20" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="K435" s="25" t="n">
-        <v>61.6</v>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" s="22" t="inlineStr">
+      <c r="D487" s="9" t="inlineStr"/>
+      <c r="E487" s="23" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="F487" s="24" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="G487" s="25" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="H487" s="9" t="inlineStr"/>
+      <c r="I487" s="9" t="inlineStr">
+        <is>
+          <t>5.57 (+1.5)</t>
+        </is>
+      </c>
+      <c r="J487" s="20" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="K487" s="25" t="n">
+        <v>64.2</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="22" t="inlineStr">
         <is>
           <t>Grace</t>
         </is>
       </c>
-      <c r="B436" s="23" t="n">
+      <c r="B488" s="23" t="n">
         <v>2.5</v>
       </c>
-      <c r="C436" s="23" t="n">
+      <c r="C488" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="D436" s="9" t="inlineStr"/>
-      <c r="E436" s="23" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="F436" s="24" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="G436" s="25" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="H436" s="9" t="inlineStr"/>
-      <c r="I436" s="9" t="inlineStr">
-        <is>
-          <t>4.62 (+1.0)</t>
-        </is>
-      </c>
-      <c r="J436" s="20" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="K436" s="25" t="n">
-        <v>60.6</v>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" s="22" t="inlineStr">
+      <c r="D488" s="9" t="inlineStr"/>
+      <c r="E488" s="23" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F488" s="24" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="G488" s="25" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="H488" s="9" t="inlineStr"/>
+      <c r="I488" s="9" t="inlineStr">
+        <is>
+          <t>4.58 (+1.0)</t>
+        </is>
+      </c>
+      <c r="J488" s="20" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="K488" s="25" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="22" t="inlineStr">
         <is>
           <t>Sthepen</t>
         </is>
       </c>
-      <c r="B437" s="23" t="n">
-        <v>3</v>
-      </c>
-      <c r="C437" s="23" t="n">
+      <c r="B489" s="23" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="C489" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="D437" s="9" t="inlineStr"/>
-      <c r="E437" s="23" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="F437" s="24" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="G437" s="25" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="H437" s="9" t="inlineStr"/>
-      <c r="I437" s="9" t="inlineStr">
-        <is>
-          <t>5.32 (+1.5)</t>
-        </is>
-      </c>
-      <c r="J437" s="20" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="K437" s="25" t="n">
-        <v>66.59999999999999</v>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" s="26" t="inlineStr">
+      <c r="D489" s="9" t="inlineStr"/>
+      <c r="E489" s="23" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="F489" s="24" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="G489" s="25" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="H489" s="9" t="inlineStr"/>
+      <c r="I489" s="9" t="inlineStr">
+        <is>
+          <t>5.33 (+1.5)</t>
+        </is>
+      </c>
+      <c r="J489" s="20" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K489" s="25" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="26" t="inlineStr">
         <is>
           <t>🟡 Escenario A — apego literal al silabo</t>
         </is>
       </c>
     </row>
-    <row r="440">
-      <c r="A440" s="27" t="inlineStr">
+    <row r="492">
+      <c r="A492" s="27" t="inlineStr">
         <is>
           <t>🟢 Escenario B — sugerido: reconoce engagement sin romper rúbrica</t>
         </is>
@@ -9211,13 +10231,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A430:J430"/>
+    <mergeCell ref="A481:J481"/>
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A126:I126"/>
-    <mergeCell ref="A429:J429"/>
-    <mergeCell ref="A125:I125"/>
+    <mergeCell ref="A140:I140"/>
+    <mergeCell ref="A482:J482"/>
+    <mergeCell ref="A139:I139"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
